--- a/Data/output/DIR Stroke Position.xlsx
+++ b/Data/output/DIR Stroke Position.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I111"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -507,12 +507,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[np.float64(11.578121115089829), np.float64(-69.26269163520737)]</t>
+          <t>[np.float64(3.5013435951142924), np.float64(-64.05833919054744)]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[np.float64(11.578121115089829), np.float64(0.0)]</t>
+          <t>[np.float64(3.5013435951142924), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -548,12 +548,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[np.float64(-34.344386760336945), np.float64(-28.115121223295375)]</t>
+          <t>[np.float64(4.581735356988119), np.float64(-22.885568405179058)]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[np.float64(-34.344386760336945), np.float64(0.0)]</t>
+          <t>[np.float64(4.581735356988119), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -589,12 +589,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[np.float64(11.42572582141743), np.float64(-32.642505538166674)]</t>
+          <t>[np.float64(4.638391256028882), np.float64(-48.18827870449227)]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[np.float64(11.42572582141743), np.float64(0.0)]</t>
+          <t>[np.float64(4.638391256028882), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[np.float64(-0.5403354094151354), np.float64(-66.94090074426532)]</t>
+          <t>[np.float64(-4.574354243009651), np.float64(-58.12003688277328)]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[np.float64(-0.5403354094151354), np.float64(0.0)]</t>
+          <t>[np.float64(-4.574354243009651), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[np.float64(-30.203950283480197), np.float64(-77.17347117137797)]</t>
+          <t>[np.float64(-56.43513320748731), np.float64(-21.183400826473033)]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[np.float64(-30.203950283480197), np.float64(0.0)]</t>
+          <t>[np.float64(-56.43513320748731), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -712,12 +712,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[np.float64(-58.535819387082114), np.float64(-49.95484235851979)]</t>
+          <t>[np.float64(0.01911319427827607), np.float64(-70.9198988504937)]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[np.float64(-58.535819387082114), np.float64(0.0)]</t>
+          <t>[np.float64(0.01911319427827607), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[np.float64(-33.634244151564985), np.float64(-92.97811972063373)]</t>
+          <t>[np.float64(-23.134064642597806), np.float64(-56.58447804838052)]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[np.float64(-33.634244151564985), np.float64(0.0)]</t>
+          <t>[np.float64(-23.134064642597806), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -794,12 +794,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[np.float64(-39.069849125845224), np.float64(-54.99413064824839)]</t>
+          <t>[np.float64(6.207016815083165), np.float64(-55.472452019343564)]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[np.float64(-39.069849125845224), np.float64(0.0)]</t>
+          <t>[np.float64(6.207016815083165), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[np.float64(-65.1916762839582), np.float64(-80.99355293449584)]</t>
+          <t>[np.float64(-36.60873390391324), np.float64(-57.80574786154982)]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[np.float64(-65.1916762839582), np.float64(0.0)]</t>
+          <t>[np.float64(-36.60873390391324), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[np.float64(4.591640841626699), np.float64(-77.23615293009756)]</t>
+          <t>[np.float64(-23.576880888141176), np.float64(-62.880164716768824)]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[np.float64(4.591640841626699), np.float64(0.0)]</t>
+          <t>[np.float64(-23.576880888141176), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[np.float64(-35.563033669199996), np.float64(-51.28690607193101)]</t>
+          <t>[np.float64(-2.5704144094446377), np.float64(-62.917712381296354)]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[np.float64(-35.563033669199996), np.float64(0.0)]</t>
+          <t>[np.float64(-2.5704144094446377), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -958,12 +958,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[np.float64(-30.067652612470994), np.float64(-45.35084932792515)]</t>
+          <t>[np.float64(14.015799149866268), np.float64(-65.99355312689951)]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[np.float64(-30.067652612470994), np.float64(0.0)]</t>
+          <t>[np.float64(14.015799149866268), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[np.float64(-2.415699957881273), np.float64(-20.696740490339778)]</t>
+          <t>[np.float64(-26.519525999658995), np.float64(-41.01179992973978)]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[np.float64(-2.415699957881273), np.float64(0.0)]</t>
+          <t>[np.float64(-26.519525999658992), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[np.float64(-58.484351349597915), np.float64(-58.36994279054713)]</t>
+          <t>[np.float64(-37.238464054476346), np.float64(-54.504558937407865)]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[np.float64(-58.484351349597915), np.float64(0.0)]</t>
+          <t>[np.float64(-37.238464054476346), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[np.float64(7.449802582737874), np.float64(-55.28947053773228)]</t>
+          <t>[np.float64(3.034548673170619), np.float64(-8.327449813530379)]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[np.float64(7.449802582737874), np.float64(0.0)]</t>
+          <t>[np.float64(3.034548673170619), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[np.float64(3.117248667027326), np.float64(-66.19059801653104)]</t>
+          <t>[np.float64(-46.812509361612314), np.float64(-69.1475386142808)]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[np.float64(3.117248667027326), np.float64(0.0)]</t>
+          <t>[np.float64(-46.812509361612314), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[np.float64(-22.22464647135412), np.float64(-4.105761330458165)]</t>
+          <t>[np.float64(8.464114627856716), np.float64(-7.096887051262428)]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[np.float64(-22.22464647135412), np.float64(0.0)]</t>
+          <t>[np.float64(8.464114627856716), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[np.float64(-18.657768891910763), np.float64(-70.50848948363668)]</t>
+          <t>[np.float64(15.98159478410821), np.float64(-1.2850265718864335)]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[np.float64(-18.657768891910763), np.float64(0.0)]</t>
+          <t>[np.float64(15.98159478410821), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[np.float64(-14.042813556611577), np.float64(-66.40539672387891)]</t>
+          <t>[np.float64(2.6650373245941665), np.float64(-18.768740071144222)]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[np.float64(-14.042813556611577), np.float64(0.0)]</t>
+          <t>[np.float64(2.6650373245941665), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[np.float64(-9.257834312700155), np.float64(-3.702662434713176)]</t>
+          <t>[np.float64(-28.999630874917358), np.float64(-54.13582847227052)]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[np.float64(-9.257834312700155), np.float64(0.0)]</t>
+          <t>[np.float64(-28.999630874917358), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[np.float64(-25.272577989998496), np.float64(-2.6799608409108657)]</t>
+          <t>[np.float64(7.330292307534023), np.float64(-33.276714595334326)]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[np.float64(-25.272577989998496), np.float64(0.0)]</t>
+          <t>[np.float64(7.330292307534023), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1368,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[np.float64(-40.0188684373499), np.float64(-43.04354189608743)]</t>
+          <t>[np.float64(-4.1862927437117605), np.float64(-11.526308988994515)]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[np.float64(-40.0188684373499), np.float64(0.0)]</t>
+          <t>[np.float64(-4.1862927437117605), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1409,12 +1409,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[np.float64(-39.98754021152267), np.float64(-78.91472522167817)]</t>
+          <t>[np.float64(-70.83917944459634), np.float64(-54.650266672159)]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[np.float64(-39.98754021152267), np.float64(0.0)]</t>
+          <t>[np.float64(-70.83917944459634), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[np.float64(-5.279498063978977), np.float64(-51.952198134467274)]</t>
+          <t>[np.float64(-20.058848010131385), np.float64(-66.72640675128989)]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[np.float64(-5.279498063978977), np.float64(0.0)]</t>
+          <t>[np.float64(-20.058848010131385), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[np.float64(-53.0123709450954), np.float64(-7.199482659874718)]</t>
+          <t>[np.float64(-34.35462761819679), np.float64(-53.48117917614401)]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[np.float64(-53.0123709450954), np.float64(0.0)]</t>
+          <t>[np.float64(-34.35462761819679), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[np.float64(10.629279246996958), np.float64(-15.622901805596484)]</t>
+          <t>[np.float64(-8.982944910994078), np.float64(-76.01926112956491)]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[np.float64(10.629279246996958), np.float64(0.0)]</t>
+          <t>[np.float64(-8.982944910994078), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[np.float64(-7.487371808289538), np.float64(-51.434012087796965)]</t>
+          <t>[np.float64(-1.3457053210349557), np.float64(-39.03413976127037)]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[np.float64(-7.487371808289538), np.float64(0.0)]</t>
+          <t>[np.float64(-1.3457053210349557), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[np.float64(-59.267402369561545), np.float64(-34.846934193916596)]</t>
+          <t>[np.float64(-39.95002954052267), np.float64(-38.20572121120067)]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[np.float64(-59.26740236956155), np.float64(0.0)]</t>
+          <t>[np.float64(-39.95002954052267), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[np.float64(-45.34089263527199), np.float64(-30.41870568307337)]</t>
+          <t>[np.float64(1.0695797860926604), np.float64(-58.80959838536335)]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[np.float64(-45.34089263527199), np.float64(0.0)]</t>
+          <t>[np.float64(1.0695797860926604), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[np.float64(-32.86739502996531), np.float64(-32.68842911823873)]</t>
+          <t>[np.float64(-22.067462001598187), np.float64(-50.32511633208851)]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[np.float64(-32.86739502996531), np.float64(0.0)]</t>
+          <t>[np.float64(-22.067462001598187), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1737,12 +1737,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[np.float64(-34.065463705425174), np.float64(-31.177213831412104)]</t>
+          <t>[np.float64(-9.319312508359786), np.float64(-85.51852024217554)]</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[np.float64(-34.065463705425174), np.float64(0.0)]</t>
+          <t>[np.float64(-9.319312508359786), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1778,12 +1778,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[np.float64(12.385580042525476), np.float64(-87.90408522839006)]</t>
+          <t>[np.float64(-40.64252594633182), np.float64(-36.67674319616909)]</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[np.float64(12.385580042525476), np.float64(0.0)]</t>
+          <t>[np.float64(-40.64252594633182), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[np.float64(-81.1015014161018), np.float64(-73.17858980973888)]</t>
+          <t>[np.float64(6.476909735392951), np.float64(-65.79583893274673)]</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[np.float64(-81.10150141610178), np.float64(0.0)]</t>
+          <t>[np.float64(6.476909735392951), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[np.float64(4.568669111444066), np.float64(-76.30656432755049)]</t>
+          <t>[np.float64(-27.683353789958403), np.float64(-25.941195411384626)]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[np.float64(4.568669111444066), np.float64(0.0)]</t>
+          <t>[np.float64(-27.683353789958403), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1901,12 +1901,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[np.float64(-18.227016238744), np.float64(-7.50925608766002)]</t>
+          <t>[np.float64(-43.3145925197234), np.float64(-65.82815626292471)]</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[np.float64(-18.227016238744), np.float64(0.0)]</t>
+          <t>[np.float64(-43.3145925197234), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[np.float64(-4.969383897741196), np.float64(-12.569959801846338)]</t>
+          <t>[np.float64(-6.83699769886293), np.float64(-84.14318377277105)]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[np.float64(-4.969383897741196), np.float64(0.0)]</t>
+          <t>[np.float64(-6.83699769886293), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[np.float64(-2.3461526192137683), np.float64(-54.066996470218)]</t>
+          <t>[np.float64(-13.546385513916988), np.float64(-50.715166770215035)]</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[np.float64(-2.3461526192137683), np.float64(0.0)]</t>
+          <t>[np.float64(-13.546385513916988), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[np.float64(-57.53711988590269), np.float64(-9.744586871686266)]</t>
+          <t>[np.float64(-38.23762133374575), np.float64(-57.08898808047611)]</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[np.float64(-57.53711988590269), np.float64(0.0)]</t>
+          <t>[np.float64(-38.23762133374575), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2065,12 +2065,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[np.float64(-1.3140623342027737), np.float64(-6.53309999503773)]</t>
+          <t>[np.float64(-25.487917456226214), np.float64(-45.2597011609224)]</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[np.float64(-1.3140623342027737), np.float64(0.0)]</t>
+          <t>[np.float64(-25.487917456226214), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[np.float64(6.228326723465244), np.float64(-34.427637860113975)]</t>
+          <t>[np.float64(-12.689674433935508), np.float64(-24.761262826234628)]</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[np.float64(6.228326723465244), np.float64(0.0)]</t>
+          <t>[np.float64(-12.689674433935508), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[np.float64(-62.03667681205792), np.float64(-21.093919904250072)]</t>
+          <t>[np.float64(-21.230264419147602), np.float64(-65.26186800353724)]</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[np.float64(-62.03667681205792), np.float64(0.0)]</t>
+          <t>[np.float64(-21.230264419147602), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2188,12 +2188,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[np.float64(-54.13100663104293), np.float64(-50.406650309898616)]</t>
+          <t>[np.float64(-5.464560609484195), np.float64(-21.252450335921466)]</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[np.float64(-54.131006631042936), np.float64(0.0)]</t>
+          <t>[np.float64(-5.464560609484195), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[np.float64(-3.1835930232220306), np.float64(-58.827726090649215)]</t>
+          <t>[np.float64(8.923261555762835), np.float64(-40.708407169330904)]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[np.float64(-3.1835930232220306), np.float64(0.0)]</t>
+          <t>[np.float64(8.923261555762835), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[np.float64(-5.853879633738956), np.float64(-32.00580837048463)]</t>
+          <t>[np.float64(-3.339491567225906), np.float64(-27.869924031772797)]</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[np.float64(-5.853879633738956), np.float64(0.0)]</t>
+          <t>[np.float64(-3.339491567225906), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2311,12 +2311,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[np.float64(-54.656970025473385), np.float64(-29.925428905743672)]</t>
+          <t>[np.float64(-21.834987802726715), np.float64(-89.70161508256005)]</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[np.float64(-54.65697002547338), np.float64(0.0)]</t>
+          <t>[np.float64(-21.834987802726715), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[np.float64(-8.514711983467038), np.float64(-3.5160147603127996)]</t>
+          <t>[np.float64(-53.99547420421869), np.float64(-0.2592743429183031)]</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[np.float64(-8.514711983467038), np.float64(0.0)]</t>
+          <t>[np.float64(-53.99547420421869), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2393,12 +2393,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[np.float64(1.6037756956690714), np.float64(-52.05696857015904)]</t>
+          <t>[np.float64(5.162176588773718), np.float64(-43.44334969970429)]</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[np.float64(1.6037756956690714), np.float64(0.0)]</t>
+          <t>[np.float64(5.162176588773718), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[np.float64(-23.2134415965494), np.float64(-20.068023137112263)]</t>
+          <t>[np.float64(-13.926933447882092), np.float64(-24.414075933683364)]</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[np.float64(-23.2134415965494), np.float64(0.0)]</t>
+          <t>[np.float64(-13.926933447882092), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2475,12 +2475,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[np.float64(-41.35081144681712), np.float64(-21.989522173115077)]</t>
+          <t>[np.float64(-50.73539196918262), np.float64(-13.628272531685084)]</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[np.float64(-41.35081144681712), np.float64(0.0)]</t>
+          <t>[np.float64(-50.73539196918262), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2516,12 +2516,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[np.float64(-25.94364481417101), np.float64(-16.83996523410127)]</t>
+          <t>[np.float64(-8.699447987761317), np.float64(-41.771874976833345)]</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[np.float64(-25.94364481417101), np.float64(0.0)]</t>
+          <t>[np.float64(-8.699447987761317), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[np.float64(-37.59705449170237), np.float64(-40.2716448704346)]</t>
+          <t>[np.float64(-9.922840272569857), np.float64(-64.68709262126968)]</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[np.float64(-37.59705449170237), np.float64(0.0)]</t>
+          <t>[np.float64(-9.922840272569857), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[np.float64(0.07586255463293412), np.float64(-45.784574973708224)]</t>
+          <t>[np.float64(-61.777948131427365), np.float64(-73.80967719022702)]</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[np.float64(0.07586255463293412), np.float64(0.0)]</t>
+          <t>[np.float64(-61.777948131427365), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2639,12 +2639,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[np.float64(-14.548763903227922), np.float64(-54.05809847868173)]</t>
+          <t>[np.float64(-3.3847468190033396), np.float64(-5.0001364447646495)]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[np.float64(-14.548763903227922), np.float64(0.0)]</t>
+          <t>[np.float64(-3.3847468190033396), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[np.float64(10.12349184713797), np.float64(-17.311009960288715)]</t>
+          <t>[np.float64(-15.222078559235172), np.float64(-21.351325431832223)]</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[np.float64(10.12349184713797), np.float64(0.0)]</t>
+          <t>[np.float64(-15.222078559235172), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[np.float64(3.3922962739002145), np.float64(-97.75293187050138)]</t>
+          <t>[np.float64(9.268421471173923), np.float64(-16.587749901002894)]</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[np.float64(3.3922962739002145), np.float64(0.0)]</t>
+          <t>[np.float64(9.268421471173923), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>[np.float64(11.28004902111411), np.float64(-18.55045161025896)]</t>
+          <t>[np.float64(-27.06905230318941), np.float64(-45.09460231887075)]</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[np.float64(11.28004902111411), np.float64(0.0)]</t>
+          <t>[np.float64(-27.06905230318941), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[np.float64(0.6551515496311566), np.float64(-56.690249811521355)]</t>
+          <t>[np.float64(12.36904872177412), np.float64(-37.97464678871074)]</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[np.float64(0.6551515496311566), np.float64(0.0)]</t>
+          <t>[np.float64(12.36904872177412), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2844,12 +2844,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>[np.float64(-33.708075814961646), np.float64(-32.12603548028261)]</t>
+          <t>[np.float64(-8.441929903354861), np.float64(-11.130261839738424)]</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[np.float64(-33.708075814961646), np.float64(0.0)]</t>
+          <t>[np.float64(-8.441929903354861), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[np.float64(-16.104890831047854), np.float64(-16.359789413283792)]</t>
+          <t>[np.float64(-5.37186789697877), np.float64(-8.657313040085882)]</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[np.float64(-16.104890831047854), np.float64(0.0)]</t>
+          <t>[np.float64(-5.37186789697877), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[np.float64(-3.2738328954194458), np.float64(-36.26334363719317)]</t>
+          <t>[np.float64(-17.589748227114555), np.float64(-35.51562746438471)]</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[np.float64(-3.2738328954194458), np.float64(0.0)]</t>
+          <t>[np.float64(-17.589748227114555), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2967,12 +2967,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[np.float64(-42.721452822332544), np.float64(-21.042015498625034)]</t>
+          <t>[np.float64(2.901885562119304), np.float64(-6.985169542435273)]</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[np.float64(-42.721452822332544), np.float64(0.0)]</t>
+          <t>[np.float64(2.901885562119304), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[np.float64(-36.12093258850014), np.float64(-10.884372552532056)]</t>
+          <t>[np.float64(9.730865719902695), np.float64(-11.883261496000415)]</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[np.float64(-36.12093258850014), np.float64(0.0)]</t>
+          <t>[np.float64(9.730865719902695), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3049,12 +3049,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[np.float64(7.045158981274767), np.float64(-23.793390665741683)]</t>
+          <t>[np.float64(-20.21925977159941), np.float64(-33.537322353400455)]</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[np.float64(7.045158981274767), np.float64(0.0)]</t>
+          <t>[np.float64(-20.21925977159941), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3090,12 +3090,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[np.float64(-26.05950474586136), np.float64(-33.26564126042638)]</t>
+          <t>[np.float64(-0.45614261141352586), np.float64(-65.6410809315037)]</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[np.float64(-26.05950474586136), np.float64(0.0)]</t>
+          <t>[np.float64(-0.45614261141352586), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[np.float64(-56.24328825898137), np.float64(-47.147305332939716)]</t>
+          <t>[np.float64(1.1728995190107128), np.float64(-17.420120723498826)]</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[np.float64(-56.24328825898138), np.float64(0.0)]</t>
+          <t>[np.float64(1.1728995190107128), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3172,12 +3172,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[np.float64(-40.30649911901949), np.float64(-55.60682153588261)]</t>
+          <t>[np.float64(-0.28806927135684646), np.float64(-51.01873180108682)]</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[np.float64(-40.30649911901949), np.float64(0.0)]</t>
+          <t>[np.float64(-0.28806927135684646), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3213,12 +3213,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[np.float64(12.579099711259985), np.float64(-32.41952713916767)]</t>
+          <t>[np.float64(-3.5053571003440283), np.float64(-19.146781255651348)]</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[np.float64(12.579099711259985), np.float64(0.0)]</t>
+          <t>[np.float64(-3.5053571003440283), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>[np.float64(-8.230549518689003), np.float64(-6.275820051247024)]</t>
+          <t>[np.float64(11.815637438031942), np.float64(-41.71468172010238)]</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[np.float64(-8.230549518689003), np.float64(0.0)]</t>
+          <t>[np.float64(11.815637438031942), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3295,12 +3295,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[np.float64(-57.153709243675195), np.float64(-43.684552439126435)]</t>
+          <t>[np.float64(-20.175874017974436), np.float64(-13.187764724743033)]</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[np.float64(-57.15370924367519), np.float64(0.0)]</t>
+          <t>[np.float64(-20.175874017974436), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3336,12 +3336,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[np.float64(2.7872997774322243), np.float64(-65.23118377018567)]</t>
+          <t>[np.float64(15.16235970194839), np.float64(-57.97609207784819)]</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[np.float64(2.7872997774322243), np.float64(0.0)]</t>
+          <t>[np.float64(15.16235970194839), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3355,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3377,12 +3377,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[np.float64(10.0759744883282), np.float64(0.08353411907550878)]</t>
+          <t>[np.float64(-16.09325349180493), np.float64(-52.45946414795741)]</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[np.float64(10.0759744883282), np.float64(0.0)]</t>
+          <t>[np.float64(-16.09325349180493), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3418,12 +3418,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[np.float64(11.181903888346028), np.float64(-28.24458414327829)]</t>
+          <t>[np.float64(-14.738600543072806), np.float64(-19.102111305887263)]</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[np.float64(11.181903888346028), np.float64(0.0)]</t>
+          <t>[np.float64(-14.738600543072806), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>[np.float64(-56.34121622950456), np.float64(-32.47455251053859)]</t>
+          <t>[np.float64(-7.2821376724266145), np.float64(-32.146665851469976)]</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[np.float64(-56.34121622950456), np.float64(0.0)]</t>
+          <t>[np.float64(-7.2821376724266145), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3500,12 +3500,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[np.float64(-33.9450655171605), np.float64(-14.746023087544131)]</t>
+          <t>[np.float64(-23.12829761757213), np.float64(-28.870319000792847)]</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[np.float64(-33.9450655171605), np.float64(0.0)]</t>
+          <t>[np.float64(-23.12829761757213), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3541,12 +3541,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[np.float64(10.031147372069924), np.float64(-12.890223914962533)]</t>
+          <t>[np.float64(-0.2238922773581038), np.float64(-53.59732879807926)]</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[np.float64(10.031147372069924), np.float64(0.0)]</t>
+          <t>[np.float64(-0.2238922773581038), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>[np.float64(-17.53685445454225), np.float64(-6.770428081883921)]</t>
+          <t>[np.float64(-54.93614397777375), np.float64(-67.67404550329219)]</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[np.float64(-17.53685445454225), np.float64(0.0)]</t>
+          <t>[np.float64(-54.93614397777375), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[np.float64(-14.381524537603852), np.float64(-50.229275532773364)]</t>
+          <t>[np.float64(-22.880161184726163), np.float64(-8.304120079336414)]</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[np.float64(-14.381524537603852), np.float64(0.0)]</t>
+          <t>[np.float64(-22.880161184726163), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3664,12 +3664,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>[np.float64(-26.779371962863394), np.float64(-4.737330746692933)]</t>
+          <t>[np.float64(-33.46374077644728), np.float64(-39.872702642223686)]</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[np.float64(-26.779371962863394), np.float64(0.0)]</t>
+          <t>[np.float64(-33.46374077644728), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>[np.float64(10.95610763229432), np.float64(-66.34953723714622)]</t>
+          <t>[np.float64(-64.42620415898918), np.float64(-4.677410482550684)]</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[np.float64(10.95610763229432), np.float64(0.0)]</t>
+          <t>[np.float64(-64.42620415898918), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3746,12 +3746,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>[np.float64(-4.407741503359247), np.float64(-2.221917582435566)]</t>
+          <t>[np.float64(-1.158603157029546), np.float64(-44.09548559929968)]</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[np.float64(-4.407741503359247), np.float64(0.0)]</t>
+          <t>[np.float64(-1.158603157029546), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3787,12 +3787,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[np.float64(-23.54415141771831), np.float64(-90.02751543113274)]</t>
+          <t>[np.float64(-24.0512172446104), np.float64(-37.858178399278856)]</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[np.float64(-23.54415141771831), np.float64(0.0)]</t>
+          <t>[np.float64(-24.0512172446104), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[np.float64(-5.8994973907381905), np.float64(-62.721547882161246)]</t>
+          <t>[np.float64(-32.45427238375622), np.float64(-74.29031336576773)]</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[np.float64(-5.8994973907381905), np.float64(0.0)]</t>
+          <t>[np.float64(-32.45427238375622), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3869,12 +3869,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>[np.float64(-2.970545773071237), np.float64(-40.586506092385854)]</t>
+          <t>[np.float64(-19.55779043907532), np.float64(-50.8434085308243)]</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[np.float64(-2.970545773071237), np.float64(0.0)]</t>
+          <t>[np.float64(-19.55779043907532), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[np.float64(-43.510232878408516), np.float64(-24.667774946741176)]</t>
+          <t>[np.float64(-12.282910815611402), np.float64(-39.03403343474976)]</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[np.float64(-43.510232878408516), np.float64(0.0)]</t>
+          <t>[np.float64(-12.282910815611402), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3951,12 +3951,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>[np.float64(7.417149242234075), np.float64(-55.63563079848892)]</t>
+          <t>[np.float64(-0.5447740153662011), np.float64(-15.41857518239334)]</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[np.float64(7.417149242234075), np.float64(0.0)]</t>
+          <t>[np.float64(-0.5447740153662011), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3992,12 +3992,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[np.float64(-23.64509470608394), np.float64(-93.9697919951832)]</t>
+          <t>[np.float64(-10.97013721895641), np.float64(-44.958352625101305)]</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[np.float64(-23.64509470608394), np.float64(0.0)]</t>
+          <t>[np.float64(-10.97013721895641), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -4033,12 +4033,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>[np.float64(-16.718410007328472), np.float64(-2.551838206408803)]</t>
+          <t>[np.float64(12.445740520242481), np.float64(-50.45735143476497)]</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[np.float64(-16.718410007328472), np.float64(0.0)]</t>
+          <t>[np.float64(12.445740520242481), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>[np.float64(7.959207395839769), np.float64(-27.674571652937388)]</t>
+          <t>[np.float64(-43.66136335741945), np.float64(-25.04019689412813)]</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[np.float64(7.959207395839769), np.float64(0.0)]</t>
+          <t>[np.float64(-43.66136335741945), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4115,12 +4115,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>[np.float64(-18.313875713860455), np.float64(-22.178871254441177)]</t>
+          <t>[np.float64(-33.263897636658285), np.float64(-18.983787474515523)]</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[np.float64(-18.313875713860455), np.float64(0.0)]</t>
+          <t>[np.float64(-33.263897636658285), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4134,7 @@
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>[np.float64(13.818138099039572), np.float64(-58.57554322058984)]</t>
+          <t>[np.float64(-15.196686666253925), np.float64(-33.473366529392834)]</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[np.float64(13.818138099039572), np.float64(0.0)]</t>
+          <t>[np.float64(-15.196686666253925), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4197,12 +4197,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>[np.float64(5.495024496368174), np.float64(-17.303733847332197)]</t>
+          <t>[np.float64(-28.400206192888973), np.float64(-59.51260678864363)]</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[np.float64(5.495024496368174), np.float64(0.0)]</t>
+          <t>[np.float64(-28.40020619288897), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4238,12 +4238,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>[np.float64(-1.6183946625854304), np.float64(-18.59954525356096)]</t>
+          <t>[np.float64(-6.751908445643139), np.float64(-42.106989861563335)]</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[np.float64(-1.6183946625854304), np.float64(0.0)]</t>
+          <t>[np.float64(-6.751908445643139), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4279,12 +4279,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>[np.float64(-60.68775675788273), np.float64(-78.4180547559189)]</t>
+          <t>[np.float64(-75.47512386922831), np.float64(-86.81725190472824)]</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[np.float64(-60.68775675788273), np.float64(0.0)]</t>
+          <t>[np.float64(-75.47512386922831), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4320,12 +4320,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>[np.float64(-34.38241593537039), np.float64(-96.00325189637604)]</t>
+          <t>[np.float64(-47.132823774987955), np.float64(-62.47033007119791)]</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[np.float64(-34.38241593537039), np.float64(0.0)]</t>
+          <t>[np.float64(-47.13282377498796), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4339,7 @@
         <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -4361,12 +4361,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>[np.float64(11.822998768760286), np.float64(-32.16822282591771)]</t>
+          <t>[np.float64(4.431991822457164), np.float64(-57.46726003357598)]</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[np.float64(11.822998768760286), np.float64(0.0)]</t>
+          <t>[np.float64(4.431991822457164), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4402,12 +4402,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>[np.float64(-25.42838128645448), np.float64(-4.02633557023195)]</t>
+          <t>[np.float64(-29.78001413281909), np.float64(-97.97058852933087)]</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[np.float64(-25.42838128645448), np.float64(0.0)]</t>
+          <t>[np.float64(-29.780014132819087), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4443,12 +4443,12 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>[np.float64(-6.185666834863454), np.float64(-48.22211890731764)]</t>
+          <t>[np.float64(-27.935615917336733), np.float64(-12.609979868357968)]</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[np.float64(-6.185666834863454), np.float64(0.0)]</t>
+          <t>[np.float64(-27.935615917336737), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>[np.float64(-16.38991133367024), np.float64(-2.3024773991112397)]</t>
+          <t>[np.float64(-33.29649486824533), np.float64(-8.97978054151855)]</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[np.float64(-16.38991133367024), np.float64(0.0)]</t>
+          <t>[np.float64(-33.29649486824533), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>[np.float64(12.159060945195534), np.float64(-24.127744916897797)]</t>
+          <t>[np.float64(-27.007785495867566), np.float64(-64.86144408969781)]</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[np.float64(12.159060945195534), np.float64(0.0)]</t>
+          <t>[np.float64(-27.007785495867562), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4566,12 +4566,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>[np.float64(-13.557895381138565), np.float64(-67.35776368234517)]</t>
+          <t>[np.float64(-19.84166792925508), np.float64(-44.97183474828581)]</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[np.float64(-13.557895381138565), np.float64(0.0)]</t>
+          <t>[np.float64(-19.84166792925508), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4607,381 +4607,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>[np.float64(-25.37378857882956), np.float64(-49.51406199812656)]</t>
+          <t>[np.float64(-14.396494176707506), np.float64(-48.66174312412181)]</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[np.float64(-25.37378857882956), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>1</v>
-      </c>
-      <c r="C103" t="n">
-        <v>1</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G103" t="n">
-        <v>1</v>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>[np.float64(-25.180862017295354), np.float64(-2.1456960837920036)]</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>[np.float64(-25.180862017295354), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>1</v>
-      </c>
-      <c r="C104" t="n">
-        <v>1</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G104" t="n">
-        <v>1</v>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>[np.float64(-24.29650967281701), np.float64(-29.27071030413009)]</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>[np.float64(-24.29650967281701), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>1</v>
-      </c>
-      <c r="C105" t="n">
-        <v>1</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G105" t="n">
-        <v>1</v>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>[np.float64(-21.903358918543802), np.float64(-45.1604810836842)]</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>[np.float64(-21.903358918543802), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>1</v>
-      </c>
-      <c r="C106" t="n">
-        <v>1</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
-        <v>1</v>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>[np.float64(-10.14954517714088), np.float64(-85.61477596322618)]</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>[np.float64(-10.14954517714088), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>1</v>
-      </c>
-      <c r="C107" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
-        <v>1</v>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>[np.float64(1.2059305966255494), np.float64(-30.412729942878713)]</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>[np.float64(1.2059305966255494), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>1</v>
-      </c>
-      <c r="C108" t="n">
-        <v>1</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
-        <v>1</v>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>[np.float64(-53.731681235406064), np.float64(-54.03366974341137)]</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>[np.float64(-53.73168123540606), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>1</v>
-      </c>
-      <c r="C109" t="n">
-        <v>1</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G109" t="n">
-        <v>1</v>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>[np.float64(-20.781481457449303), np.float64(-19.294267412175458)]</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>[np.float64(-20.781481457449303), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>1</v>
-      </c>
-      <c r="C110" t="n">
-        <v>1</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G110" t="n">
-        <v>1</v>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>[np.float64(-12.048209837611068), np.float64(-4.251485145968786)]</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>[np.float64(-12.048209837611068), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>1</v>
-      </c>
-      <c r="C111" t="n">
-        <v>1</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G111" t="n">
-        <v>1</v>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>[np.float64(-22.84857630802496), np.float64(-2.6582182562673324)]</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>[np.float64(-22.84857630802496), np.float64(0.0)]</t>
+          <t>[np.float64(-14.396494176707506), np.float64(0.0)]</t>
         </is>
       </c>
     </row>

--- a/Data/output/DIR Stroke Position.xlsx
+++ b/Data/output/DIR Stroke Position.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,16 +485,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -507,12 +507,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[np.float64(3.5013435951142924), np.float64(-64.05833919054744)]</t>
+          <t>[np.float64(557.126423455547), np.float64(50.45425072909568)]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[np.float64(3.5013435951142924), np.float64(0.0)]</t>
+          <t>[np.float64(557.126423455547), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -526,16 +526,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[np.float64(4.581735356988119), np.float64(-22.885568405179058)]</t>
+          <t>[np.float64(554.6302164332288), np.float64(24.59874357784955)]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[np.float64(4.581735356988119), np.float64(0.0)]</t>
+          <t>[np.float64(554.6302164332288), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -567,16 +567,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[np.float64(4.638391256028882), np.float64(-48.18827870449227)]</t>
+          <t>[np.float64(578.4385173845728), np.float64(87.21479152923663)]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[np.float64(4.638391256028882), np.float64(0.0)]</t>
+          <t>[np.float64(578.4385173845728), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -608,16 +608,16 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -630,12 +630,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[np.float64(-4.574354243009651), np.float64(-58.12003688277328)]</t>
+          <t>[np.float64(493.53324512804693), np.float64(60.629438748980995)]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[np.float64(-4.574354243009651), np.float64(0.0)]</t>
+          <t>[np.float64(493.53324512804693), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -649,16 +649,16 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[np.float64(-56.43513320748731), np.float64(-21.183400826473033)]</t>
+          <t>[np.float64(539.2500186721627), np.float64(37.978444262004665)]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[np.float64(-56.43513320748731), np.float64(0.0)]</t>
+          <t>[np.float64(539.2500186721627), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -690,16 +690,16 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -712,12 +712,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[np.float64(0.01911319427827607), np.float64(-70.9198988504937)]</t>
+          <t>[np.float64(554.5577712576638), np.float64(16.0811768642987)]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[np.float64(0.01911319427827607), np.float64(0.0)]</t>
+          <t>[np.float64(554.5577712576638), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -731,16 +731,16 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -753,12 +753,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[np.float64(-23.134064642597806), np.float64(-56.58447804838052)]</t>
+          <t>[np.float64(516.1757348559302), np.float64(74.98550982153655)]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[np.float64(-23.134064642597806), np.float64(0.0)]</t>
+          <t>[np.float64(516.1757348559302), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -772,16 +772,16 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -794,12 +794,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[np.float64(6.207016815083165), np.float64(-55.472452019343564)]</t>
+          <t>[np.float64(449.46164601054954), np.float64(88.58325801269805)]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[np.float64(6.207016815083165), np.float64(0.0)]</t>
+          <t>[np.float64(449.46164601054954), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -813,16 +813,16 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[np.float64(-36.60873390391324), np.float64(-57.80574786154982)]</t>
+          <t>[np.float64(552.556102674878), np.float64(70.56994150268467)]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[np.float64(-36.60873390391324), np.float64(0.0)]</t>
+          <t>[np.float64(552.556102674878), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -854,16 +854,16 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[np.float64(-23.576880888141176), np.float64(-62.880164716768824)]</t>
+          <t>[np.float64(416.84776537889746), np.float64(17.37689332021643)]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[np.float64(-23.576880888141176), np.float64(0.0)]</t>
+          <t>[np.float64(416.84776537889746), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -895,16 +895,16 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -917,12 +917,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[np.float64(-2.5704144094446377), np.float64(-62.917712381296354)]</t>
+          <t>[np.float64(410.41312343882737), np.float64(45.18659051583526)]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[np.float64(-2.5704144094446377), np.float64(0.0)]</t>
+          <t>[np.float64(410.41312343882737), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -936,16 +936,16 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[np.float64(14.015799149866268), np.float64(-65.99355312689951)]</t>
+          <t>[np.float64(461.47664063150773), np.float64(78.62310231091507)]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[np.float64(14.015799149866268), np.float64(0.0)]</t>
+          <t>[np.float64(461.47664063150773), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -977,16 +977,16 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[np.float64(-26.519525999658995), np.float64(-41.01179992973978)]</t>
+          <t>[np.float64(552.9168912023396), np.float64(36.62690955199312)]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[np.float64(-26.519525999658992), np.float64(0.0)]</t>
+          <t>[np.float64(552.9168912023396), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1018,16 +1018,16 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[np.float64(-37.238464054476346), np.float64(-54.504558937407865)]</t>
+          <t>[np.float64(523.279519947555), np.float64(9.753341508213017)]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[np.float64(-37.238464054476346), np.float64(0.0)]</t>
+          <t>[np.float64(523.279519947555), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1059,16 +1059,16 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[np.float64(3.034548673170619), np.float64(-8.327449813530379)]</t>
+          <t>[np.float64(575.3567295064993), np.float64(15.371863563421932)]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[np.float64(3.034548673170619), np.float64(0.0)]</t>
+          <t>[np.float64(575.3567295064993), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1100,16 +1100,16 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[np.float64(-46.812509361612314), np.float64(-69.1475386142808)]</t>
+          <t>[np.float64(452.6418006045327), np.float64(11.442862501001358)]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[np.float64(-46.812509361612314), np.float64(0.0)]</t>
+          <t>[np.float64(452.6418006045327), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1141,16 +1141,16 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[np.float64(8.464114627856716), np.float64(-7.096887051262428)]</t>
+          <t>[np.float64(520.040246573068), np.float64(33.528218872449365)]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[np.float64(8.464114627856716), np.float64(0.0)]</t>
+          <t>[np.float64(520.040246573068), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1182,16 +1182,16 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[np.float64(15.98159478410821), np.float64(-1.2850265718864335)]</t>
+          <t>[np.float64(585.4900790674501), np.float64(78.56479473665645)]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[np.float64(15.98159478410821), np.float64(0.0)]</t>
+          <t>[np.float64(585.4900790674501), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1223,16 +1223,16 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[np.float64(2.6650373245941665), np.float64(-18.768740071144222)]</t>
+          <t>[np.float64(440.32406451046734), np.float64(66.66865956958304)]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[np.float64(2.6650373245941665), np.float64(0.0)]</t>
+          <t>[np.float64(440.32406451046734), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1264,16 +1264,16 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[np.float64(-28.999630874917358), np.float64(-54.13582847227052)]</t>
+          <t>[np.float64(542.9798193487343), np.float64(63.935181892399505)]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[np.float64(-28.999630874917358), np.float64(0.0)]</t>
+          <t>[np.float64(542.9798193487343), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1305,16 +1305,16 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[np.float64(7.330292307534023), np.float64(-33.276714595334326)]</t>
+          <t>[np.float64(595.0459730602638), np.float64(104.24717765902665)]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[np.float64(7.330292307534023), np.float64(0.0)]</t>
+          <t>[np.float64(595.0459730602638), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1346,16 +1346,16 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[np.float64(-4.1862927437117605), np.float64(-11.526308988994515)]</t>
+          <t>[np.float64(440.2723005347759), np.float64(35.15300464415633)]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[np.float64(-4.1862927437117605), np.float64(0.0)]</t>
+          <t>[np.float64(440.2723005347759), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1387,16 +1387,16 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[np.float64(-70.83917944459634), np.float64(-54.650266672159)]</t>
+          <t>[np.float64(552.2730895407974), np.float64(105.80245185770754)]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[np.float64(-70.83917944459634), np.float64(0.0)]</t>
+          <t>[np.float64(552.2730895407974), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1428,16 +1428,16 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[np.float64(-20.058848010131385), np.float64(-66.72640675128989)]</t>
+          <t>[np.float64(454.3946714654224), np.float64(70.33516539466613)]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[np.float64(-20.058848010131385), np.float64(0.0)]</t>
+          <t>[np.float64(454.3946714654224), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1469,16 +1469,16 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[np.float64(-34.35462761819679), np.float64(-53.48117917614401)]</t>
+          <t>[np.float64(491.43032541027526), np.float64(57.43825915075075)]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[np.float64(-34.35462761819679), np.float64(0.0)]</t>
+          <t>[np.float64(491.43032541027526), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1510,16 +1510,16 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[np.float64(-8.982944910994078), np.float64(-76.01926112956491)]</t>
+          <t>[np.float64(584.9734156810706), np.float64(65.8072496200298)]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[np.float64(-8.982944910994078), np.float64(0.0)]</t>
+          <t>[np.float64(584.9734156810706), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1551,16 +1551,16 @@
         <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[np.float64(-1.3457053210349557), np.float64(-39.03413976127037)]</t>
+          <t>[np.float64(546.5874123765725), np.float64(30.719391938447576)]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[np.float64(-1.3457053210349557), np.float64(0.0)]</t>
+          <t>[np.float64(546.5874123765725), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1592,16 +1592,16 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[np.float64(-39.95002954052267), np.float64(-38.20572121120067)]</t>
+          <t>[np.float64(415.0435135641442), np.float64(93.89323365086155)]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[np.float64(-39.95002954052267), np.float64(0.0)]</t>
+          <t>[np.float64(415.0435135641442), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1633,16 +1633,16 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[np.float64(1.0695797860926604), np.float64(-58.80959838536335)]</t>
+          <t>[np.float64(552.5391694580023), np.float64(38.39305918445164)]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[np.float64(1.0695797860926604), np.float64(0.0)]</t>
+          <t>[np.float64(552.5391694580023), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1674,16 +1674,16 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[np.float64(-22.067462001598187), np.float64(-50.32511633208851)]</t>
+          <t>[np.float64(553.0701243318201), np.float64(104.5057405761375)]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[np.float64(-22.067462001598187), np.float64(0.0)]</t>
+          <t>[np.float64(553.0701243318201), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1715,16 +1715,16 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1737,12 +1737,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[np.float64(-9.319312508359786), np.float64(-85.51852024217554)]</t>
+          <t>[np.float64(506.49726068366596), np.float64(40.40005067644388)]</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[np.float64(-9.319312508359786), np.float64(0.0)]</t>
+          <t>[np.float64(506.49726068366596), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1756,16 +1756,16 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[np.float64(-40.64252594633182), np.float64(-36.67674319616909)]</t>
+          <t>[np.float64(445.4402815708713), np.float64(51.51183135457203)]</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[np.float64(-40.64252594633182), np.float64(0.0)]</t>
+          <t>[np.float64(445.4402815708713), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1797,16 +1797,16 @@
         <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[np.float64(6.476909735392951), np.float64(-65.79583893274673)]</t>
+          <t>[np.float64(520.8020220569288), np.float64(27.180784301121466)]</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[np.float64(6.476909735392951), np.float64(0.0)]</t>
+          <t>[np.float64(520.8020220569288), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1838,16 +1838,16 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[np.float64(-27.683353789958403), np.float64(-25.941195411384626)]</t>
+          <t>[np.float64(582.6235053443029), np.float64(49.35407566516467)]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[np.float64(-27.683353789958403), np.float64(0.0)]</t>
+          <t>[np.float64(582.6235053443029), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1879,16 +1879,16 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[np.float64(-43.3145925197234), np.float64(-65.82815626292471)]</t>
+          <t>[np.float64(540.1788134241726), np.float64(43.24897563024219)]</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[np.float64(-43.3145925197234), np.float64(0.0)]</t>
+          <t>[np.float64(540.1788134241726), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1920,16 +1920,16 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[np.float64(-6.83699769886293), np.float64(-84.14318377277105)]</t>
+          <t>[np.float64(599.5087890489737), np.float64(56.11289581593489)]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[np.float64(-6.83699769886293), np.float64(0.0)]</t>
+          <t>[np.float64(599.5087890489737), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -1961,16 +1961,16 @@
         <v>1</v>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[np.float64(-13.546385513916988), np.float64(-50.715166770215035)]</t>
+          <t>[np.float64(445.86921730962985), np.float64(13.083232455584602)]</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[np.float64(-13.546385513916988), np.float64(0.0)]</t>
+          <t>[np.float64(445.86921730962985), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2002,16 +2002,16 @@
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2024,12 +2024,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[np.float64(-38.23762133374575), np.float64(-57.08898808047611)]</t>
+          <t>[np.float64(441.8762697702133), np.float64(42.30487596692784)]</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[np.float64(-38.23762133374575), np.float64(0.0)]</t>
+          <t>[np.float64(441.8762697702133), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2043,16 +2043,16 @@
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[np.float64(-25.487917456226214), np.float64(-45.2597011609224)]</t>
+          <t>[np.float64(567.3066559236458), np.float64(23.265922398127163)]</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[np.float64(-25.487917456226214), np.float64(0.0)]</t>
+          <t>[np.float64(567.3066559236458), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2084,16 +2084,16 @@
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2106,12 +2106,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[np.float64(-12.689674433935508), np.float64(-24.761262826234628)]</t>
+          <t>[np.float64(526.5550989939172), np.float64(5.045488201346462)]</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[np.float64(-12.689674433935508), np.float64(0.0)]</t>
+          <t>[np.float64(526.5550989939172), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[np.float64(-21.230264419147602), np.float64(-65.26186800353724)]</t>
+          <t>[np.float64(449.8513526641823), np.float64(47.08424127084865)]</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[np.float64(-21.230264419147602), np.float64(0.0)]</t>
+          <t>[np.float64(449.8513526641823), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2166,16 +2166,16 @@
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[np.float64(-5.464560609484195), np.float64(-21.252450335921466)]</t>
+          <t>[np.float64(428.33909077852263), np.float64(63.34692051285493)]</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[np.float64(-5.464560609484195), np.float64(0.0)]</t>
+          <t>[np.float64(428.33909077852263), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2207,16 +2207,16 @@
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[np.float64(8.923261555762835), np.float64(-40.708407169330904)]</t>
+          <t>[np.float64(479.4031063404469), np.float64(23.472101904896217)]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[np.float64(8.923261555762835), np.float64(0.0)]</t>
+          <t>[np.float64(479.4031063404469), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2248,16 +2248,16 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2270,12 +2270,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[np.float64(-3.339491567225906), np.float64(-27.869924031772797)]</t>
+          <t>[np.float64(519.3815512068987), np.float64(58.63655247350966)]</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[np.float64(-3.339491567225906), np.float64(0.0)]</t>
+          <t>[np.float64(519.3815512068987), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2289,16 +2289,16 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[np.float64(-21.834987802726715), np.float64(-89.70161508256005)]</t>
+          <t>[np.float64(418.14239161210526), np.float64(13.994399219953271)]</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[np.float64(-21.834987802726715), np.float64(0.0)]</t>
+          <t>[np.float64(418.14239161210526), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2330,16 +2330,16 @@
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[np.float64(-53.99547420421869), np.float64(-0.2592743429183031)]</t>
+          <t>[np.float64(570.8142641480634), np.float64(81.20073352291155)]</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[np.float64(-53.99547420421869), np.float64(0.0)]</t>
+          <t>[np.float64(570.8142641480634), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2371,16 +2371,16 @@
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[np.float64(5.162176588773718), np.float64(-43.44334969970429)]</t>
+          <t>[np.float64(580.0064077943184), np.float64(71.34137284420872)]</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[np.float64(5.162176588773718), np.float64(0.0)]</t>
+          <t>[np.float64(580.0064077943184), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2412,16 +2412,16 @@
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[np.float64(-13.926933447882092), np.float64(-24.414075933683364)]</t>
+          <t>[np.float64(502.088430576178), np.float64(7.716975967735672)]</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[np.float64(-13.926933447882092), np.float64(0.0)]</t>
+          <t>[np.float64(502.088430576178), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2453,16 +2453,16 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[np.float64(-50.73539196918262), np.float64(-13.628272531685084)]</t>
+          <t>[np.float64(441.05413928703547), np.float64(11.856802972835352)]</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[np.float64(-50.73539196918262), np.float64(0.0)]</t>
+          <t>[np.float64(441.05413928703547), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2494,16 +2494,16 @@
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[np.float64(-8.699447987761317), np.float64(-41.771874976833345)]</t>
+          <t>[np.float64(508.36010845578807), np.float64(91.59653355945392)]</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[np.float64(-8.699447987761317), np.float64(0.0)]</t>
+          <t>[np.float64(508.36010845578807), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2535,16 +2535,16 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[np.float64(-9.922840272569857), np.float64(-64.68709262126968)]</t>
+          <t>[np.float64(479.35954295425654), np.float64(27.805305662683942)]</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[np.float64(-9.922840272569857), np.float64(0.0)]</t>
+          <t>[np.float64(479.35954295425654), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2576,16 +2576,16 @@
         <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[np.float64(-61.777948131427365), np.float64(-73.80967719022702)]</t>
+          <t>[np.float64(577.273071072465), np.float64(85.37045916227453)]</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[np.float64(-61.777948131427365), np.float64(0.0)]</t>
+          <t>[np.float64(577.273071072465), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2617,16 +2617,16 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[np.float64(-3.3847468190033396), np.float64(-5.0001364447646495)]</t>
+          <t>[np.float64(589.2009763593119), np.float64(37.59716348320875)]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[np.float64(-3.3847468190033396), np.float64(0.0)]</t>
+          <t>[np.float64(589.2009763593119), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2658,16 +2658,16 @@
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[np.float64(-15.222078559235172), np.float64(-21.351325431832223)]</t>
+          <t>[np.float64(584.5805909327544), np.float64(90.04027477914362)]</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[np.float64(-15.222078559235172), np.float64(0.0)]</t>
+          <t>[np.float64(584.5805909327544), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2699,16 +2699,16 @@
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2721,12 +2721,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[np.float64(9.268421471173923), np.float64(-16.587749901002894)]</t>
+          <t>[np.float64(440.46376025697293), np.float64(96.05305613809065)]</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[np.float64(9.268421471173923), np.float64(0.0)]</t>
+          <t>[np.float64(440.46376025697293), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2740,16 +2740,16 @@
         <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>[np.float64(-27.06905230318941), np.float64(-45.09460231887075)]</t>
+          <t>[np.float64(406.79948514782274), np.float64(2.6126767700766456)]</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[np.float64(-27.06905230318941), np.float64(0.0)]</t>
+          <t>[np.float64(406.79948514782274), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2781,16 +2781,16 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[np.float64(12.36904872177412), np.float64(-37.97464678871074)]</t>
+          <t>[np.float64(464.1262525494561), np.float64(54.45149260882476)]</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[np.float64(12.36904872177412), np.float64(0.0)]</t>
+          <t>[np.float64(464.1262525494561), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2822,16 +2822,16 @@
         <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>[np.float64(-8.441929903354861), np.float64(-11.130261839738424)]</t>
+          <t>[np.float64(530.8732539990864), np.float64(94.5418360643047)]</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[np.float64(-8.441929903354861), np.float64(0.0)]</t>
+          <t>[np.float64(530.8732539990864), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2863,16 +2863,16 @@
         <v>1</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[np.float64(-5.37186789697877), np.float64(-8.657313040085882)]</t>
+          <t>[np.float64(471.0446387316562), np.float64(53.61512543229938)]</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[np.float64(-5.37186789697877), np.float64(0.0)]</t>
+          <t>[np.float64(471.0446387316562), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2904,16 +2904,16 @@
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[np.float64(-17.589748227114555), np.float64(-35.51562746438471)]</t>
+          <t>[np.float64(447.7953990201016), np.float64(19.97012868252464)]</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[np.float64(-17.589748227114555), np.float64(0.0)]</t>
+          <t>[np.float64(447.7953990201016), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2945,16 +2945,16 @@
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[np.float64(2.901885562119304), np.float64(-6.985169542435273)]</t>
+          <t>[np.float64(420.7082039370328), np.float64(38.5031582197363)]</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[np.float64(2.901885562119304), np.float64(0.0)]</t>
+          <t>[np.float64(420.7082039370328), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -2986,16 +2986,16 @@
         <v>1</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[np.float64(9.730865719902695), np.float64(-11.883261496000415)]</t>
+          <t>[np.float64(547.0626291376701), np.float64(48.19704715118341)]</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[np.float64(9.730865719902695), np.float64(0.0)]</t>
+          <t>[np.float64(547.0626291376701), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3027,16 @@
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[np.float64(-20.21925977159941), np.float64(-33.537322353400455)]</t>
+          <t>[np.float64(563.755989134125), np.float64(42.631209961698836)]</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[np.float64(-20.21925977159941), np.float64(0.0)]</t>
+          <t>[np.float64(563.755989134125), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3068,16 +3068,16 @@
         <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[np.float64(-0.45614261141352586), np.float64(-65.6410809315037)]</t>
+          <t>[np.float64(481.5026864314838), np.float64(89.35885211974404)]</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[np.float64(-0.45614261141352586), np.float64(0.0)]</t>
+          <t>[np.float64(481.5026864314838), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3109,16 +3109,16 @@
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[np.float64(1.1728995190107128), np.float64(-17.420120723498826)]</t>
+          <t>[np.float64(544.9279479260395), np.float64(59.41741540344282)]</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[np.float64(1.1728995190107128), np.float64(0.0)]</t>
+          <t>[np.float64(544.9279479260395), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3150,16 +3150,16 @@
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[np.float64(-0.28806927135684646), np.float64(-51.01873180108682)]</t>
+          <t>[np.float64(424.38727716536124), np.float64(98.49486374372117)]</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[np.float64(-0.28806927135684646), np.float64(0.0)]</t>
+          <t>[np.float64(424.38727716536124), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3191,16 +3191,16 @@
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3213,12 +3213,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[np.float64(-3.5053571003440283), np.float64(-19.146781255651348)]</t>
+          <t>[np.float64(421.1302242576676), np.float64(74.22032279000105)]</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[np.float64(-3.5053571003440283), np.float64(0.0)]</t>
+          <t>[np.float64(421.1302242576676), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3232,16 +3232,16 @@
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>[np.float64(11.815637438031942), np.float64(-41.71468172010238)]</t>
+          <t>[np.float64(528.6193465368784), np.float64(61.15276996502763)]</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[np.float64(11.815637438031942), np.float64(0.0)]</t>
+          <t>[np.float64(528.6193465368784), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3273,16 +3273,16 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[np.float64(-20.175874017974436), np.float64(-13.187764724743033)]</t>
+          <t>[np.float64(553.4838916835799), np.float64(48.11389492903618)]</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[np.float64(-20.175874017974436), np.float64(0.0)]</t>
+          <t>[np.float64(553.4838916835799), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3314,16 +3314,16 @@
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[np.float64(15.16235970194839), np.float64(-57.97609207784819)]</t>
+          <t>[np.float64(520.0328105049089), np.float64(3.474537774822995)]</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[np.float64(15.16235970194839), np.float64(0.0)]</t>
+          <t>[np.float64(520.0328105049089), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3355,16 +3355,16 @@
         <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3377,12 +3377,12 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[np.float64(-16.09325349180493), np.float64(-52.45946414795741)]</t>
+          <t>[np.float64(448.80106406436846), np.float64(29.589702574668294)]</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[np.float64(-16.09325349180493), np.float64(0.0)]</t>
+          <t>[np.float64(448.80106406436846), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3396,16 +3396,16 @@
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[np.float64(-14.738600543072806), np.float64(-19.102111305887263)]</t>
+          <t>[np.float64(541.4460221412787), np.float64(58.79219956417392)]</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[np.float64(-14.738600543072806), np.float64(0.0)]</t>
+          <t>[np.float64(541.4460221412787), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3437,16 +3437,16 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>[np.float64(-7.2821376724266145), np.float64(-32.146665851469976)]</t>
+          <t>[np.float64(449.5934965050732), np.float64(47.07982505832962)]</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[np.float64(-7.2821376724266145), np.float64(0.0)]</t>
+          <t>[np.float64(449.5934965050732), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3478,16 +3478,16 @@
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[np.float64(-23.12829761757213), np.float64(-28.870319000792847)]</t>
+          <t>[np.float64(485.4745181496246), np.float64(72.23512454455378)]</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[np.float64(-23.12829761757213), np.float64(0.0)]</t>
+          <t>[np.float64(485.4745181496246), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3519,16 +3519,16 @@
         <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[np.float64(-0.2238922773581038), np.float64(-53.59732879807926)]</t>
+          <t>[np.float64(591.530448281459), np.float64(17.662154416260023)]</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[np.float64(-0.2238922773581038), np.float64(0.0)]</t>
+          <t>[np.float64(591.530448281459), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3560,16 +3560,16 @@
         <v>1</v>
       </c>
       <c r="C77" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>[np.float64(-54.93614397777375), np.float64(-67.67404550329219)]</t>
+          <t>[np.float64(487.7011032596199), np.float64(37.13715238980269)]</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[np.float64(-54.93614397777375), np.float64(0.0)]</t>
+          <t>[np.float64(487.7011032596199), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3601,16 +3601,16 @@
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[np.float64(-22.880161184726163), np.float64(-8.304120079336414)]</t>
+          <t>[np.float64(423.82798782171074), np.float64(89.97360643332178)]</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[np.float64(-22.880161184726163), np.float64(0.0)]</t>
+          <t>[np.float64(423.82798782171074), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3642,16 +3642,16 @@
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>[np.float64(-33.46374077644728), np.float64(-39.872702642223686)]</t>
+          <t>[np.float64(592.660347666696), np.float64(24.863905836483365)]</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[np.float64(-33.46374077644728), np.float64(0.0)]</t>
+          <t>[np.float64(592.660347666696), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3683,16 +3683,16 @@
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>[np.float64(-64.42620415898918), np.float64(-4.677410482550684)]</t>
+          <t>[np.float64(513.859008226024), np.float64(81.63735733460908)]</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[np.float64(-64.42620415898918), np.float64(0.0)]</t>
+          <t>[np.float64(513.859008226024), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3724,16 +3724,16 @@
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>[np.float64(-1.158603157029546), np.float64(-44.09548559929968)]</t>
+          <t>[np.float64(554.1006907537754), np.float64(35.69107100114401)]</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[np.float64(-1.158603157029546), np.float64(0.0)]</t>
+          <t>[np.float64(554.1006907537754), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3765,16 +3765,16 @@
         <v>1</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[np.float64(-24.0512172446104), np.float64(-37.858178399278856)]</t>
+          <t>[np.float64(579.3356684731863), np.float64(74.68398414975098)]</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[np.float64(-24.0512172446104), np.float64(0.0)]</t>
+          <t>[np.float64(579.3356684731863), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3806,16 +3806,16 @@
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[np.float64(-32.45427238375622), np.float64(-74.29031336576773)]</t>
+          <t>[np.float64(576.2124951443517), np.float64(25.321448746456344)]</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[np.float64(-32.45427238375622), np.float64(0.0)]</t>
+          <t>[np.float64(576.2124951443517), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3847,16 +3847,16 @@
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>[np.float64(-19.55779043907532), np.float64(-50.8434085308243)]</t>
+          <t>[np.float64(473.3609964872956), np.float64(5.488198574522754)]</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[np.float64(-19.55779043907532), np.float64(0.0)]</t>
+          <t>[np.float64(473.3609964872956), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3888,16 +3888,16 @@
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[np.float64(-12.282910815611402), np.float64(-39.03403343474976)]</t>
+          <t>[np.float64(509.8503543452645), np.float64(138.19210427686184)]</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[np.float64(-12.282910815611402), np.float64(0.0)]</t>
+          <t>[np.float64(509.8503543452645), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3929,16 +3929,16 @@
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>[np.float64(-0.5447740153662011), np.float64(-15.41857518239334)]</t>
+          <t>[np.float64(578.0592236289441), np.float64(144.02908675601876)]</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[np.float64(-0.5447740153662011), np.float64(0.0)]</t>
+          <t>[np.float64(578.0592236289441), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -3970,16 +3970,16 @@
         <v>1</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[np.float64(-10.97013721895641), np.float64(-44.958352625101305)]</t>
+          <t>[np.float64(425.0573297095231), np.float64(137.43011113021308)]</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[np.float64(-10.97013721895641), np.float64(0.0)]</t>
+          <t>[np.float64(425.0573297095231), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4011,16 +4011,16 @@
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>[np.float64(12.445740520242481), np.float64(-50.45735143476497)]</t>
+          <t>[np.float64(440.80915815025907), np.float64(119.10938218395484)]</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[np.float64(12.445740520242481), np.float64(0.0)]</t>
+          <t>[np.float64(440.80915815025907), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4052,16 +4052,16 @@
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>[np.float64(-43.66136335741945), np.float64(-25.04019689412813)]</t>
+          <t>[np.float64(547.6354151888004), np.float64(114.99587441027312)]</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[np.float64(-43.66136335741945), np.float64(0.0)]</t>
+          <t>[np.float64(547.6354151888004), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4093,16 +4093,16 @@
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>[np.float64(-33.263897636658285), np.float64(-18.983787474515523)]</t>
+          <t>[np.float64(488.0845405626251), np.float64(129.27903502482448)]</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[np.float64(-33.263897636658285), np.float64(0.0)]</t>
+          <t>[np.float64(488.0845405626251), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4134,16 +4134,16 @@
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>[np.float64(-15.196686666253925), np.float64(-33.473366529392834)]</t>
+          <t>[np.float64(544.9034975364523), np.float64(121.12901012014437)]</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[np.float64(-15.196686666253925), np.float64(0.0)]</t>
+          <t>[np.float64(544.9034975364523), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4175,16 +4175,16 @@
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>[np.float64(-28.400206192888973), np.float64(-59.51260678864363)]</t>
+          <t>[np.float64(593.8336827882274), np.float64(111.82610292737672)]</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[np.float64(-28.40020619288897), np.float64(0.0)]</t>
+          <t>[np.float64(593.8336827882274), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4216,16 +4216,16 @@
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>[np.float64(-6.751908445643139), np.float64(-42.106989861563335)]</t>
+          <t>[np.float64(533.8286029223639), np.float64(129.39259665728304)]</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[np.float64(-6.751908445643139), np.float64(0.0)]</t>
+          <t>[np.float64(533.8286029223639), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4257,16 +4257,16 @@
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>[np.float64(-75.47512386922831), np.float64(-86.81725190472824)]</t>
+          <t>[np.float64(559.8109614091907), np.float64(152.35984153629863)]</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[np.float64(-75.47512386922831), np.float64(0.0)]</t>
+          <t>[np.float64(559.8109614091907), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4298,16 +4298,16 @@
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>[np.float64(-47.132823774987955), np.float64(-62.47033007119791)]</t>
+          <t>[np.float64(588.5222194227712), np.float64(114.83140014605928)]</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[np.float64(-47.13282377498796), np.float64(0.0)]</t>
+          <t>[np.float64(588.5222194227712), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4339,16 +4339,16 @@
         <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4361,12 +4361,12 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>[np.float64(4.431991822457164), np.float64(-57.46726003357598)]</t>
+          <t>[np.float64(510.54125344707586), np.float64(110.7866246664128)]</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[np.float64(4.431991822457164), np.float64(0.0)]</t>
+          <t>[np.float64(510.54125344707586), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -4380,16 +4380,16 @@
         <v>1</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1001.0</t>
+          <t>3001.0</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4402,217 +4402,12 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>[np.float64(-29.78001413281909), np.float64(-97.97058852933087)]</t>
+          <t>[np.float64(438.9499874803707), np.float64(188.17044189654047)]</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[np.float64(-29.780014132819087), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
-        <v>1</v>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>[np.float64(-27.935615917336733), np.float64(-12.609979868357968)]</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>[np.float64(-27.935615917336737), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>1</v>
-      </c>
-      <c r="C99" t="n">
-        <v>1</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
-        <v>1</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>[np.float64(-33.29649486824533), np.float64(-8.97978054151855)]</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>[np.float64(-33.29649486824533), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>1</v>
-      </c>
-      <c r="C100" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G100" t="n">
-        <v>1</v>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>[np.float64(-27.007785495867566), np.float64(-64.86144408969781)]</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>[np.float64(-27.007785495867562), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>1</v>
-      </c>
-      <c r="C101" t="n">
-        <v>1</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
-        <v>1</v>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>[np.float64(-19.84166792925508), np.float64(-44.97183474828581)]</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>[np.float64(-19.84166792925508), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>1</v>
-      </c>
-      <c r="C102" t="n">
-        <v>1</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G102" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>[np.float64(-14.396494176707506), np.float64(-48.66174312412181)]</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>[np.float64(-14.396494176707506), np.float64(0.0)]</t>
+          <t>[np.float64(438.9499874803707), np.float64(0.0)]</t>
         </is>
       </c>
     </row>

--- a/Data/output/DIR Stroke Position.xlsx
+++ b/Data/output/DIR Stroke Position.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,7 +485,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -507,12 +507,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[np.float64(581.9623415292153), np.float64(74.28053264224589)]</t>
+          <t>[np.float64(526.7740881929956), np.float64(58.53427933597605)]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[np.float64(581.9623415292153), np.float64(0.0)]</t>
+          <t>[np.float64(526.7740881929956), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -548,12 +548,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[np.float64(427.5389194409033), np.float64(13.139467651369284)]</t>
+          <t>[np.float64(439.90629560083175), np.float64(27.505218577204193)]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[np.float64(427.5389194409033), np.float64(0.0)]</t>
+          <t>[np.float64(439.90629560083175), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[np.float64(481.580315860976), np.float64(73.10364554244254)]</t>
+          <t>[np.float64(454.98544805520856), np.float64(49.51944832352716)]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[np.float64(481.580315860976), np.float64(0.0)]</t>
+          <t>[np.float64(454.98544805520856), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[np.float64(470.98600656335327), np.float64(54.728033889556286)]</t>
+          <t>[np.float64(463.68143214662285), np.float64(53.65444629619699)]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[np.float64(470.98600656335327), np.float64(0.0)]</t>
+          <t>[np.float64(463.68143214662285), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -671,12 +671,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[np.float64(425.39385839859904), np.float64(30.339924229481515)]</t>
+          <t>[np.float64(452.3907703771814), np.float64(99.02010682545833)]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[np.float64(425.39385839859904), np.float64(0.0)]</t>
+          <t>[np.float64(452.3907703771814), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -712,12 +712,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[np.float64(562.2987462533855), np.float64(37.280635358544316)]</t>
+          <t>[np.float64(478.1371890048886), np.float64(73.74047013181865)]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[np.float64(562.2987462533855), np.float64(0.0)]</t>
+          <t>[np.float64(478.1371890048886), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -753,12 +753,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[np.float64(565.9304438944039), np.float64(97.09298880620555)]</t>
+          <t>[np.float64(512.2209502906907), np.float64(70.31947733975066)]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[np.float64(565.9304438944039), np.float64(0.0)]</t>
+          <t>[np.float64(512.2209502906907), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -794,12 +794,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[np.float64(410.57408897117205), np.float64(48.59849644102287)]</t>
+          <t>[np.float64(456.9673920496537), np.float64(83.00406957741662)]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[np.float64(410.57408897117205), np.float64(0.0)]</t>
+          <t>[np.float64(456.9673920496537), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -835,12 +835,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[np.float64(495.65436736777207), np.float64(33.94009211215396)]</t>
+          <t>[np.float64(429.49123683290713), np.float64(86.05889496357275)]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[np.float64(495.65436736777207), np.float64(0.0)]</t>
+          <t>[np.float64(429.49123683290713), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -876,12 +876,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[np.float64(543.6539450097129), np.float64(66.00370801171425)]</t>
+          <t>[np.float64(487.3335723736542), np.float64(89.94482366542364)]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[np.float64(543.6539450097129), np.float64(0.0)]</t>
+          <t>[np.float64(487.3335723736542), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -917,12 +917,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[np.float64(491.85231834415606), np.float64(163.4768486914395)]</t>
+          <t>[np.float64(404.959130789992), np.float64(35.25190717655197)]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[np.float64(491.85231834415606), np.float64(0.0)]</t>
+          <t>[np.float64(404.959130789992), np.float64(0.0)]</t>
         </is>
       </c>
     </row>
@@ -936,34 +936,6143 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[np.float64(595.1537878744684), np.float64(2.8683647002868407)]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>[np.float64(595.1537878744684), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[np.float64(557.9777498162782), np.float64(29.857354639899885)]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>[np.float64(557.9777498162782), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[np.float64(575.3117606482449), np.float64(56.31691300272267)]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>[np.float64(575.3117606482449), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="n">
         <v>9</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3001.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>[np.float64(449.40023061256255), np.float64(119.86455887290299)]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>[np.float64(449.40023061256255), np.float64(0.0)]</t>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[np.float64(461.04376165556346), np.float64(54.174942490912926)]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>[np.float64(461.04376165556346), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>11</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[np.float64(550.9907125481448), np.float64(1.7987112498091777)]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>[np.float64(550.9907125481448), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[np.float64(570.2486239995491), np.float64(59.02167628637324)]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>[np.float64(570.2486239995491), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[np.float64(572.8985276980342), np.float64(10.827912642036196)]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[np.float64(572.8985276980342), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[np.float64(560.5463953701201), np.float64(4.715109378715118)]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>[np.float64(560.5463953701201), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[np.float64(541.6833378237011), np.float64(18.90700888348419)]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>[np.float64(541.6833378237011), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[np.float64(414.5162077720399), np.float64(37.98047096171483)]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>[np.float64(414.5162077720399), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[np.float64(509.01983229458517), np.float64(68.75188516804829)]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>[np.float64(509.01983229458517), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="n">
+        <v>9</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[np.float64(450.41101805697804), np.float64(9.577585851783024)]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>[np.float64(450.41101805697804), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[np.float64(541.9231601765807), np.float64(24.836442067099444)]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>[np.float64(541.9231601765807), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>9</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[np.float64(432.0183238523615), np.float64(9.393659387729997)]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[np.float64(432.0183238523615), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>9</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[np.float64(445.56935440287987), np.float64(49.54039278142844)]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>[np.float64(445.56935440287987), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[np.float64(543.342964680134), np.float64(7.3372115705559215)]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>[np.float64(543.342964680134), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="n">
+        <v>10</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[np.float64(499.0015445634382), np.float64(20.452623936805033)]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[np.float64(499.0015445634382), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>10</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[np.float64(534.3942360850177), np.float64(56.2545892385609)]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>[np.float64(534.3942360850177), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>11</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[np.float64(584.8423738118661), np.float64(13.936023699382782)]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>[np.float64(584.8423738118661), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[np.float64(413.26544636261303), np.float64(16.630699822099743)]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>[np.float64(413.26544636261303), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="n">
+        <v>10</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[np.float64(513.8222276553904), np.float64(0.8388261900800775)]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>[np.float64(513.8222276553904), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[np.float64(429.38604679123455), np.float64(101.40109101746535)]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>[np.float64(429.38604679123455), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[np.float64(526.3844745994888), np.float64(7.312742554033933)]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>[np.float64(526.3844745994888), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[np.float64(426.04546024031316), np.float64(55.74690588725943)]</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>[np.float64(426.04546024031316), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="n">
+        <v>9</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>[np.float64(445.3998005051479), np.float64(57.12153275086734)]</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>[np.float64(445.3998005051479), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="n">
+        <v>10</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[np.float64(518.8722052231285), np.float64(16.126124792918933)]</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>[np.float64(518.8722052231285), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>9</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>[np.float64(486.1966375803487), np.float64(72.37413231295707)]</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>[np.float64(486.1966375803487), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>[np.float64(406.96571443686685), np.float64(31.0135871873785)]</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>[np.float64(406.96571443686685), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>[np.float64(428.5197312811317), np.float64(86.76741600338802)]</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>[np.float64(428.5197312811317), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>10</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[np.float64(517.296853372661), np.float64(58.01841292375631)]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>[np.float64(517.296853372661), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>11</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>[np.float64(574.462192949732), np.float64(45.79434055808677)]</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>[np.float64(574.462192949732), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>9</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[np.float64(436.37528643709055), np.float64(60.75516291354565)]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>[np.float64(436.37528643709055), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>10</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[np.float64(508.8150292016314), np.float64(54.303186726633754)]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>[np.float64(508.8150292016314), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>9</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>[np.float64(462.6093875106827), np.float64(57.50802426620702)]</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>[np.float64(462.6093875106827), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>10</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[np.float64(503.4848844812837), np.float64(97.15531041543855)]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>[np.float64(503.4848844812837), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>11</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>[np.float64(559.4238993340273), np.float64(32.33198821811892)]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>[np.float64(559.4238993340273), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>10</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[np.float64(544.3825969583903), np.float64(68.6774516629173)]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>[np.float64(544.3825969583903), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>9</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[np.float64(438.66751835742525), np.float64(65.1645853352646)]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>[np.float64(438.66751835742525), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>9</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>[np.float64(447.88590970100233), np.float64(15.963658753313005)]</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>[np.float64(447.88590970100233), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>10</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>[np.float64(501.46945289052786), np.float64(56.63297978340923)]</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>[np.float64(501.46945289052786), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>[np.float64(401.00294672963815), np.float64(4.3273552182406725)]</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>[np.float64(401.00294672963815), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>[np.float64(407.76181450319433), np.float64(51.309325810899445)]</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>[np.float64(407.76181450319433), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>[np.float64(412.9555075904286), np.float64(57.60434438724461)]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>[np.float64(412.9555075904286), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[np.float64(409.97743862551164), np.float64(46.171824955947365)]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>[np.float64(409.97743862551164), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="n">
+        <v>9</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>[np.float64(487.8552123478938), np.float64(28.77740610520725)]</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>[np.float64(487.8552123478938), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>10</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>[np.float64(501.611165984752), np.float64(55.417580065974036)]</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>[np.float64(501.611165984752), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="n">
+        <v>11</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>[np.float64(553.3695922189868), np.float64(15.381894858354048)]</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>[np.float64(553.3695922189868), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="n">
+        <v>10</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>[np.float64(492.89731211436936), np.float64(68.38794729596869)]</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>[np.float64(492.89731211436936), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="n">
+        <v>10</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>[np.float64(513.7716737547689), np.float64(56.26080944398081)]</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>[np.float64(513.7716737547689), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>9</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>[np.float64(433.15127196559956), np.float64(50.99354972791799)]</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>[np.float64(433.15127196559956), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>[np.float64(411.0582977234837), np.float64(18.10318699116844)]</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>[np.float64(411.0582977234837), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="n">
+        <v>9</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>[np.float64(461.0114462566846), np.float64(39.82821041683502)]</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>[np.float64(461.0114462566846), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>[np.float64(407.7905028044101), np.float64(46.80908275612995)]</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>[np.float64(407.7905028044101), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="n">
+        <v>11</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>[np.float64(589.0339406807354), np.float64(58.54810649866828)]</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>[np.float64(589.0339406807354), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>10</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>[np.float64(500.8678138816444), np.float64(99.6909079405786)]</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>[np.float64(500.8678138816444), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="n">
+        <v>11</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>[np.float64(555.754156719715), np.float64(31.119035336490843)]</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>[np.float64(555.754156719715), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="n">
+        <v>11</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>[np.float64(550.0001427099119), np.float64(90.52109392991086)]</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>[np.float64(550.0001427099119), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="n">
+        <v>9</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>[np.float64(443.4237184862788), np.float64(2.1105734837690213)]</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>[np.float64(443.4237184862788), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>10</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>[np.float64(549.9926600694897), np.float64(84.89642629677256)]</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>[np.float64(549.9926600694897), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="n">
+        <v>11</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>[np.float64(592.1101704948067), np.float64(38.54445478063828)]</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>[np.float64(592.1101704948067), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="n">
+        <v>10</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>[np.float64(501.0307837239401), np.float64(11.217671741019274)]</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>[np.float64(501.0307837239401), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="n">
+        <v>9</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>[np.float64(468.93446883461945), np.float64(39.04809475705295)]</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>[np.float64(468.93446883461945), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="n">
+        <v>8</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>[np.float64(426.4864596829842), np.float64(18.15860445315932)]</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>[np.float64(426.4864596829842), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="n">
+        <v>8</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>[np.float64(406.3118571513786), np.float64(42.54616629566501)]</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>[np.float64(406.3118571513786), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="n">
+        <v>9</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>[np.float64(480.46022351460704), np.float64(77.33816683805829)]</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>[np.float64(480.46022351460704), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="n">
+        <v>10</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>[np.float64(527.7293493540928), np.float64(82.88032239024827)]</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>[np.float64(527.7293493540928), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="n">
+        <v>10</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>[np.float64(511.91521557893265), np.float64(67.8041008709057)]</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>[np.float64(511.91521557893265), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="n">
+        <v>11</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>[np.float64(592.9887917281225), np.float64(22.75521226523734)]</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>[np.float64(592.9887917281225), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>10</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>[np.float64(523.7958729765838), np.float64(77.65508816315838)]</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>[np.float64(523.7958729765838), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="n">
+        <v>8</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>[np.float64(404.6589502244303), np.float64(16.613068014896417)]</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>[np.float64(404.6589502244303), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>8</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>[np.float64(417.03455869325086), np.float64(55.34321626710359)]</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>[np.float64(417.03455869325086), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="n">
+        <v>11</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>[np.float64(559.926216063155), np.float64(77.344150524584)]</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>[np.float64(559.926216063155), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="n">
+        <v>9</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>[np.float64(483.58846058337565), np.float64(22.801739440098455)]</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>[np.float64(483.58846058337565), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="n">
+        <v>8</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>[np.float64(407.5439736657833), np.float64(56.18520606340218)]</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>[np.float64(407.5439736657833), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="n">
+        <v>9</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>[np.float64(451.64332551851135), np.float64(33.149674738820465)]</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>[np.float64(451.64332551851135), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="n">
+        <v>10</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>[np.float64(548.1763784671485), np.float64(32.85398592992081)]</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>[np.float64(548.1763784671485), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="n">
+        <v>9</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>[np.float64(485.3272768249979), np.float64(49.09549221649401)]</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>[np.float64(485.3272768249979), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="n">
+        <v>9</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>[np.float64(459.03445426258116), np.float64(0.8470641100231459)]</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>[np.float64(459.03445426258116), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>[np.float64(409.7742048814724), np.float64(55.90200522433172)]</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>[np.float64(409.7742048814724), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="n">
+        <v>11</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>[np.float64(591.7417694988827), np.float64(59.79976226790013)]</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>[np.float64(591.7417694988827), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>11</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>[np.float64(582.1986556226082), np.float64(41.24002536276303)]</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>[np.float64(582.1986556226082), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="n">
+        <v>9</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>[np.float64(489.1012322150907), np.float64(0.7684228382065981)]</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>[np.float64(489.1012322150907), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="n">
+        <v>8</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>[np.float64(400.7895763765045), np.float64(36.45597774273784)]</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>[np.float64(400.7895763765045), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>10</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>[np.float64(490.38938419813485), np.float64(39.12166490924121)]</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>[np.float64(490.38938419813485), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>10</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>[np.float64(493.08965538496614), np.float64(10.398765324863533)]</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>[np.float64(493.08965538496614), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="n">
+        <v>10</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>1</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>[np.float64(535.3504302304393), np.float64(10.374111618163047)]</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>[np.float64(535.3504302304393), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="n">
+        <v>11</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>1</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>[np.float64(566.4694862149772), np.float64(71.29955059799816)]</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>[np.float64(566.4694862149772), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="n">
+        <v>8</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>[np.float64(425.2327719849826), np.float64(81.28906781559148)]</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>[np.float64(425.2327719849826), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="n">
+        <v>9</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>1</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>[np.float64(485.77415343760583), np.float64(59.635550556753394)]</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>[np.float64(485.77415343760583), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="n">
+        <v>10</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>[np.float64(507.9967778060196), np.float64(17.351100893698206)]</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>[np.float64(507.9967778060196), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="n">
+        <v>11</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>1</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>[np.float64(598.5244356635269), np.float64(15.97406396017736)]</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>[np.float64(598.5244356635269), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="n">
+        <v>9</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>[np.float64(487.466528895978), np.float64(86.41693304157353)]</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>[np.float64(487.466528895978), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="n">
+        <v>11</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>1</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>[np.float64(583.183805455699), np.float64(56.43289161091123)]</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>[np.float64(583.183805455699), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="n">
+        <v>11</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>[np.float64(580.2743203069892), np.float64(54.55812047224714)]</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>[np.float64(580.2743203069892), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="n">
+        <v>11</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>[np.float64(550.4770119231957), np.float64(21.416701955402814)]</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>[np.float64(550.4770119231957), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="n">
+        <v>10</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>[np.float64(541.1808980186554), np.float64(18.195172362943627)]</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>[np.float64(541.1808980186554), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="n">
+        <v>10</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>[np.float64(491.42639908527997), np.float64(16.78024494479017)]</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>[np.float64(491.42639908527997), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="n">
+        <v>9</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>[np.float64(481.15701322334087), np.float64(36.29278573977688)]</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>[np.float64(481.15701322334087), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="n">
+        <v>11</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>[np.float64(561.6290644878454), np.float64(10.080073728553268)]</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>[np.float64(561.6290644878454), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="n">
+        <v>9</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>1</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>[np.float64(431.16223394839915), np.float64(19.838720192713502)]</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>[np.float64(431.16223394839915), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="n">
+        <v>10</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>[np.float64(505.70754612945893), np.float64(63.97381618639785)]</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>[np.float64(505.70754612945893), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="n">
+        <v>8</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>[np.float64(410.3410297203055), np.float64(70.77866687000765)]</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>[np.float64(410.3410297203055), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="n">
+        <v>10</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>1</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>[np.float64(516.590210142737), np.float64(65.74855826967982)]</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>[np.float64(516.590210142737), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="n">
+        <v>11</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>1</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>[np.float64(562.0200412405911), np.float64(17.884108662955768)]</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>[np.float64(562.0200412405911), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="n">
+        <v>10</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>[np.float64(494.0995043057062), np.float64(57.91901020501929)]</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>[np.float64(494.0995043057062), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="n">
+        <v>11</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>[np.float64(556.6743092528673), np.float64(43.97482612535307)]</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>[np.float64(556.6743092528673), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="n">
+        <v>11</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>[np.float64(588.2830081267505), np.float64(35.41011535212109)]</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>[np.float64(588.2830081267505), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="n">
+        <v>10</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>[np.float64(491.8086470676619), np.float64(103.26200251721387)]</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>[np.float64(491.8086470676619), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="n">
+        <v>9</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>[np.float64(458.71094522050225), np.float64(37.142952289392284)]</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>[np.float64(458.71094522050225), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="n">
+        <v>9</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>[np.float64(469.5373068707415), np.float64(3.968779776757747)]</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>[np.float64(469.5373068707415), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="n">
+        <v>11</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>[np.float64(564.0134887086236), np.float64(10.59172073450842)]</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>[np.float64(564.0134887086236), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="n">
+        <v>10</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>[np.float64(511.5311241216415), np.float64(50.01194947202355)]</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>[np.float64(511.5311241216415), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" t="n">
+        <v>9</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>[np.float64(440.3572615898394), np.float64(50.152743629909864)]</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>[np.float64(440.3572615898394), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" t="n">
+        <v>8</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>[np.float64(414.14726746255553), np.float64(49.841268208576594)]</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>[np.float64(414.14726746255553), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" t="n">
+        <v>10</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>[np.float64(538.4876569655032), np.float64(58.07729393897049)]</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>[np.float64(538.4876569655032), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="n">
+        <v>11</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>[np.float64(599.9035067884347), np.float64(13.37364351816926)]</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>[np.float64(599.9035067884347), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" t="n">
+        <v>9</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>1</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>[np.float64(476.4535542471352), np.float64(31.584321113514935)]</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>[np.float64(476.4535542471352), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" t="n">
+        <v>10</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>1</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>[np.float64(519.8128506361495), np.float64(50.689131169696985)]</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>[np.float64(519.8128506361495), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" t="n">
+        <v>8</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>[np.float64(413.4851898720405), np.float64(40.308508642147814)]</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>[np.float64(413.4851898720405), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" t="n">
+        <v>9</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>[np.float64(463.3415264124469), np.float64(37.141141334506244)]</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>[np.float64(463.3415264124469), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" t="n">
+        <v>11</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>1</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>[np.float64(571.4012550452269), np.float64(34.39626844955131)]</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>[np.float64(571.4012550452269), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" t="n">
+        <v>11</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>[np.float64(591.214146257906), np.float64(8.528554487153672)]</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>[np.float64(591.214146257906), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" t="n">
+        <v>9</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>1</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>[np.float64(471.22442966855914), np.float64(92.72184320539517)]</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>[np.float64(471.22442966855914), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" t="n">
+        <v>10</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>[np.float64(522.7894871192374), np.float64(61.07692827048421)]</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>[np.float64(522.7894871192374), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" t="n">
+        <v>9</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>[np.float64(439.28067240362515), np.float64(53.01864446719399)]</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>[np.float64(439.28067240362515), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="n">
+        <v>11</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>1</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>[np.float64(572.3429409294965), np.float64(20.6601076032302)]</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>[np.float64(572.3429409294965), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="n">
+        <v>9</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>1</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>[np.float64(488.0950952669641), np.float64(61.91537411222067)]</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>[np.float64(488.0950952669641), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" t="n">
+        <v>8</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>1</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>[np.float64(401.7669592409966), np.float64(111.56604976027336)]</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>[np.float64(401.7669592409966), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="n">
+        <v>11</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>[np.float64(579.0750886933396), np.float64(177.69390306702195)]</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>[np.float64(579.0750886933396), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="n">
+        <v>11</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>[np.float64(597.3051450393441), np.float64(128.33292915751304)]</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>[np.float64(597.3051450393441), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="n">
+        <v>9</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>1</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>[np.float64(440.45980371598074), np.float64(122.57772937093793)]</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>[np.float64(440.45980371598074), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" t="n">
+        <v>11</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>[np.float64(551.1070340259128), np.float64(124.57216938793223)]</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>[np.float64(551.1070340259128), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="n">
+        <v>10</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>1</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>[np.float64(542.0086290126808), np.float64(112.32522419643698)]</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>[np.float64(542.0086290126808), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" t="n">
+        <v>10</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>[np.float64(533.6814720906084), np.float64(136.92932826979248)]</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>[np.float64(533.6814720906084), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="n">
+        <v>11</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>[np.float64(582.0157600579328), np.float64(113.45419521033493)]</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>[np.float64(582.0157600579328), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="n">
+        <v>8</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>[np.float64(410.68276887838726), np.float64(129.09786755004154)]</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>[np.float64(410.68276887838726), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="n">
+        <v>8</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>[np.float64(426.6351231876716), np.float64(145.51225318552514)]</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>[np.float64(426.6351231876716), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="n">
+        <v>11</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>[np.float64(554.1724979294196), np.float64(109.00859096243596)]</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>[np.float64(554.1724979294196), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" t="n">
+        <v>9</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>[np.float64(472.3645940022402), np.float64(122.52656156223695)]</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>[np.float64(472.3645940022402), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="n">
+        <v>10</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>[np.float64(500.01277026961577), np.float64(160.1134249945232)]</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>[np.float64(500.01277026961577), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" t="n">
+        <v>11</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>[np.float64(588.2157810133549), np.float64(115.15172335590117)]</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>[np.float64(588.2157810133549), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" t="n">
+        <v>10</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>[np.float64(496.0813072631903), np.float64(124.51533979168028)]</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>[np.float64(496.0813072631903), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" t="n">
+        <v>9</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>[np.float64(473.08333985238437), np.float64(111.38479613183024)]</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>[np.float64(473.08333985238437), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" t="n">
+        <v>8</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>[np.float64(410.1108267257912), np.float64(128.67859890611024)]</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>[np.float64(410.1108267257912), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" t="n">
+        <v>11</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>[np.float64(564.2483954443657), np.float64(126.34162457961543)]</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>[np.float64(564.2483954443657), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="n">
+        <v>8</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>1</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>[np.float64(427.37418080290695), np.float64(139.96573957659783)]</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>[np.float64(427.37418080290695), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="n">
+        <v>10</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>[np.float64(516.0207279532747), np.float64(125.1595655095212)]</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>[np.float64(516.0207279532747), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" t="n">
+        <v>10</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>[np.float64(548.7155018997637), np.float64(122.7803854447836)]</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>[np.float64(548.7155018997637), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" t="n">
+        <v>9</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>1</v>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>[np.float64(451.87598465574047), np.float64(117.20440532580773)]</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>[np.float64(451.87598465574047), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="n">
+        <v>11</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>3001.0</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>1</v>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>[np.float64(571.9296966395005), np.float64(107.69458921309915)]</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>[np.float64(571.9296966395005), np.float64(0.0)]</t>
         </is>
       </c>
     </row>

--- a/Data/output/DIR Stroke Position.xlsx
+++ b/Data/output/DIR Stroke Position.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,14 +482,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1015.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -503,16 +503,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[np.float64(851.8748704218192), np.float64(-42.12647066504758)]</t>
+          <t>[711.4149427916846, -38.96119287257261]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[np.float64(851.8748704218192), np.float64(0.0)]</t>
+          <t>[711.4149427916844, 0.0]</t>
         </is>
       </c>
     </row>
@@ -526,11 +526,11 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1014.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[np.float64(782.3475232506007), np.float64(-58.31101530623607)]</t>
+          <t>[988.025289283913, -62.54265039809593]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[np.float64(782.3475232506007), np.float64(0.0)]</t>
+          <t>[988.025289283913, 0.0]</t>
         </is>
       </c>
     </row>
@@ -564,14 +564,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1008.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[np.float64(418.0968579350375), np.float64(-83.58157232283094)]</t>
+          <t>[440.9745241542289, -36.20109395191241]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[np.float64(418.0968579350375), np.float64(0.0)]</t>
+          <t>[440.97452415422896, 0.0]</t>
         </is>
       </c>
     </row>
@@ -605,14 +605,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1002.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -626,16 +626,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[np.float64(45.86295964661508), np.float64(-19.598456182041048)]</t>
+          <t>[387.88510119470595, -132.72510898347076]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[np.float64(45.86295964661508), np.float64(0.0)]</t>
+          <t>[387.88510119470595, 0.0]</t>
         </is>
       </c>
     </row>
@@ -646,14 +646,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1013.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -667,16 +667,16 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[np.float64(749.4354939913844), np.float64(-51.96592582627744)]</t>
+          <t>[674.2519117533775, -40.49178675782605]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[np.float64(749.4354939913844), np.float64(0.0)]</t>
+          <t>[674.2519117533775, 0.0]</t>
         </is>
       </c>
     </row>
@@ -687,14 +687,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1005.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -708,16 +708,16 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[np.float64(254.58296765113062), np.float64(-7.987680158056605)]</t>
+          <t>[569.0066152128634, -94.987982984996]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[np.float64(254.58296765113062), np.float64(0.0)]</t>
+          <t>[569.0066152128635, 0.0]</t>
         </is>
       </c>
     </row>
@@ -728,14 +728,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1016.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -749,16 +749,16 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[np.float64(933.7504717270785), np.float64(-14.792172559060077)]</t>
+          <t>[199.61441225628926, -93.21179020483675]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[np.float64(933.7504717270785), np.float64(0.0)]</t>
+          <t>[199.61441225628923, 0.0]</t>
         </is>
       </c>
     </row>
@@ -769,14 +769,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -790,16 +790,16 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[np.float64(967.0666704136202), np.float64(-33.473786348624515)]</t>
+          <t>[739.9200769721833, -104.87223026029534]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[np.float64(967.0666704136202), np.float64(0.0)]</t>
+          <t>[739.9200769721833, 0.0]</t>
         </is>
       </c>
     </row>
@@ -810,14 +810,14 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1011.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -831,16 +831,16 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[np.float64(601.9695264549127), np.float64(-53.53414346999341)]</t>
+          <t>[736.9870572287637, -13.989857572530354]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[np.float64(601.9695264549127), np.float64(0.0)]</t>
+          <t>[736.9870572287637, 0.0]</t>
         </is>
       </c>
     </row>
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -872,16 +872,16 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[np.float64(20.249386932683592), np.float64(-43.077578047099564)]</t>
+          <t>[396.3757829459415, -15.440590032324224]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[np.float64(20.249386932683592), np.float64(0.0)]</t>
+          <t>[396.3757829459416, 0.0]</t>
         </is>
       </c>
     </row>
@@ -892,14 +892,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1014.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -913,16 +913,16 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[np.float64(761.4711691969874), np.float64(-6.67475010645569)]</t>
+          <t>[977.6619615985026, -14.92213309882419]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[np.float64(761.4711691969874), np.float64(0.0)]</t>
+          <t>[977.6619615985026, 0.0]</t>
         </is>
       </c>
     </row>
@@ -933,14 +933,14 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1003.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[np.float64(120.75718504831468), np.float64(-9.91457111515723)]</t>
+          <t>[172.37733931254718, -0.1756887297338494]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[np.float64(120.75718504831468), np.float64(0.0)]</t>
+          <t>[172.37733931254718, 0.0]</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -995,16 +995,16 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[np.float64(13.66550055606001), np.float64(-39.301237712587636)]</t>
+          <t>[768.3910342068, -16.84002239735463]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[np.float64(13.66550055606001), np.float64(0.0)]</t>
+          <t>[768.3910342067999, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1015,14 +1015,14 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[np.float64(967.4663546644279), np.float64(-58.02138382350495)]</t>
+          <t>[447.79803581333647, -45.56001618240305]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[np.float64(967.4663546644279), np.float64(0.0)]</t>
+          <t>[447.79803581333647, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1056,14 +1056,14 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1002.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[np.float64(74.25655486454548), np.float64(-0.30728599014105384)]</t>
+          <t>[368.06078390318237, -3.8872736757702455]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[np.float64(74.25655486454548), np.float64(0.0)]</t>
+          <t>[368.06078390318237, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1097,14 +1097,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1017.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1118,16 +1118,16 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[np.float64(994.5411516886545), np.float64(-4.176608242736336)]</t>
+          <t>[362.779745321165, -5.92696174200222]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[np.float64(994.5411516886545), np.float64(0.0)]</t>
+          <t>[362.779745321165, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -1159,16 +1159,16 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[np.float64(-53.181777021032985), np.float64(-65.85164522447451)]</t>
+          <t>[481.9412486237626, -30.368440835954686]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[np.float64(-53.181777021032985), np.float64(0.0)]</t>
+          <t>[481.9412486237626, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1179,14 +1179,14 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1003.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1200,16 +1200,16 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[np.float64(132.17496308304692), np.float64(-2.4096568277015535)]</t>
+          <t>[523.2538288688173, -55.62964281996972]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[np.float64(132.17496308304692), np.float64(0.0)]</t>
+          <t>[523.2538288688173, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1220,14 +1220,14 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1010.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1241,16 +1241,16 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[np.float64(567.6266930319835), np.float64(-24.407685355475223)]</t>
+          <t>[900.7854883309012, -26.436066508189185]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[np.float64(567.6266930319835), np.float64(0.0)]</t>
+          <t>[900.7854883309012, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1261,14 +1261,14 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1014.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1282,16 +1282,16 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[np.float64(800.276317967749), np.float64(-5.066202421486139)]</t>
+          <t>[16.3597494817202, -13.247986250413248]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[np.float64(800.276317967749), np.float64(0.0)]</t>
+          <t>[16.3597494817202, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1302,14 +1302,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1003.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1323,16 +1323,16 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[np.float64(155.0872482129637), np.float64(-12.409820375556023)]</t>
+          <t>[337.10736152553955, -13.888243168483712]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[np.float64(155.0872482129637), np.float64(0.0)]</t>
+          <t>[337.10736152553955, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1343,14 +1343,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1006.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1364,16 +1364,16 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[np.float64(325.21019648190247), np.float64(-10.31495826104566)]</t>
+          <t>[963.6520666308811, -46.625102632453434]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[np.float64(325.21019648190247), np.float64(0.0)]</t>
+          <t>[963.6520666308812, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1384,14 +1384,14 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1013.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1405,16 +1405,16 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[np.float64(749.0589222830006), np.float64(-19.474185973185286)]</t>
+          <t>[512.6595542678502, -2.9977453322518386]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[np.float64(749.0589222830006), np.float64(0.0)]</t>
+          <t>[512.6595542678502, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1425,14 +1425,14 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1014.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1446,16 +1446,16 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[np.float64(793.8288757931396), np.float64(-42.43908220516346)]</t>
+          <t>[881.6520836730645, -22.653093118935374]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[np.float64(793.8288757931396), np.float64(0.0)]</t>
+          <t>[881.6520836730645, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1466,14 +1466,14 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1012.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1487,16 +1487,16 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[np.float64(655.5011019289511), np.float64(-34.15828751186558)]</t>
+          <t>[305.003008013736, -85.42972545720238]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[np.float64(655.5011019289511), np.float64(0.0)]</t>
+          <t>[305.00300801373595, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1507,14 +1507,14 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1013.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1528,16 +1528,16 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[np.float64(712.8726804860341), np.float64(-83.05064756304682)]</t>
+          <t>[448.7426222794495, -9.51304164219323]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[np.float64(712.8726804860341), np.float64(0.0)]</t>
+          <t>[448.7426222794495, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1548,37 +1548,37 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1001.0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
         <v>14</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1014.0</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[np.float64(773.2754086688242), np.float64(-99.70178475181814)]</t>
+          <t>[414.7916015141619, -114.37257766599441]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[np.float64(773.2754086688242), np.float64(0.0)]</t>
+          <t>[414.79160151416187, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1589,14 +1589,14 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1014.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1610,16 +1610,16 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[np.float64(772.984530598274), np.float64(-49.69138018308962)]</t>
+          <t>[464.57781955332416, -4.402587444413882]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[np.float64(772.984530598274), np.float64(0.0)]</t>
+          <t>[464.5778195533241, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1630,14 +1630,14 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1003.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1651,16 +1651,16 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[np.float64(110.22202187898756), np.float64(-15.666464088874307)]</t>
+          <t>[457.09051614141697, -13.108824452144574]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[np.float64(110.22202187898756), np.float64(0.0)]</t>
+          <t>[457.09051614141697, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1671,14 +1671,14 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1006.0</t>
+          <t>1001.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1692,303 +1692,16 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[np.float64(324.0391440398797), np.float64(-117.03582577619119)]</t>
+          <t>[694.7286605941454, -13.106988608288987]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[np.float64(324.0391440398797), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="n">
-        <v>6</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1006.0</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>[np.float64(294.3511365166413), np.float64(-6.120849617444833)]</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>[np.float64(294.3511365166413), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="n">
-        <v>9</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1008.0</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>[np.float64(434.4392799133958), np.float64(-52.982279708372005)]</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>[np.float64(434.4392799133958), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="n">
-        <v>4</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1004.0</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>[np.float64(185.9872004246845), np.float64(-16.9679639346939)]</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>[np.float64(185.9872004246845), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" t="n">
-        <v>9</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1009.0</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>[np.float64(466.29444675744196), np.float64(-50.555639702091526)]</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>[np.float64(466.29444675744196), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="n">
-        <v>13</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>1012.0</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>[np.float64(671.4248552937579), np.float64(-42.02079440929617)]</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>[np.float64(671.4248552937579), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="n">
-        <v>14</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1014.0</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>[np.float64(763.1009110577531), np.float64(-69.73835660973629)]</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>[np.float64(763.1009110577531), np.float64(0.0)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="n">
-        <v>8</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1007.0</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>[np.float64(393.61134096416106), np.float64(-54.28810357974669)]</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>[np.float64(393.61134096416106), np.float64(0.0)]</t>
+          <t>[694.7286605941454, 0.0]</t>
         </is>
       </c>
     </row>

--- a/Data/output/DIR Stroke Position.xlsx
+++ b/Data/output/DIR Stroke Position.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,47 +472,6 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Location_of_the_lightning_strike_point_XY</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="n">
-        <v>8</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1001.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[np.float64(402.51612832532305), np.float64(0.03358675066214012)]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>[np.float64(402.51612832532305), np.float64(0.0)]</t>
         </is>
       </c>
     </row>

--- a/Data/output/DIR Stroke Position.xlsx
+++ b/Data/output/DIR Stroke Position.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,1892 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1013.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[np.float64(733.0165081135141), np.float64(-8.048430391955549)]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>[np.float64(733.0165081135141), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1009.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[np.float64(465.56850038899034), np.float64(-27.33039238628305)]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>[np.float64(465.56850038899034), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1013.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[np.float64(727.6704240682467), np.float64(-88.0388975997713)]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>[np.float64(727.6704240682467), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1004.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[np.float64(211.25324107854914), np.float64(-0.2447719879946817)]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>[np.float64(211.25324107854914), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1004.0</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[np.float64(195.9000279514228), np.float64(-48.51627851917897)]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>[np.float64(195.9000279514228), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1011.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[np.float64(598.4355813683216), np.float64(-51.2829789086602)]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>[np.float64(598.4355813683216), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1001.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[np.float64(6.810474343095341), np.float64(-150.2835441118225)]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>[np.float64(6.810474343095341), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1012.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[np.float64(660.2527143803798), np.float64(-56.30352140165883)]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>[np.float64(660.2527143803798), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1012.0</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[np.float64(669.6845689037859), np.float64(-7.159859822210592)]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>[np.float64(669.6845689037859), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>1005.0</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[np.float64(249.09770583766823), np.float64(-17.726645364130718)]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>[np.float64(249.09770583766823), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1012.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[np.float64(660.0720001359277), np.float64(-67.14333653061794)]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>[np.float64(660.0720001359277), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1012.0</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[np.float64(663.982273698885), np.float64(-2.089225258634883)]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>[np.float64(663.982273698885), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1010.0</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[np.float64(575.0605205047472), np.float64(-8.006389192669417)]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>[np.float64(575.0605205047472), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1005.0</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[np.float64(267.5070680264031), np.float64(-69.66029371019715)]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>[np.float64(267.5070680264031), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1009.0</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[np.float64(512.4542648393992), np.float64(-71.24396120960193)]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>[np.float64(512.4542648393992), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1003.0</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[np.float64(129.76512141032137), np.float64(-11.643524857276475)]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>[np.float64(129.76512141032137), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1006.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[np.float64(318.45451472565014), np.float64(-85.89133205903579)]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>[np.float64(318.45451472565014), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1008.0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[np.float64(408.12792322606884), np.float64(-16.59951654531494)]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>[np.float64(408.12792322606884), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1006.0</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[np.float64(293.8821352890807), np.float64(-82.07912299052634)]</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>[np.float64(293.8821352890807), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>9</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1009.0</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[np.float64(510.5001109595427), np.float64(-43.884826055324766)]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>[np.float64(510.5001109595427), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C22" t="n">
+        <v>16</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1016.0</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[np.float64(920.5643150298087), np.float64(-47.876259546955794)]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>[np.float64(920.5643150298087), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" t="n">
+        <v>16</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1016.0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[np.float64(889.4710772791987), np.float64(-26.130419758297307)]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>[np.float64(889.4710772791987), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>11</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1011.0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[np.float64(596.2461960642526), np.float64(-83.18217821426788)]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>[np.float64(596.2461960642526), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1004.0</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[np.float64(192.3943345758178), np.float64(-4.97916690202419)]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>[np.float64(192.3943345758178), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1006.0</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[np.float64(315.6894420488119), np.float64(-11.251957946407288)]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>[np.float64(315.6894420488119), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" t="n">
+        <v>16</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1016.0</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[np.float64(888.3234208703924), np.float64(-18.76941076156777)]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>[np.float64(888.3234208703924), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1009.0</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[np.float64(475.5587624130323), np.float64(-59.51322403823167)]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>[np.float64(475.5587624130323), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>13</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1013.0</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[np.float64(727.5548094802912), np.float64(-27.943629654302185)]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>[np.float64(727.5548094802912), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1003.0</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[np.float64(137.1493156982253), np.float64(-9.281235105344535)]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>[np.float64(137.1493156982253), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="n">
+        <v>16</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1016.0</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[np.float64(917.0557854939545), np.float64(-33.34745049514049)]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>[np.float64(917.0557854939545), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1005.0</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[np.float64(255.56073538372138), np.float64(-79.75568304341743)]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>[np.float64(255.56073538372138), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1008.0</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[np.float64(405.02920371032167), np.float64(-47.872325345489344)]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>[np.float64(405.02920371032167), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>13</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1013.0</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[np.float64(737.5443689303721), np.float64(-17.36577581236122)]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>[np.float64(737.5443689303721), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="n">
+        <v>12</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1012.0</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[np.float64(681.9445320922364), np.float64(-6.22372175455007)]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>[np.float64(681.9445320922364), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="n">
+        <v>10</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1010.0</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[np.float64(545.1922579186834), np.float64(-0.7272660485410825)]</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>[np.float64(545.1922579186834), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1005.0</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>[np.float64(250.6474911691805), np.float64(-47.579716077582134)]</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>[np.float64(250.6474911691805), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>12</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1012.0</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[np.float64(676.7711989897225), np.float64(-65.64363865179348)]</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>[np.float64(676.7711989897225), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" t="n">
+        <v>14</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1014.0</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>[np.float64(796.0798196733929), np.float64(-42.93584623144477)]</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>[np.float64(796.0798196733929), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" t="n">
+        <v>15</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1015.0</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>[np.float64(867.2597990294473), np.float64(-31.925571050027088)]</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>[np.float64(867.2597990294473), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1002.0</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>[np.float64(91.73887142820914), np.float64(-31.005637531957746)]</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>[np.float64(91.73887142820914), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="n">
+        <v>9</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1009.0</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[np.float64(502.2358607820674), np.float64(-25.745271595576696)]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>[np.float64(502.2358607820674), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1002.0</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>[np.float64(48.800607611819366), np.float64(-33.71395420003239)]</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>[np.float64(48.800607611819366), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1012.0</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[np.float64(675.624128830836), np.float64(-38.76339034251123)]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>[np.float64(675.624128830836), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="n">
+        <v>9</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1009.0</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[np.float64(486.3442518574466), np.float64(-66.15214471885838)]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>[np.float64(486.3442518574466), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>15</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1015.0</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>[np.float64(847.3312793092756), np.float64(-42.30849093581571)]</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>[np.float64(847.3312793092756), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1004.0</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[np.float64(208.2124117309694), np.float64(-20.15560013021718)]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>[np.float64(208.2124117309694), np.float64(0.0)]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/output/DIR Stroke Position.xlsx
+++ b/Data/output/DIR Stroke Position.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="151">
   <si>
     <t>Direct_or_Indirect</t>
   </si>
@@ -46,463 +46,427 @@
     <t>Direct</t>
   </si>
   <si>
+    <t>1013.0</t>
+  </si>
+  <si>
+    <t>1008.0</t>
+  </si>
+  <si>
+    <t>1014.0</t>
+  </si>
+  <si>
+    <t>1015.0</t>
+  </si>
+  <si>
+    <t>1016.0</t>
+  </si>
+  <si>
+    <t>1011.0</t>
+  </si>
+  <si>
+    <t>1017.0</t>
+  </si>
+  <si>
+    <t>1004.0</t>
+  </si>
+  <si>
+    <t>1010.0</t>
+  </si>
+  <si>
+    <t>1007.0</t>
+  </si>
+  <si>
+    <t>1002.0</t>
+  </si>
+  <si>
+    <t>1003.0</t>
+  </si>
+  <si>
     <t>1005.0</t>
   </si>
   <si>
-    <t>1008.0</t>
-  </si>
-  <si>
-    <t>1003.0</t>
+    <t>1009.0</t>
+  </si>
+  <si>
+    <t>1012.0</t>
+  </si>
+  <si>
+    <t>1001.0</t>
   </si>
   <si>
     <t>1006.0</t>
   </si>
   <si>
-    <t>1014.0</t>
-  </si>
-  <si>
-    <t>1011.0</t>
-  </si>
-  <si>
-    <t>1002.0</t>
-  </si>
-  <si>
-    <t>1012.0</t>
-  </si>
-  <si>
-    <t>1001.0</t>
-  </si>
-  <si>
-    <t>1010.0</t>
-  </si>
-  <si>
-    <t>1015.0</t>
-  </si>
-  <si>
-    <t>1009.0</t>
-  </si>
-  <si>
-    <t>1007.0</t>
-  </si>
-  <si>
-    <t>1017.0</t>
-  </si>
-  <si>
-    <t>1004.0</t>
-  </si>
-  <si>
-    <t>1016.0</t>
-  </si>
-  <si>
-    <t>1013.0</t>
-  </si>
-  <si>
     <t>0.0</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>[np.float64(231.71003177618599), np.float64(-3.4165205459649997)]</t>
-  </si>
-  <si>
-    <t>[np.float64(445.18921536453195), np.float64(-23.798254587244628)]</t>
-  </si>
-  <si>
-    <t>[np.float64(142.19211639975182), np.float64(-3.9311899917245228)]</t>
-  </si>
-  <si>
-    <t>[np.float64(319.81772955242707), np.float64(-11.110784022481198)]</t>
-  </si>
-  <si>
-    <t>[np.float64(240.17948976033333), np.float64(-5.60337612122828)]</t>
-  </si>
-  <si>
-    <t>[np.float64(768.5116696903372), np.float64(-72.50162721265872)]</t>
-  </si>
-  <si>
-    <t>[np.float64(606.5645702399255), np.float64(-20.399068107249832)]</t>
-  </si>
-  <si>
-    <t>[np.float64(227.95852068553256), np.float64(-12.082123739137842)]</t>
-  </si>
-  <si>
-    <t>[np.float64(75.11112295657551), np.float64(-107.59558050057785)]</t>
-  </si>
-  <si>
-    <t>[np.float64(66.57354907390078), np.float64(-52.67790729291073)]</t>
-  </si>
-  <si>
-    <t>[np.float64(262.8525109119766), np.float64(-53.60673718970918)]</t>
-  </si>
-  <si>
-    <t>[np.float64(286.27773924561995), np.float64(-42.75653578220977)]</t>
-  </si>
-  <si>
-    <t>[np.float64(674.656771217474), np.float64(-27.728158507613216)]</t>
-  </si>
-  <si>
-    <t>[np.float64(1.1819023614690893), np.float64(-44.2118328276174)]</t>
-  </si>
-  <si>
-    <t>[np.float64(88.59870121887514), np.float64(-79.37943683241963)]</t>
-  </si>
-  <si>
-    <t>[np.float64(581.143707294216), np.float64(-35.138101340500725)]</t>
-  </si>
-  <si>
-    <t>[np.float64(655.7625087941029), np.float64(-41.21195893202946)]</t>
-  </si>
-  <si>
-    <t>[np.float64(525.4400506264218), np.float64(-27.987089896670568)]</t>
-  </si>
-  <si>
-    <t>[np.float64(824.10898743638), np.float64(-2.7055652008100424)]</t>
-  </si>
-  <si>
-    <t>[np.float64(321.98782793810096), np.float64(-2.446485103831378)]</t>
-  </si>
-  <si>
-    <t>[np.float64(493.43988425284215), np.float64(-7.115149603733357)]</t>
-  </si>
-  <si>
-    <t>[np.float64(372.76497165362923), np.float64(-72.08282529378607)]</t>
-  </si>
-  <si>
-    <t>[np.float64(285.0180345535004), np.float64(-77.2999823496408)]</t>
-  </si>
-  <si>
-    <t>[np.float64(436.7604069236606), np.float64(-64.88853297608728)]</t>
-  </si>
-  <si>
-    <t>[np.float64(437.18004835442), np.float64(-49.01593116591414)]</t>
-  </si>
-  <si>
-    <t>[np.float64(554.3042907052726), np.float64(-9.554471898064321)]</t>
-  </si>
-  <si>
-    <t>[np.float64(30.951759635157394), np.float64(-32.13481442144098)]</t>
-  </si>
-  <si>
-    <t>[np.float64(454.85432586238693), np.float64(-44.13459090751758)]</t>
-  </si>
-  <si>
-    <t>[np.float64(971.6331769750963), np.float64(-75.29046827450895)]</t>
-  </si>
-  <si>
-    <t>[np.float64(195.90763949129507), np.float64(-17.596036439643058)]</t>
-  </si>
-  <si>
-    <t>[np.float64(784.143632304911), np.float64(-56.12723133731458)]</t>
-  </si>
-  <si>
-    <t>[np.float64(5.093074479552984), np.float64(-5.806121133469446)]</t>
-  </si>
-  <si>
-    <t>[np.float64(965.5174259092523), np.float64(-37.031811972372225)]</t>
-  </si>
-  <si>
-    <t>[np.float64(872.9377385467667), np.float64(-33.813569031166594)]</t>
-  </si>
-  <si>
-    <t>[np.float64(246.40801982308147), np.float64(-103.77122792336922)]</t>
-  </si>
-  <si>
-    <t>[np.float64(987.3450374599581), np.float64(-25.504011852920712)]</t>
-  </si>
-  <si>
-    <t>[np.float64(599.4221391063784), np.float64(-34.859087923588845)]</t>
-  </si>
-  <si>
-    <t>[np.float64(286.1669064652197), np.float64(-6.419765876051883)]</t>
-  </si>
-  <si>
-    <t>[np.float64(352.0690873614002), np.float64(-79.3832103517891)]</t>
-  </si>
-  <si>
-    <t>[np.float64(568.2802040420816), np.float64(-87.5637988269292)]</t>
-  </si>
-  <si>
-    <t>[np.float64(674.2414416435481), np.float64(-27.56898267049951)]</t>
-  </si>
-  <si>
-    <t>[np.float64(892.0941070986829), np.float64(-105.07869740599881)]</t>
-  </si>
-  <si>
-    <t>[np.float64(756.9549170968362), np.float64(-23.292191599127136)]</t>
-  </si>
-  <si>
-    <t>[np.float64(116.15090218690993), np.float64(-63.67459536477429)]</t>
-  </si>
-  <si>
-    <t>[np.float64(2.9343853371807116), np.float64(-64.3841063079069)]</t>
-  </si>
-  <si>
-    <t>[np.float64(717.7144142966872), np.float64(-7.007104740793579)]</t>
-  </si>
-  <si>
-    <t>[np.float64(405.8842702902299), np.float64(-45.021948300630356)]</t>
-  </si>
-  <si>
-    <t>[np.float64(992.9137793357693), np.float64(-12.438357570055473)]</t>
-  </si>
-  <si>
-    <t>[np.float64(329.80698491187235), np.float64(-5.175917040471859)]</t>
-  </si>
-  <si>
-    <t>[np.float64(613.7142040421347), np.float64(-57.41061866461223)]</t>
-  </si>
-  <si>
-    <t>[np.float64(782.7583280292491), np.float64(-70.56093464047137)]</t>
-  </si>
-  <si>
-    <t>[np.float64(74.20416999277369), np.float64(-6.300946546961427)]</t>
-  </si>
-  <si>
-    <t>[np.float64(307.3890382680287), np.float64(-60.170112283841945)]</t>
-  </si>
-  <si>
-    <t>[np.float64(970.6949506495354), np.float64(-8.510183780177385)]</t>
-  </si>
-  <si>
-    <t>[np.float64(499.51574785022945), np.float64(-90.46349914949536)]</t>
-  </si>
-  <si>
-    <t>[np.float64(461.470899433068), np.float64(-44.088720879724974)]</t>
-  </si>
-  <si>
-    <t>[np.float64(15.531867531233035), np.float64(-9.219499073907059)]</t>
-  </si>
-  <si>
-    <t>[np.float64(620.4903227623192), np.float64(-96.57297471848631)]</t>
-  </si>
-  <si>
-    <t>[np.float64(19.560442923199915), np.float64(-24.64656708543953)]</t>
-  </si>
-  <si>
-    <t>[np.float64(677.9365412293106), np.float64(-80.01874998344033)]</t>
-  </si>
-  <si>
-    <t>[np.float64(3.9203034697736783), np.float64(-34.78097090201254)]</t>
-  </si>
-  <si>
-    <t>[np.float64(239.5138928681505), np.float64(-18.440852160953455)]</t>
-  </si>
-  <si>
-    <t>[np.float64(247.65838539774387), np.float64(-27.375225130207696)]</t>
-  </si>
-  <si>
-    <t>[np.float64(133.54299702143646), np.float64(-1.9363471096623925)]</t>
-  </si>
-  <si>
-    <t>[np.float64(264.7481276679059), np.float64(-68.47169516860038)]</t>
-  </si>
-  <si>
-    <t>[np.float64(753.6743275614348), np.float64(-45.267796896993445)]</t>
-  </si>
-  <si>
-    <t>[np.float64(583.4648780289866), np.float64(-48.217055312468915)]</t>
-  </si>
-  <si>
-    <t>[np.float64(231.71003177618599), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(445.18921536453195), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(142.19211639975182), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(319.81772955242707), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(240.17948976033333), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(768.5116696903372), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(606.5645702399255), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(227.95852068553256), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(75.11112295657551), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(66.57354907390078), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(262.8525109119766), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(286.27773924561995), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(674.656771217474), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(1.1819023614690893), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(88.59870121887514), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(581.143707294216), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(655.7625087941029), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(525.4400506264218), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(824.10898743638), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(321.98782793810096), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(493.43988425284215), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(372.76497165362923), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(285.0180345535004), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(436.7604069236606), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(437.18004835442), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(554.3042907052726), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(30.951759635157394), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(454.85432586238693), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(971.6331769750963), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(195.90763949129507), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(784.143632304911), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(5.093074479552984), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(965.5174259092523), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(872.9377385467667), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(246.40801982308147), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(987.3450374599581), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(599.4221391063784), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(286.1669064652197), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(352.0690873614002), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(568.2802040420816), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(674.2414416435481), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(892.0941070986829), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(756.9549170968362), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(116.15090218690993), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(2.9343853371807116), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(717.7144142966872), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(405.8842702902299), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(992.9137793357693), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(329.80698491187235), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(613.7142040421347), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(782.7583280292491), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(74.20416999277369), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(307.3890382680287), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(970.6949506495354), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(499.51574785022945), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(461.470899433068), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(15.531867531233035), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(620.4903227623192), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(19.560442923199915), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(677.9365412293106), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(3.9203034697736783), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(239.5138928681505), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(247.65838539774387), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(133.54299702143646), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(264.7481276679059), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(753.6743275614348), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(583.4648780289866), np.float64(0.0)]</t>
+    <t>[np.float64(736.864941489601), np.float64(-23.459933625752)]</t>
+  </si>
+  <si>
+    <t>[np.float64(433.80953060443494), np.float64(-41.183859911030254)]</t>
+  </si>
+  <si>
+    <t>[np.float64(721.3154875579597), np.float64(-31.980641502339836)]</t>
+  </si>
+  <si>
+    <t>[np.float64(811.8124186294002), np.float64(-41.72594195300769)]</t>
+  </si>
+  <si>
+    <t>[np.float64(820.1635608302231), np.float64(-56.68205648449202)]</t>
+  </si>
+  <si>
+    <t>[np.float64(900.9325768686019), np.float64(-7.333511952245999)]</t>
+  </si>
+  <si>
+    <t>[np.float64(620.0288105096155), np.float64(-16.598211526448154)]</t>
+  </si>
+  <si>
+    <t>[np.float64(623.2259535298366), np.float64(-58.97509988310628)]</t>
+  </si>
+  <si>
+    <t>[np.float64(982.7380577882424), np.float64(-10.858647597939125)]</t>
+  </si>
+  <si>
+    <t>[np.float64(162.05563907935772), np.float64(-69.65763660008031)]</t>
+  </si>
+  <si>
+    <t>[np.float64(976.3971823296371), np.float64(-77.0522692894682)]</t>
+  </si>
+  <si>
+    <t>[np.float64(570.4203613518029), np.float64(-39.91313106366556)]</t>
+  </si>
+  <si>
+    <t>[np.float64(353.62518362069704), np.float64(-27.699101968806076)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.7701657566072), np.float64(-33.5029644667527)]</t>
+  </si>
+  <si>
+    <t>[np.float64(786.3395522722296), np.float64(-74.53171280564175)]</t>
+  </si>
+  <si>
+    <t>[np.float64(354.62686667034274), np.float64(-46.45634425014248)]</t>
+  </si>
+  <si>
+    <t>[np.float64(905.6535786277253), np.float64(-45.577125053637246)]</t>
+  </si>
+  <si>
+    <t>[np.float64(747.4932420161771), np.float64(-9.747233383561593)]</t>
+  </si>
+  <si>
+    <t>[np.float64(57.88797961583481), np.float64(-33.68400617047348)]</t>
+  </si>
+  <si>
+    <t>[np.float64(430.67235501854316), np.float64(-5.211151016687268)]</t>
+  </si>
+  <si>
+    <t>[np.float64(123.26482231534585), np.float64(-5.399359883844795)]</t>
+  </si>
+  <si>
+    <t>[np.float64(139.7143991073193), np.float64(-49.4027326371795)]</t>
+  </si>
+  <si>
+    <t>[np.float64(859.3321330637649), np.float64(-13.220859307199134)]</t>
+  </si>
+  <si>
+    <t>[np.float64(223.13305618651646), np.float64(-24.77141480516684)]</t>
+  </si>
+  <si>
+    <t>[np.float64(500.18315201707696), np.float64(-89.92887358557749)]</t>
+  </si>
+  <si>
+    <t>[np.float64(834.1094922128001), np.float64(-41.694854513005225)]</t>
+  </si>
+  <si>
+    <t>[np.float64(667.9412688011267), np.float64(-39.90715488673311)]</t>
+  </si>
+  <si>
+    <t>[np.float64(103.01970808235583), np.float64(-71.97603240249339)]</t>
+  </si>
+  <si>
+    <t>[np.float64(400.9560004253943), np.float64(-4.500144181129826)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4031417705256963), np.float64(-14.546923054125159)]</t>
+  </si>
+  <si>
+    <t>[np.float64(499.4687735212923), np.float64(-83.37678223695775)]</t>
+  </si>
+  <si>
+    <t>[np.float64(325.0003886349967), np.float64(-5.52106448347547)]</t>
+  </si>
+  <si>
+    <t>[np.float64(833.1349332932796), np.float64(-63.854839411081684)]</t>
+  </si>
+  <si>
+    <t>[np.float64(497.64054452854924), np.float64(-83.63775670309292)]</t>
+  </si>
+  <si>
+    <t>[np.float64(14.763121206316065), np.float64(-46.639917018454526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(859.5378356386898), np.float64(-2.8716986032735576)]</t>
+  </si>
+  <si>
+    <t>[np.float64(972.0760605582678), np.float64(-54.90338935387649)]</t>
+  </si>
+  <si>
+    <t>[np.float64(794.9570421646395), np.float64(-34.657824840789544)]</t>
+  </si>
+  <si>
+    <t>[np.float64(964.3303594495613), np.float64(-20.699746479376245)]</t>
+  </si>
+  <si>
+    <t>[np.float64(144.2048124302978), np.float64(-29.57745301221871)]</t>
+  </si>
+  <si>
+    <t>[np.float64(178.66835135721283), np.float64(-25.768941052179912)]</t>
+  </si>
+  <si>
+    <t>[np.float64(874.0060269906589), np.float64(-38.57362718882348)]</t>
+  </si>
+  <si>
+    <t>[np.float64(783.4932261968663), np.float64(-106.28786672668838)]</t>
+  </si>
+  <si>
+    <t>[np.float64(742.5381671551078), np.float64(-24.338046909968057)]</t>
+  </si>
+  <si>
+    <t>[np.float64(595.4516410544009), np.float64(-44.66042430220682)]</t>
+  </si>
+  <si>
+    <t>[np.float64(573.9981213204974), np.float64(-10.627129148001586)]</t>
+  </si>
+  <si>
+    <t>[np.float64(615.0656398203273), np.float64(-20.086481242965874)]</t>
+  </si>
+  <si>
+    <t>[np.float64(888.0420178215439), np.float64(-20.564276636114528)]</t>
+  </si>
+  <si>
+    <t>[np.float64(688.4191865508111), np.float64(-6.373162720602295)]</t>
+  </si>
+  <si>
+    <t>[np.float64(211.52498376490092), np.float64(-22.10937271547789)]</t>
+  </si>
+  <si>
+    <t>[np.float64(205.16035376916898), np.float64(-19.414352995102035)]</t>
+  </si>
+  <si>
+    <t>[np.float64(377.208002721977), np.float64(-47.091939151830616)]</t>
+  </si>
+  <si>
+    <t>[np.float64(692.2187629553888), np.float64(-51.02097134462292)]</t>
+  </si>
+  <si>
+    <t>[np.float64(393.1493963793832), np.float64(-66.78958345449837)]</t>
+  </si>
+  <si>
+    <t>[np.float64(148.1505615779981), np.float64(-23.448459099112483)]</t>
+  </si>
+  <si>
+    <t>[np.float64(514.2681836084121), np.float64(-57.86500664155665)]</t>
+  </si>
+  <si>
+    <t>[np.float64(735.8520577115462), np.float64(-90.32256844245438)]</t>
+  </si>
+  <si>
+    <t>[np.float64(611.830587918147), np.float64(-31.948575870406785)]</t>
+  </si>
+  <si>
+    <t>[np.float64(541.0520910436898), np.float64(-20.12501610370896)]</t>
+  </si>
+  <si>
+    <t>[np.float64(268.6109457607336), np.float64(-36.081593792960916)]</t>
+  </si>
+  <si>
+    <t>[np.float64(450.84587393826223), np.float64(-55.9431475510396)]</t>
+  </si>
+  <si>
+    <t>[np.float64(736.864941489601), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(433.80953060443494), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(721.3154875579597), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(811.8124186294002), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(820.1635608302231), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(900.9325768686019), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(620.0288105096155), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(623.2259535298366), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(982.7380577882424), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(162.05563907935772), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(976.3971823296371), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(570.4203613518029), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(353.62518362069704), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.7701657566072), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(786.3395522722296), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(354.62686667034274), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(905.6535786277253), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(747.4932420161771), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(57.88797961583481), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(430.67235501854316), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(123.26482231534585), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(139.7143991073193), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(859.3321330637649), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(223.13305618651646), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(500.18315201707696), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(834.1094922128001), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(667.9412688011267), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(103.01970808235583), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(400.9560004253943), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.4031417705256963), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(499.4687735212923), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(325.0003886349967), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(833.1349332932796), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(497.64054452854924), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(14.763121206316065), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(859.5378356386898), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(972.0760605582678), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(794.9570421646395), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(964.3303594495613), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(144.2048124302978), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(178.66835135721283), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(874.0060269906589), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(783.4932261968663), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(742.5381671551078), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(595.4516410544009), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(573.9981213204974), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(615.0656398203273), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(888.0420178215439), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(688.4191865508111), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(211.52498376490092), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(205.16035376916898), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(377.208002721977), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(692.2187629553888), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(393.1493963793832), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(148.1505615779981), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(514.2681836084121), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(735.8520577115462), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(611.830587918147), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(541.0520910436898), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(268.6109457607336), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(450.84587393826223), np.float64(0.0)]</t>
   </si>
 </sst>
 </file>
@@ -860,7 +824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -900,7 +864,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -912,13 +876,13 @@
         <v>28</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="s">
         <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -941,13 +905,13 @@
         <v>28</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="s">
         <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -958,10 +922,10 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
@@ -970,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="s">
         <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -987,10 +951,10 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
@@ -999,13 +963,13 @@
         <v>28</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="s">
         <v>32</v>
       </c>
       <c r="I5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1016,10 +980,10 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
@@ -1028,13 +992,13 @@
         <v>28</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="s">
         <v>33</v>
       </c>
       <c r="I6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1045,7 +1009,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
@@ -1057,13 +1021,13 @@
         <v>28</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="s">
         <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1086,13 +1050,13 @@
         <v>28</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="s">
         <v>35</v>
       </c>
       <c r="I8" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1103,10 +1067,10 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D9" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
@@ -1115,13 +1079,13 @@
         <v>28</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="s">
         <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1132,7 +1096,7 @@
         <v>2</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
@@ -1144,13 +1108,13 @@
         <v>28</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="s">
         <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1161,10 +1125,10 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
         <v>27</v>
@@ -1173,13 +1137,13 @@
         <v>28</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
         <v>38</v>
       </c>
       <c r="I11" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1190,10 +1154,10 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
         <v>27</v>
@@ -1202,13 +1166,13 @@
         <v>28</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="s">
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1219,10 +1183,10 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -1231,13 +1195,13 @@
         <v>28</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="s">
         <v>40</v>
       </c>
       <c r="I13" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1248,10 +1212,10 @@
         <v>2</v>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -1260,13 +1224,13 @@
         <v>28</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="s">
         <v>41</v>
       </c>
       <c r="I14" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1277,10 +1241,10 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" t="s">
         <v>27</v>
@@ -1289,13 +1253,13 @@
         <v>28</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1306,10 +1270,10 @@
         <v>2</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E16" t="s">
         <v>27</v>
@@ -1318,13 +1282,13 @@
         <v>28</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>43</v>
       </c>
       <c r="I16" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1335,10 +1299,10 @@
         <v>2</v>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
@@ -1353,7 +1317,7 @@
         <v>44</v>
       </c>
       <c r="I17" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1364,10 +1328,10 @@
         <v>2</v>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -1376,13 +1340,13 @@
         <v>28</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
       </c>
       <c r="I18" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1393,11 +1357,11 @@
         <v>2</v>
       </c>
       <c r="C19">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
         <v>10</v>
       </c>
-      <c r="D19" t="s">
-        <v>19</v>
-      </c>
       <c r="E19" t="s">
         <v>27</v>
       </c>
@@ -1405,13 +1369,13 @@
         <v>28</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" t="s">
         <v>46</v>
       </c>
       <c r="I19" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1422,7 +1386,7 @@
         <v>2</v>
       </c>
       <c r="C20">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
         <v>20</v>
@@ -1440,7 +1404,7 @@
         <v>47</v>
       </c>
       <c r="I20" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1451,10 +1415,10 @@
         <v>2</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -1463,13 +1427,13 @@
         <v>28</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21" t="s">
         <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1480,7 +1444,7 @@
         <v>2</v>
       </c>
       <c r="C22">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D22" t="s">
         <v>21</v>
@@ -1498,7 +1462,7 @@
         <v>49</v>
       </c>
       <c r="I22" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1509,10 +1473,10 @@
         <v>2</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E23" t="s">
         <v>27</v>
@@ -1527,7 +1491,7 @@
         <v>50</v>
       </c>
       <c r="I23" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1538,7 +1502,7 @@
         <v>2</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
         <v>13</v>
@@ -1550,13 +1514,13 @@
         <v>28</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="s">
         <v>51</v>
       </c>
       <c r="I24" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1567,10 +1531,10 @@
         <v>2</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>
@@ -1579,13 +1543,13 @@
         <v>28</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="s">
         <v>52</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1596,10 +1560,10 @@
         <v>2</v>
       </c>
       <c r="C26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
@@ -1608,13 +1572,13 @@
         <v>28</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" t="s">
         <v>53</v>
       </c>
       <c r="I26" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1625,10 +1589,10 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
@@ -1637,13 +1601,13 @@
         <v>28</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="s">
         <v>54</v>
       </c>
       <c r="I27" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1654,10 +1618,10 @@
         <v>2</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -1672,7 +1636,7 @@
         <v>55</v>
       </c>
       <c r="I28" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1683,10 +1647,10 @@
         <v>2</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -1695,13 +1659,13 @@
         <v>28</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H29" t="s">
         <v>56</v>
       </c>
       <c r="I29" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1712,10 +1676,10 @@
         <v>2</v>
       </c>
       <c r="C30">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E30" t="s">
         <v>27</v>
@@ -1724,13 +1688,13 @@
         <v>28</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="s">
         <v>57</v>
       </c>
       <c r="I30" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1741,10 +1705,10 @@
         <v>2</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
@@ -1753,13 +1717,13 @@
         <v>28</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="s">
         <v>58</v>
       </c>
       <c r="I31" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1770,10 +1734,10 @@
         <v>2</v>
       </c>
       <c r="C32">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E32" t="s">
         <v>27</v>
@@ -1788,7 +1752,7 @@
         <v>59</v>
       </c>
       <c r="I32" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1799,10 +1763,10 @@
         <v>2</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E33" t="s">
         <v>27</v>
@@ -1811,13 +1775,13 @@
         <v>28</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" t="s">
         <v>60</v>
       </c>
       <c r="I33" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1828,10 +1792,10 @@
         <v>2</v>
       </c>
       <c r="C34">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -1840,13 +1804,13 @@
         <v>28</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="s">
         <v>61</v>
       </c>
       <c r="I34" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1857,10 +1821,10 @@
         <v>2</v>
       </c>
       <c r="C35">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D35" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E35" t="s">
         <v>27</v>
@@ -1869,13 +1833,13 @@
         <v>28</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H35" t="s">
         <v>62</v>
       </c>
       <c r="I35" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1886,10 +1850,10 @@
         <v>2</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D36" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -1898,13 +1862,13 @@
         <v>28</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="s">
         <v>63</v>
       </c>
       <c r="I36" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1915,10 +1879,10 @@
         <v>2</v>
       </c>
       <c r="C37">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="E37" t="s">
         <v>27</v>
@@ -1927,13 +1891,13 @@
         <v>28</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" t="s">
         <v>64</v>
       </c>
       <c r="I37" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1944,10 +1908,10 @@
         <v>2</v>
       </c>
       <c r="C38">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E38" t="s">
         <v>27</v>
@@ -1956,13 +1920,13 @@
         <v>28</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="s">
         <v>65</v>
       </c>
       <c r="I38" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1973,10 +1937,10 @@
         <v>2</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E39" t="s">
         <v>27</v>
@@ -1985,13 +1949,13 @@
         <v>28</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="s">
         <v>66</v>
       </c>
       <c r="I39" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2002,10 +1966,10 @@
         <v>2</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D40" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E40" t="s">
         <v>27</v>
@@ -2014,13 +1978,13 @@
         <v>28</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="s">
         <v>67</v>
       </c>
       <c r="I40" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2031,10 +1995,10 @@
         <v>2</v>
       </c>
       <c r="C41">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E41" t="s">
         <v>27</v>
@@ -2049,7 +2013,7 @@
         <v>68</v>
       </c>
       <c r="I41" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2060,7 +2024,7 @@
         <v>2</v>
       </c>
       <c r="C42">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D42" t="s">
         <v>17</v>
@@ -2072,13 +2036,13 @@
         <v>28</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="s">
         <v>69</v>
       </c>
       <c r="I42" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2089,10 +2053,10 @@
         <v>2</v>
       </c>
       <c r="C43">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -2101,13 +2065,13 @@
         <v>28</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H43" t="s">
         <v>70</v>
       </c>
       <c r="I43" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2118,10 +2082,10 @@
         <v>2</v>
       </c>
       <c r="C44">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -2130,13 +2094,13 @@
         <v>28</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>71</v>
       </c>
       <c r="I44" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2147,10 +2111,10 @@
         <v>2</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2159,13 +2123,13 @@
         <v>28</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" t="s">
         <v>72</v>
       </c>
       <c r="I45" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2176,10 +2140,10 @@
         <v>2</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -2194,7 +2158,7 @@
         <v>73</v>
       </c>
       <c r="I46" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2205,10 +2169,10 @@
         <v>2</v>
       </c>
       <c r="C47">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D47" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2217,13 +2181,13 @@
         <v>28</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47" t="s">
         <v>74</v>
       </c>
       <c r="I47" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2234,10 +2198,10 @@
         <v>2</v>
       </c>
       <c r="C48">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D48" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2246,13 +2210,13 @@
         <v>28</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="s">
         <v>75</v>
       </c>
       <c r="I48" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2263,10 +2227,10 @@
         <v>2</v>
       </c>
       <c r="C49">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E49" t="s">
         <v>27</v>
@@ -2275,13 +2239,13 @@
         <v>28</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H49" t="s">
         <v>76</v>
       </c>
       <c r="I49" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2292,10 +2256,10 @@
         <v>2</v>
       </c>
       <c r="C50">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
         <v>27</v>
@@ -2310,7 +2274,7 @@
         <v>77</v>
       </c>
       <c r="I50" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2321,10 +2285,10 @@
         <v>2</v>
       </c>
       <c r="C51">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E51" t="s">
         <v>27</v>
@@ -2333,13 +2297,13 @@
         <v>28</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" t="s">
         <v>78</v>
       </c>
       <c r="I51" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2350,10 +2314,10 @@
         <v>2</v>
       </c>
       <c r="C52">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -2362,13 +2326,13 @@
         <v>28</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52" t="s">
         <v>79</v>
       </c>
       <c r="I52" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2379,10 +2343,10 @@
         <v>2</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D53" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -2397,7 +2361,7 @@
         <v>80</v>
       </c>
       <c r="I53" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2408,10 +2372,10 @@
         <v>2</v>
       </c>
       <c r="C54">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -2420,13 +2384,13 @@
         <v>28</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" t="s">
         <v>81</v>
       </c>
       <c r="I54" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2437,10 +2401,10 @@
         <v>2</v>
       </c>
       <c r="C55">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D55" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E55" t="s">
         <v>27</v>
@@ -2449,13 +2413,13 @@
         <v>28</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55" t="s">
         <v>82</v>
       </c>
       <c r="I55" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2466,7 +2430,7 @@
         <v>2</v>
       </c>
       <c r="C56">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D56" t="s">
         <v>21</v>
@@ -2478,13 +2442,13 @@
         <v>28</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56" t="s">
         <v>83</v>
       </c>
       <c r="I56" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2498,7 +2462,7 @@
         <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
@@ -2507,13 +2471,13 @@
         <v>28</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" t="s">
         <v>84</v>
       </c>
       <c r="I57" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2524,25 +2488,25 @@
         <v>2</v>
       </c>
       <c r="C58">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" t="s">
+        <v>28</v>
+      </c>
+      <c r="G58">
         <v>1</v>
-      </c>
-      <c r="D58" t="s">
-        <v>18</v>
-      </c>
-      <c r="E58" t="s">
-        <v>27</v>
-      </c>
-      <c r="F58" t="s">
-        <v>28</v>
-      </c>
-      <c r="G58">
-        <v>0</v>
       </c>
       <c r="H58" t="s">
         <v>85</v>
       </c>
       <c r="I58" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2565,13 +2529,13 @@
         <v>28</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H59" t="s">
         <v>86</v>
       </c>
       <c r="I59" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2582,7 +2546,7 @@
         <v>2</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D60" t="s">
         <v>18</v>
@@ -2594,13 +2558,13 @@
         <v>28</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="s">
         <v>87</v>
       </c>
       <c r="I60" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2611,10 +2575,10 @@
         <v>2</v>
       </c>
       <c r="C61">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D61" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E61" t="s">
         <v>27</v>
@@ -2623,13 +2587,13 @@
         <v>28</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61" t="s">
         <v>88</v>
       </c>
       <c r="I61" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2640,10 +2604,10 @@
         <v>2</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E62" t="s">
         <v>27</v>
@@ -2652,187 +2616,13 @@
         <v>28</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62" t="s">
         <v>89</v>
       </c>
       <c r="I62" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
-      <c r="C63">
-        <v>5</v>
-      </c>
-      <c r="D63" t="s">
-        <v>10</v>
-      </c>
-      <c r="E63" t="s">
-        <v>27</v>
-      </c>
-      <c r="F63" t="s">
-        <v>28</v>
-      </c>
-      <c r="G63">
-        <v>0</v>
-      </c>
-      <c r="H63" t="s">
-        <v>90</v>
-      </c>
-      <c r="I63" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
-      </c>
-      <c r="C64">
-        <v>5</v>
-      </c>
-      <c r="D64" t="s">
-        <v>10</v>
-      </c>
-      <c r="E64" t="s">
-        <v>27</v>
-      </c>
-      <c r="F64" t="s">
-        <v>28</v>
-      </c>
-      <c r="G64">
-        <v>1</v>
-      </c>
-      <c r="H64" t="s">
-        <v>91</v>
-      </c>
-      <c r="I64" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
-      <c r="A65" t="s">
-        <v>9</v>
-      </c>
-      <c r="B65">
-        <v>2</v>
-      </c>
-      <c r="C65">
-        <v>3</v>
-      </c>
-      <c r="D65" t="s">
-        <v>12</v>
-      </c>
-      <c r="E65" t="s">
-        <v>27</v>
-      </c>
-      <c r="F65" t="s">
-        <v>28</v>
-      </c>
-      <c r="G65">
-        <v>1</v>
-      </c>
-      <c r="H65" t="s">
-        <v>92</v>
-      </c>
-      <c r="I65" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
-      <c r="A66" t="s">
-        <v>9</v>
-      </c>
-      <c r="B66">
-        <v>2</v>
-      </c>
-      <c r="C66">
-        <v>5</v>
-      </c>
-      <c r="D66" t="s">
-        <v>10</v>
-      </c>
-      <c r="E66" t="s">
-        <v>27</v>
-      </c>
-      <c r="F66" t="s">
-        <v>28</v>
-      </c>
-      <c r="G66">
-        <v>2</v>
-      </c>
-      <c r="H66" t="s">
-        <v>93</v>
-      </c>
-      <c r="I66" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
-      <c r="A67" t="s">
-        <v>9</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
-      </c>
-      <c r="C67">
-        <v>13</v>
-      </c>
-      <c r="D67" t="s">
-        <v>26</v>
-      </c>
-      <c r="E67" t="s">
-        <v>27</v>
-      </c>
-      <c r="F67" t="s">
-        <v>28</v>
-      </c>
-      <c r="G67">
-        <v>2</v>
-      </c>
-      <c r="H67" t="s">
-        <v>94</v>
-      </c>
-      <c r="I67" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
-      <c r="A68" t="s">
-        <v>9</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
-      <c r="C68">
-        <v>11</v>
-      </c>
-      <c r="D68" t="s">
-        <v>15</v>
-      </c>
-      <c r="E68" t="s">
-        <v>27</v>
-      </c>
-      <c r="F68" t="s">
-        <v>28</v>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68" t="s">
-        <v>95</v>
-      </c>
-      <c r="I68" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/DIR Stroke Position.xlsx
+++ b/Data/output/DIR Stroke Position.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="171">
   <si>
     <t>Direct_or_Indirect</t>
   </si>
@@ -46,427 +46,487 @@
     <t>Direct</t>
   </si>
   <si>
+    <t>1006.0</t>
+  </si>
+  <si>
+    <t>1009.0</t>
+  </si>
+  <si>
+    <t>1010.0</t>
+  </si>
+  <si>
+    <t>1015.0</t>
+  </si>
+  <si>
+    <t>1016.0</t>
+  </si>
+  <si>
+    <t>1014.0</t>
+  </si>
+  <si>
+    <t>1017.0</t>
+  </si>
+  <si>
+    <t>1004.0</t>
+  </si>
+  <si>
+    <t>1003.0</t>
+  </si>
+  <si>
+    <t>1007.0</t>
+  </si>
+  <si>
+    <t>1002.0</t>
+  </si>
+  <si>
+    <t>1011.0</t>
+  </si>
+  <si>
     <t>1013.0</t>
   </si>
   <si>
+    <t>1012.0</t>
+  </si>
+  <si>
     <t>1008.0</t>
   </si>
   <si>
-    <t>1014.0</t>
-  </si>
-  <si>
-    <t>1015.0</t>
-  </si>
-  <si>
-    <t>1016.0</t>
-  </si>
-  <si>
-    <t>1011.0</t>
-  </si>
-  <si>
-    <t>1017.0</t>
-  </si>
-  <si>
-    <t>1004.0</t>
-  </si>
-  <si>
-    <t>1010.0</t>
-  </si>
-  <si>
-    <t>1007.0</t>
-  </si>
-  <si>
-    <t>1002.0</t>
-  </si>
-  <si>
-    <t>1003.0</t>
+    <t>1001.0</t>
   </si>
   <si>
     <t>1005.0</t>
   </si>
   <si>
-    <t>1009.0</t>
-  </si>
-  <si>
-    <t>1012.0</t>
-  </si>
-  <si>
-    <t>1001.0</t>
-  </si>
-  <si>
-    <t>1006.0</t>
-  </si>
-  <si>
     <t>0.0</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>[np.float64(736.864941489601), np.float64(-23.459933625752)]</t>
-  </si>
-  <si>
-    <t>[np.float64(433.80953060443494), np.float64(-41.183859911030254)]</t>
-  </si>
-  <si>
-    <t>[np.float64(721.3154875579597), np.float64(-31.980641502339836)]</t>
-  </si>
-  <si>
-    <t>[np.float64(811.8124186294002), np.float64(-41.72594195300769)]</t>
-  </si>
-  <si>
-    <t>[np.float64(820.1635608302231), np.float64(-56.68205648449202)]</t>
-  </si>
-  <si>
-    <t>[np.float64(900.9325768686019), np.float64(-7.333511952245999)]</t>
-  </si>
-  <si>
-    <t>[np.float64(620.0288105096155), np.float64(-16.598211526448154)]</t>
-  </si>
-  <si>
-    <t>[np.float64(623.2259535298366), np.float64(-58.97509988310628)]</t>
-  </si>
-  <si>
-    <t>[np.float64(982.7380577882424), np.float64(-10.858647597939125)]</t>
-  </si>
-  <si>
-    <t>[np.float64(162.05563907935772), np.float64(-69.65763660008031)]</t>
-  </si>
-  <si>
-    <t>[np.float64(976.3971823296371), np.float64(-77.0522692894682)]</t>
-  </si>
-  <si>
-    <t>[np.float64(570.4203613518029), np.float64(-39.91313106366556)]</t>
-  </si>
-  <si>
-    <t>[np.float64(353.62518362069704), np.float64(-27.699101968806076)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.7701657566072), np.float64(-33.5029644667527)]</t>
-  </si>
-  <si>
-    <t>[np.float64(786.3395522722296), np.float64(-74.53171280564175)]</t>
-  </si>
-  <si>
-    <t>[np.float64(354.62686667034274), np.float64(-46.45634425014248)]</t>
-  </si>
-  <si>
-    <t>[np.float64(905.6535786277253), np.float64(-45.577125053637246)]</t>
-  </si>
-  <si>
-    <t>[np.float64(747.4932420161771), np.float64(-9.747233383561593)]</t>
-  </si>
-  <si>
-    <t>[np.float64(57.88797961583481), np.float64(-33.68400617047348)]</t>
-  </si>
-  <si>
-    <t>[np.float64(430.67235501854316), np.float64(-5.211151016687268)]</t>
-  </si>
-  <si>
-    <t>[np.float64(123.26482231534585), np.float64(-5.399359883844795)]</t>
-  </si>
-  <si>
-    <t>[np.float64(139.7143991073193), np.float64(-49.4027326371795)]</t>
-  </si>
-  <si>
-    <t>[np.float64(859.3321330637649), np.float64(-13.220859307199134)]</t>
-  </si>
-  <si>
-    <t>[np.float64(223.13305618651646), np.float64(-24.77141480516684)]</t>
-  </si>
-  <si>
-    <t>[np.float64(500.18315201707696), np.float64(-89.92887358557749)]</t>
-  </si>
-  <si>
-    <t>[np.float64(834.1094922128001), np.float64(-41.694854513005225)]</t>
-  </si>
-  <si>
-    <t>[np.float64(667.9412688011267), np.float64(-39.90715488673311)]</t>
-  </si>
-  <si>
-    <t>[np.float64(103.01970808235583), np.float64(-71.97603240249339)]</t>
-  </si>
-  <si>
-    <t>[np.float64(400.9560004253943), np.float64(-4.500144181129826)]</t>
-  </si>
-  <si>
-    <t>[np.float64(2.4031417705256963), np.float64(-14.546923054125159)]</t>
-  </si>
-  <si>
-    <t>[np.float64(499.4687735212923), np.float64(-83.37678223695775)]</t>
-  </si>
-  <si>
-    <t>[np.float64(325.0003886349967), np.float64(-5.52106448347547)]</t>
-  </si>
-  <si>
-    <t>[np.float64(833.1349332932796), np.float64(-63.854839411081684)]</t>
-  </si>
-  <si>
-    <t>[np.float64(497.64054452854924), np.float64(-83.63775670309292)]</t>
-  </si>
-  <si>
-    <t>[np.float64(14.763121206316065), np.float64(-46.639917018454526)]</t>
-  </si>
-  <si>
-    <t>[np.float64(859.5378356386898), np.float64(-2.8716986032735576)]</t>
-  </si>
-  <si>
-    <t>[np.float64(972.0760605582678), np.float64(-54.90338935387649)]</t>
-  </si>
-  <si>
-    <t>[np.float64(794.9570421646395), np.float64(-34.657824840789544)]</t>
-  </si>
-  <si>
-    <t>[np.float64(964.3303594495613), np.float64(-20.699746479376245)]</t>
-  </si>
-  <si>
-    <t>[np.float64(144.2048124302978), np.float64(-29.57745301221871)]</t>
-  </si>
-  <si>
-    <t>[np.float64(178.66835135721283), np.float64(-25.768941052179912)]</t>
-  </si>
-  <si>
-    <t>[np.float64(874.0060269906589), np.float64(-38.57362718882348)]</t>
-  </si>
-  <si>
-    <t>[np.float64(783.4932261968663), np.float64(-106.28786672668838)]</t>
-  </si>
-  <si>
-    <t>[np.float64(742.5381671551078), np.float64(-24.338046909968057)]</t>
-  </si>
-  <si>
-    <t>[np.float64(595.4516410544009), np.float64(-44.66042430220682)]</t>
-  </si>
-  <si>
-    <t>[np.float64(573.9981213204974), np.float64(-10.627129148001586)]</t>
-  </si>
-  <si>
-    <t>[np.float64(615.0656398203273), np.float64(-20.086481242965874)]</t>
-  </si>
-  <si>
-    <t>[np.float64(888.0420178215439), np.float64(-20.564276636114528)]</t>
-  </si>
-  <si>
-    <t>[np.float64(688.4191865508111), np.float64(-6.373162720602295)]</t>
-  </si>
-  <si>
-    <t>[np.float64(211.52498376490092), np.float64(-22.10937271547789)]</t>
-  </si>
-  <si>
-    <t>[np.float64(205.16035376916898), np.float64(-19.414352995102035)]</t>
-  </si>
-  <si>
-    <t>[np.float64(377.208002721977), np.float64(-47.091939151830616)]</t>
-  </si>
-  <si>
-    <t>[np.float64(692.2187629553888), np.float64(-51.02097134462292)]</t>
-  </si>
-  <si>
-    <t>[np.float64(393.1493963793832), np.float64(-66.78958345449837)]</t>
-  </si>
-  <si>
-    <t>[np.float64(148.1505615779981), np.float64(-23.448459099112483)]</t>
-  </si>
-  <si>
-    <t>[np.float64(514.2681836084121), np.float64(-57.86500664155665)]</t>
-  </si>
-  <si>
-    <t>[np.float64(735.8520577115462), np.float64(-90.32256844245438)]</t>
-  </si>
-  <si>
-    <t>[np.float64(611.830587918147), np.float64(-31.948575870406785)]</t>
-  </si>
-  <si>
-    <t>[np.float64(541.0520910436898), np.float64(-20.12501610370896)]</t>
-  </si>
-  <si>
-    <t>[np.float64(268.6109457607336), np.float64(-36.081593792960916)]</t>
-  </si>
-  <si>
-    <t>[np.float64(450.84587393826223), np.float64(-55.9431475510396)]</t>
-  </si>
-  <si>
-    <t>[np.float64(736.864941489601), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(433.80953060443494), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(721.3154875579597), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(811.8124186294002), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(820.1635608302231), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(900.9325768686019), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(620.0288105096155), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(623.2259535298366), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(982.7380577882424), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(162.05563907935772), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(976.3971823296371), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(570.4203613518029), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(353.62518362069704), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.7701657566072), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(786.3395522722296), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(354.62686667034274), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(905.6535786277253), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(747.4932420161771), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(57.88797961583481), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(430.67235501854316), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(123.26482231534585), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(139.7143991073193), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(859.3321330637649), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(223.13305618651646), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(500.18315201707696), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(834.1094922128001), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(667.9412688011267), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(103.01970808235583), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(400.9560004253943), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(2.4031417705256963), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(499.4687735212923), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(325.0003886349967), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(833.1349332932796), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(497.64054452854924), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(14.763121206316065), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(859.5378356386898), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(972.0760605582678), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(794.9570421646395), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(964.3303594495613), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(144.2048124302978), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(178.66835135721283), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(874.0060269906589), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(783.4932261968663), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(742.5381671551078), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(595.4516410544009), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(573.9981213204974), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(615.0656398203273), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(888.0420178215439), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(688.4191865508111), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(211.52498376490092), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(205.16035376916898), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(377.208002721977), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(692.2187629553888), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(393.1493963793832), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(148.1505615779981), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(514.2681836084121), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(735.8520577115462), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(611.830587918147), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(541.0520910436898), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(268.6109457607336), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(450.84587393826223), np.float64(0.0)]</t>
+    <t>[np.float64(309.07792657045565), np.float64(-19.980874914081028)]</t>
+  </si>
+  <si>
+    <t>[np.float64(467.2134461320424), np.float64(-58.211043640662524)]</t>
+  </si>
+  <si>
+    <t>[np.float64(544.2373016278519), np.float64(-39.2473250414082)]</t>
+  </si>
+  <si>
+    <t>[np.float64(499.7015975978243), np.float64(-34.45364004949192)]</t>
+  </si>
+  <si>
+    <t>[np.float64(832.8129768102044), np.float64(-14.754545134642285)]</t>
+  </si>
+  <si>
+    <t>[np.float64(910.6620944880085), np.float64(-8.916355259011198)]</t>
+  </si>
+  <si>
+    <t>[np.float64(781.5501525827768), np.float64(-62.71486244876269)]</t>
+  </si>
+  <si>
+    <t>[np.float64(947.1449473255919), np.float64(-81.10412013845178)]</t>
+  </si>
+  <si>
+    <t>[np.float64(174.2738604561519), np.float64(-31.15418484401573)]</t>
+  </si>
+  <si>
+    <t>[np.float64(512.1460983817421), np.float64(-24.45498323323261)]</t>
+  </si>
+  <si>
+    <t>[np.float64(133.5228554717268), np.float64(-40.800813088918744)]</t>
+  </si>
+  <si>
+    <t>[np.float64(806.0827033823335), np.float64(-7.708818420504144)]</t>
+  </si>
+  <si>
+    <t>[np.float64(373.1191762822642), np.float64(-69.84060290989441)]</t>
+  </si>
+  <si>
+    <t>[np.float64(83.55910418932244), np.float64(-68.93929132641404)]</t>
+  </si>
+  <si>
+    <t>[np.float64(821.391156499109), np.float64(-11.01222739908917)]</t>
+  </si>
+  <si>
+    <t>[np.float64(614.3008628509622), np.float64(-72.57659705813728)]</t>
+  </si>
+  <si>
+    <t>[np.float64(550.4766263352727), np.float64(-54.676935854252065)]</t>
+  </si>
+  <si>
+    <t>[np.float64(146.48117776003156), np.float64(-71.11663424418998)]</t>
+  </si>
+  <si>
+    <t>[np.float64(151.91438805955605), np.float64(-44.8919973841945)]</t>
+  </si>
+  <si>
+    <t>[np.float64(884.6591539083929), np.float64(-12.20608398294928)]</t>
+  </si>
+  <si>
+    <t>[np.float64(167.37641387361924), np.float64(-46.34145468142276)]</t>
+  </si>
+  <si>
+    <t>[np.float64(527.7962224036208), np.float64(-117.6965675074776)]</t>
+  </si>
+  <si>
+    <t>[np.float64(470.0764498824211), np.float64(-81.8587951708497)]</t>
+  </si>
+  <si>
+    <t>[np.float64(68.42759695717471), np.float64(-5.9840809325996815)]</t>
+  </si>
+  <si>
+    <t>[np.float64(713.0236483111931), np.float64(-29.90283111100962)]</t>
+  </si>
+  <si>
+    <t>[np.float64(501.4141731493591), np.float64(-23.317593792115076)]</t>
+  </si>
+  <si>
+    <t>[np.float64(554.3734961789373), np.float64(-22.00591202014141)]</t>
+  </si>
+  <si>
+    <t>[np.float64(513.2872096191246), np.float64(-4.243257125701916)]</t>
+  </si>
+  <si>
+    <t>[np.float64(707.5779928397983), np.float64(-66.3046274217545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(802.0294223684026), np.float64(-19.869895625765707)]</t>
+  </si>
+  <si>
+    <t>[np.float64(387.5915283514927), np.float64(-68.14259665757709)]</t>
+  </si>
+  <si>
+    <t>[np.float64(491.47471311471793), np.float64(-3.24603432692993)]</t>
+  </si>
+  <si>
+    <t>[np.float64(980.9536194267416), np.float64(-19.751000734120908)]</t>
+  </si>
+  <si>
+    <t>[np.float64(147.44271915579776), np.float64(-5.799415953770563)]</t>
+  </si>
+  <si>
+    <t>[np.float64(345.2525525256166), np.float64(-50.23746671541505)]</t>
+  </si>
+  <si>
+    <t>[np.float64(128.89423288713175), np.float64(-4.411330898339884)]</t>
+  </si>
+  <si>
+    <t>[np.float64(754.9306496156581), np.float64(-28.031209767393648)]</t>
+  </si>
+  <si>
+    <t>[np.float64(666.785139287678), np.float64(-40.6091633648831)]</t>
+  </si>
+  <si>
+    <t>[np.float64(143.02988453272468), np.float64(-78.21884491280298)]</t>
+  </si>
+  <si>
+    <t>[np.float64(875.2089984637561), np.float64(-43.22791400348444)]</t>
+  </si>
+  <si>
+    <t>[np.float64(429.89647105010164), np.float64(-68.86941684224905)]</t>
+  </si>
+  <si>
+    <t>[np.float64(510.7467837494648), np.float64(-61.07779398565742)]</t>
+  </si>
+  <si>
+    <t>[np.float64(466.2601077893962), np.float64(-12.006452918763102)]</t>
+  </si>
+  <si>
+    <t>[np.float64(896.239937176825), np.float64(-100.17753689404844)]</t>
+  </si>
+  <si>
+    <t>[np.float64(133.86816695213122), np.float64(-50.287668940173376)]</t>
+  </si>
+  <si>
+    <t>[np.float64(800.6848565574288), np.float64(-89.90426334076756)]</t>
+  </si>
+  <si>
+    <t>[np.float64(538.4101999868036), np.float64(-0.2641324633360682)]</t>
+  </si>
+  <si>
+    <t>[np.float64(471.1315686490597), np.float64(-97.84504839489279)]</t>
+  </si>
+  <si>
+    <t>[np.float64(189.13299068015522), np.float64(-17.33483689494608)]</t>
+  </si>
+  <si>
+    <t>[np.float64(348.1636088676187), np.float64(-69.4549427261478)]</t>
+  </si>
+  <si>
+    <t>[np.float64(858.9805263499992), np.float64(-63.402135727277596)]</t>
+  </si>
+  <si>
+    <t>[np.float64(24.42865535692629), np.float64(-33.833809086513725)]</t>
+  </si>
+  <si>
+    <t>[np.float64(270.0603020061123), np.float64(-37.6748905641731)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.2896514724931603), np.float64(-28.645207879792906)]</t>
+  </si>
+  <si>
+    <t>[np.float64(85.04452184792343), np.float64(-7.859798606545382)]</t>
+  </si>
+  <si>
+    <t>[np.float64(511.99171540345776), np.float64(-67.20213399405077)]</t>
+  </si>
+  <si>
+    <t>[np.float64(274.3871479539144), np.float64(-26.37579469243576)]</t>
+  </si>
+  <si>
+    <t>[np.float64(476.243197546716), np.float64(-27.668164515952753)]</t>
+  </si>
+  <si>
+    <t>[np.float64(372.27575658718837), np.float64(-8.923579081905814)]</t>
+  </si>
+  <si>
+    <t>[np.float64(213.06099580998915), np.float64(-58.878423435315085)]</t>
+  </si>
+  <si>
+    <t>[np.float64(245.41806500849762), np.float64(-53.66809300145917)]</t>
+  </si>
+  <si>
+    <t>[np.float64(435.30722428107174), np.float64(-19.55097914387011)]</t>
+  </si>
+  <si>
+    <t>[np.float64(249.67324304343063), np.float64(-40.36057476880205)]</t>
+  </si>
+  <si>
+    <t>[np.float64(479.2141914670593), np.float64(-51.96073837672577)]</t>
+  </si>
+  <si>
+    <t>[np.float64(29.916895541495347), np.float64(-25.86389714047573)]</t>
+  </si>
+  <si>
+    <t>[np.float64(912.048718153437), np.float64(-44.24370026803558)]</t>
+  </si>
+  <si>
+    <t>[np.float64(54.22602847740543), np.float64(-11.96276471375586)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.7319118281209365), np.float64(-75.331224230869)]</t>
+  </si>
+  <si>
+    <t>[np.float64(13.405757534372565), np.float64(-52.44495308885985)]</t>
+  </si>
+  <si>
+    <t>[np.float64(763.1763577701931), np.float64(-47.241535244172155)]</t>
+  </si>
+  <si>
+    <t>[np.float64(974.6562422443867), np.float64(-40.93645053245609)]</t>
+  </si>
+  <si>
+    <t>[np.float64(309.07792657045565), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(467.2134461320424), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(544.2373016278519), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(499.7015975978243), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(832.8129768102044), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(910.6620944880085), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(781.5501525827768), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(947.1449473255919), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(174.2738604561519), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(512.1460983817421), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(133.5228554717268), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(806.0827033823335), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(373.1191762822642), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(83.55910418932244), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(821.391156499109), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(614.3008628509622), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(550.4766263352727), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(146.48117776003156), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(151.91438805955605), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(884.6591539083929), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(167.37641387361924), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(527.7962224036208), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(470.0764498824211), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(68.42759695717471), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(713.0236483111931), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(501.4141731493591), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(554.3734961789373), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(513.2872096191246), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(707.5779928397983), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(802.0294223684026), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(387.5915283514927), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(491.47471311471793), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(980.9536194267416), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(147.44271915579776), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(345.2525525256166), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(128.89423288713175), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(754.9306496156581), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(666.785139287678), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(143.02988453272468), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(875.2089984637561), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(429.89647105010164), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(510.7467837494648), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(466.2601077893962), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(896.239937176825), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(133.86816695213122), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(800.6848565574288), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(538.4101999868036), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(471.1315686490597), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(189.13299068015522), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(348.1636088676187), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(858.9805263499992), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(24.42865535692629), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(270.0603020061123), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(3.2896514724931607), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(85.04452184792343), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(511.99171540345776), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(274.3871479539144), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(476.243197546716), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(372.27575658718837), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(213.06099580998915), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(245.41806500849762), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(435.30722428107174), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(249.67324304343063), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(479.2141914670593), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(29.916895541495347), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(912.048718153437), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(54.22602847740543), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(2.7319118281209365), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(13.405757534372567), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(763.1763577701931), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(974.6562422443867), np.float64(0.0)]</t>
   </si>
 </sst>
 </file>
@@ -824,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -864,7 +924,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -882,7 +942,7 @@
         <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -893,7 +953,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -905,13 +965,13 @@
         <v>28</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="s">
         <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -922,10 +982,10 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
@@ -940,7 +1000,7 @@
         <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -951,10 +1011,10 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
@@ -963,13 +1023,13 @@
         <v>28</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="s">
         <v>32</v>
       </c>
       <c r="I5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -998,7 +1058,7 @@
         <v>33</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1027,7 +1087,7 @@
         <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1038,7 +1098,7 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
@@ -1050,13 +1110,13 @@
         <v>28</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="s">
         <v>35</v>
       </c>
       <c r="I8" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1067,10 +1127,10 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
@@ -1079,13 +1139,13 @@
         <v>28</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H9" t="s">
         <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1096,11 +1156,11 @@
         <v>2</v>
       </c>
       <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
         <v>17</v>
       </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
       <c r="E10" t="s">
         <v>27</v>
       </c>
@@ -1108,13 +1168,13 @@
         <v>28</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="s">
         <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1125,10 +1185,10 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E11" t="s">
         <v>27</v>
@@ -1137,13 +1197,13 @@
         <v>28</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="s">
         <v>38</v>
       </c>
       <c r="I11" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1154,10 +1214,10 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E12" t="s">
         <v>27</v>
@@ -1172,7 +1232,7 @@
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1183,10 +1243,10 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -1201,7 +1261,7 @@
         <v>40</v>
       </c>
       <c r="I13" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1224,13 +1284,13 @@
         <v>28</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="s">
         <v>41</v>
       </c>
       <c r="I14" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1241,10 +1301,10 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E15" t="s">
         <v>27</v>
@@ -1259,7 +1319,7 @@
         <v>42</v>
       </c>
       <c r="I15" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1270,10 +1330,10 @@
         <v>2</v>
       </c>
       <c r="C16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
         <v>27</v>
@@ -1282,13 +1342,13 @@
         <v>28</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="s">
         <v>43</v>
       </c>
       <c r="I16" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1299,10 +1359,10 @@
         <v>2</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
@@ -1311,13 +1371,13 @@
         <v>28</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>44</v>
       </c>
       <c r="I17" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1328,10 +1388,10 @@
         <v>2</v>
       </c>
       <c r="C18">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -1346,7 +1406,7 @@
         <v>45</v>
       </c>
       <c r="I18" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1357,10 +1417,10 @@
         <v>2</v>
       </c>
       <c r="C19">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -1375,7 +1435,7 @@
         <v>46</v>
       </c>
       <c r="I19" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1386,10 +1446,10 @@
         <v>2</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E20" t="s">
         <v>27</v>
@@ -1398,13 +1458,13 @@
         <v>28</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="s">
         <v>47</v>
       </c>
       <c r="I20" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1415,10 +1475,10 @@
         <v>2</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -1427,13 +1487,13 @@
         <v>28</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="s">
         <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1444,10 +1504,10 @@
         <v>2</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E22" t="s">
         <v>27</v>
@@ -1456,13 +1516,13 @@
         <v>28</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="s">
         <v>49</v>
       </c>
       <c r="I22" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1473,10 +1533,10 @@
         <v>2</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E23" t="s">
         <v>27</v>
@@ -1485,13 +1545,13 @@
         <v>28</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="s">
         <v>50</v>
       </c>
       <c r="I23" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1502,10 +1562,10 @@
         <v>2</v>
       </c>
       <c r="C24">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E24" t="s">
         <v>27</v>
@@ -1514,13 +1574,13 @@
         <v>28</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="s">
         <v>51</v>
       </c>
       <c r="I24" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1531,10 +1591,10 @@
         <v>2</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>
@@ -1543,13 +1603,13 @@
         <v>28</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="s">
         <v>52</v>
       </c>
       <c r="I25" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1560,10 +1620,10 @@
         <v>2</v>
       </c>
       <c r="C26">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
@@ -1572,13 +1632,13 @@
         <v>28</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="s">
         <v>53</v>
       </c>
       <c r="I26" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1589,10 +1649,10 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
@@ -1601,13 +1661,13 @@
         <v>28</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="s">
         <v>54</v>
       </c>
       <c r="I27" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1618,10 +1678,10 @@
         <v>2</v>
       </c>
       <c r="C28">
+        <v>10</v>
+      </c>
+      <c r="D28" t="s">
         <v>12</v>
-      </c>
-      <c r="D28" t="s">
-        <v>24</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -1636,7 +1696,7 @@
         <v>55</v>
       </c>
       <c r="I28" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1647,10 +1707,10 @@
         <v>2</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -1659,13 +1719,13 @@
         <v>28</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="s">
         <v>56</v>
       </c>
       <c r="I29" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1676,10 +1736,10 @@
         <v>2</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E30" t="s">
         <v>27</v>
@@ -1694,7 +1754,7 @@
         <v>57</v>
       </c>
       <c r="I30" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1705,10 +1765,10 @@
         <v>2</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
@@ -1717,13 +1777,13 @@
         <v>28</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="s">
         <v>58</v>
       </c>
       <c r="I31" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1734,10 +1794,10 @@
         <v>2</v>
       </c>
       <c r="C32">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s">
         <v>27</v>
@@ -1746,13 +1806,13 @@
         <v>28</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" t="s">
         <v>59</v>
       </c>
       <c r="I32" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1763,10 +1823,10 @@
         <v>2</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="E33" t="s">
         <v>27</v>
@@ -1775,13 +1835,13 @@
         <v>28</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" t="s">
         <v>60</v>
       </c>
       <c r="I33" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1792,10 +1852,10 @@
         <v>2</v>
       </c>
       <c r="C34">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D34" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -1804,13 +1864,13 @@
         <v>28</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="s">
         <v>61</v>
       </c>
       <c r="I34" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1821,10 +1881,10 @@
         <v>2</v>
       </c>
       <c r="C35">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E35" t="s">
         <v>27</v>
@@ -1833,13 +1893,13 @@
         <v>28</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="s">
         <v>62</v>
       </c>
       <c r="I35" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1850,10 +1910,10 @@
         <v>2</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D36" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -1868,7 +1928,7 @@
         <v>63</v>
       </c>
       <c r="I36" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1879,10 +1939,10 @@
         <v>2</v>
       </c>
       <c r="C37">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E37" t="s">
         <v>27</v>
@@ -1897,7 +1957,7 @@
         <v>64</v>
       </c>
       <c r="I37" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1908,10 +1968,10 @@
         <v>2</v>
       </c>
       <c r="C38">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E38" t="s">
         <v>27</v>
@@ -1920,13 +1980,13 @@
         <v>28</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" t="s">
         <v>65</v>
       </c>
       <c r="I38" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1937,10 +1997,10 @@
         <v>2</v>
       </c>
       <c r="C39">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E39" t="s">
         <v>27</v>
@@ -1955,7 +2015,7 @@
         <v>66</v>
       </c>
       <c r="I39" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1966,10 +2026,10 @@
         <v>2</v>
       </c>
       <c r="C40">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E40" t="s">
         <v>27</v>
@@ -1978,13 +2038,13 @@
         <v>28</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" t="s">
         <v>67</v>
       </c>
       <c r="I40" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1995,10 +2055,10 @@
         <v>2</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E41" t="s">
         <v>27</v>
@@ -2013,7 +2073,7 @@
         <v>68</v>
       </c>
       <c r="I41" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2024,10 +2084,10 @@
         <v>2</v>
       </c>
       <c r="C42">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D42" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E42" t="s">
         <v>27</v>
@@ -2036,13 +2096,13 @@
         <v>28</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="s">
         <v>69</v>
       </c>
       <c r="I42" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2053,10 +2113,10 @@
         <v>2</v>
       </c>
       <c r="C43">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D43" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -2071,7 +2131,7 @@
         <v>70</v>
       </c>
       <c r="I43" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2082,10 +2142,10 @@
         <v>2</v>
       </c>
       <c r="C44">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -2094,13 +2154,13 @@
         <v>28</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="s">
         <v>71</v>
       </c>
       <c r="I44" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2111,10 +2171,10 @@
         <v>2</v>
       </c>
       <c r="C45">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D45" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2123,13 +2183,13 @@
         <v>28</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H45" t="s">
         <v>72</v>
       </c>
       <c r="I45" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2140,10 +2200,10 @@
         <v>2</v>
       </c>
       <c r="C46">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -2152,13 +2212,13 @@
         <v>28</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="s">
         <v>73</v>
       </c>
       <c r="I46" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2169,10 +2229,10 @@
         <v>2</v>
       </c>
       <c r="C47">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2187,7 +2247,7 @@
         <v>74</v>
       </c>
       <c r="I47" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2198,10 +2258,10 @@
         <v>2</v>
       </c>
       <c r="C48">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2210,13 +2270,13 @@
         <v>28</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48" t="s">
         <v>75</v>
       </c>
       <c r="I48" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2227,10 +2287,10 @@
         <v>2</v>
       </c>
       <c r="C49">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E49" t="s">
         <v>27</v>
@@ -2245,7 +2305,7 @@
         <v>76</v>
       </c>
       <c r="I49" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2256,10 +2316,10 @@
         <v>2</v>
       </c>
       <c r="C50">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E50" t="s">
         <v>27</v>
@@ -2268,13 +2328,13 @@
         <v>28</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" t="s">
         <v>77</v>
       </c>
       <c r="I50" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2285,10 +2345,10 @@
         <v>2</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E51" t="s">
         <v>27</v>
@@ -2297,13 +2357,13 @@
         <v>28</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H51" t="s">
         <v>78</v>
       </c>
       <c r="I51" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -2314,10 +2374,10 @@
         <v>2</v>
       </c>
       <c r="C52">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="D52" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E52" t="s">
         <v>27</v>
@@ -2326,13 +2386,13 @@
         <v>28</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52" t="s">
         <v>79</v>
       </c>
       <c r="I52" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -2343,10 +2403,10 @@
         <v>2</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D53" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E53" t="s">
         <v>27</v>
@@ -2361,7 +2421,7 @@
         <v>80</v>
       </c>
       <c r="I53" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -2372,10 +2432,10 @@
         <v>2</v>
       </c>
       <c r="C54">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D54" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E54" t="s">
         <v>27</v>
@@ -2390,7 +2450,7 @@
         <v>81</v>
       </c>
       <c r="I54" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -2401,10 +2461,10 @@
         <v>2</v>
       </c>
       <c r="C55">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D55" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E55" t="s">
         <v>27</v>
@@ -2413,13 +2473,13 @@
         <v>28</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H55" t="s">
         <v>82</v>
       </c>
       <c r="I55" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -2430,10 +2490,10 @@
         <v>2</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D56" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E56" t="s">
         <v>27</v>
@@ -2448,7 +2508,7 @@
         <v>83</v>
       </c>
       <c r="I56" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -2462,7 +2522,7 @@
         <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E57" t="s">
         <v>27</v>
@@ -2477,7 +2537,7 @@
         <v>84</v>
       </c>
       <c r="I57" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -2488,10 +2548,10 @@
         <v>2</v>
       </c>
       <c r="C58">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D58" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E58" t="s">
         <v>27</v>
@@ -2500,13 +2560,13 @@
         <v>28</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58" t="s">
         <v>85</v>
       </c>
       <c r="I58" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -2517,11 +2577,11 @@
         <v>2</v>
       </c>
       <c r="C59">
+        <v>9</v>
+      </c>
+      <c r="D59" t="s">
         <v>11</v>
       </c>
-      <c r="D59" t="s">
-        <v>15</v>
-      </c>
       <c r="E59" t="s">
         <v>27</v>
       </c>
@@ -2529,13 +2589,13 @@
         <v>28</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="s">
         <v>86</v>
       </c>
       <c r="I59" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -2546,10 +2606,10 @@
         <v>2</v>
       </c>
       <c r="C60">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D60" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E60" t="s">
         <v>27</v>
@@ -2564,7 +2624,7 @@
         <v>87</v>
       </c>
       <c r="I60" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -2575,10 +2635,10 @@
         <v>2</v>
       </c>
       <c r="C61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D61" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E61" t="s">
         <v>27</v>
@@ -2593,7 +2653,7 @@
         <v>88</v>
       </c>
       <c r="I61" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2604,10 +2664,10 @@
         <v>2</v>
       </c>
       <c r="C62">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D62" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E62" t="s">
         <v>27</v>
@@ -2616,13 +2676,303 @@
         <v>28</v>
       </c>
       <c r="G62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62" t="s">
         <v>89</v>
       </c>
       <c r="I62" t="s">
-        <v>150</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63">
+        <v>8</v>
+      </c>
+      <c r="D63" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" t="s">
+        <v>28</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63" t="s">
+        <v>90</v>
+      </c>
+      <c r="I63" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64">
+        <v>5</v>
+      </c>
+      <c r="D64" t="s">
+        <v>26</v>
+      </c>
+      <c r="E64" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64" t="s">
+        <v>28</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
+        <v>91</v>
+      </c>
+      <c r="I64" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65">
+        <v>2</v>
+      </c>
+      <c r="C65">
+        <v>9</v>
+      </c>
+      <c r="D65" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" t="s">
+        <v>28</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65" t="s">
+        <v>92</v>
+      </c>
+      <c r="I65" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
+        <v>9</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+      <c r="D66" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66" t="s">
+        <v>28</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66" t="s">
+        <v>93</v>
+      </c>
+      <c r="I66" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="C67">
+        <v>16</v>
+      </c>
+      <c r="D67" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" t="s">
+        <v>27</v>
+      </c>
+      <c r="F67" t="s">
+        <v>28</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
+        <v>94</v>
+      </c>
+      <c r="I67" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>9</v>
+      </c>
+      <c r="B68">
+        <v>2</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+      <c r="D68" t="s">
+        <v>20</v>
+      </c>
+      <c r="E68" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" t="s">
+        <v>28</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68" t="s">
+        <v>95</v>
+      </c>
+      <c r="I68" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+      <c r="D69" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" t="s">
+        <v>28</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69" t="s">
+        <v>96</v>
+      </c>
+      <c r="I69" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" t="s">
+        <v>28</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70" t="s">
+        <v>97</v>
+      </c>
+      <c r="I70" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>9</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
+      <c r="C71">
+        <v>14</v>
+      </c>
+      <c r="D71" t="s">
+        <v>15</v>
+      </c>
+      <c r="E71" t="s">
+        <v>27</v>
+      </c>
+      <c r="F71" t="s">
+        <v>28</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71" t="s">
+        <v>98</v>
+      </c>
+      <c r="I71" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
+      </c>
+      <c r="C72">
+        <v>17</v>
+      </c>
+      <c r="D72" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" t="s">
+        <v>27</v>
+      </c>
+      <c r="F72" t="s">
+        <v>28</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72" t="s">
+        <v>99</v>
+      </c>
+      <c r="I72" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/DIR Stroke Position.xlsx
+++ b/Data/output/DIR Stroke Position.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="129">
   <si>
     <t>Direct_or_Indirect</t>
   </si>
@@ -46,487 +46,361 @@
     <t>Direct</t>
   </si>
   <si>
+    <t>1008.0</t>
+  </si>
+  <si>
+    <t>1003.0</t>
+  </si>
+  <si>
+    <t>1007.0</t>
+  </si>
+  <si>
+    <t>1012.0</t>
+  </si>
+  <si>
+    <t>1015.0</t>
+  </si>
+  <si>
+    <t>1016.0</t>
+  </si>
+  <si>
+    <t>1001.0</t>
+  </si>
+  <si>
+    <t>1013.0</t>
+  </si>
+  <si>
+    <t>1002.0</t>
+  </si>
+  <si>
+    <t>1005.0</t>
+  </si>
+  <si>
+    <t>1011.0</t>
+  </si>
+  <si>
+    <t>1009.0</t>
+  </si>
+  <si>
+    <t>1004.0</t>
+  </si>
+  <si>
+    <t>1014.0</t>
+  </si>
+  <si>
     <t>1006.0</t>
   </si>
   <si>
-    <t>1009.0</t>
-  </si>
-  <si>
     <t>1010.0</t>
   </si>
   <si>
-    <t>1015.0</t>
-  </si>
-  <si>
-    <t>1016.0</t>
-  </si>
-  <si>
-    <t>1014.0</t>
-  </si>
-  <si>
     <t>1017.0</t>
   </si>
   <si>
-    <t>1004.0</t>
-  </si>
-  <si>
-    <t>1003.0</t>
-  </si>
-  <si>
-    <t>1007.0</t>
-  </si>
-  <si>
-    <t>1002.0</t>
-  </si>
-  <si>
-    <t>1011.0</t>
-  </si>
-  <si>
-    <t>1013.0</t>
-  </si>
-  <si>
-    <t>1012.0</t>
-  </si>
-  <si>
-    <t>1008.0</t>
-  </si>
-  <si>
-    <t>1001.0</t>
-  </si>
-  <si>
-    <t>1005.0</t>
-  </si>
-  <si>
     <t>0.0</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>[np.float64(309.07792657045565), np.float64(-19.980874914081028)]</t>
-  </si>
-  <si>
-    <t>[np.float64(467.2134461320424), np.float64(-58.211043640662524)]</t>
-  </si>
-  <si>
-    <t>[np.float64(544.2373016278519), np.float64(-39.2473250414082)]</t>
-  </si>
-  <si>
-    <t>[np.float64(499.7015975978243), np.float64(-34.45364004949192)]</t>
-  </si>
-  <si>
-    <t>[np.float64(832.8129768102044), np.float64(-14.754545134642285)]</t>
-  </si>
-  <si>
-    <t>[np.float64(910.6620944880085), np.float64(-8.916355259011198)]</t>
-  </si>
-  <si>
-    <t>[np.float64(781.5501525827768), np.float64(-62.71486244876269)]</t>
-  </si>
-  <si>
-    <t>[np.float64(947.1449473255919), np.float64(-81.10412013845178)]</t>
-  </si>
-  <si>
-    <t>[np.float64(174.2738604561519), np.float64(-31.15418484401573)]</t>
-  </si>
-  <si>
-    <t>[np.float64(512.1460983817421), np.float64(-24.45498323323261)]</t>
-  </si>
-  <si>
-    <t>[np.float64(133.5228554717268), np.float64(-40.800813088918744)]</t>
-  </si>
-  <si>
-    <t>[np.float64(806.0827033823335), np.float64(-7.708818420504144)]</t>
-  </si>
-  <si>
-    <t>[np.float64(373.1191762822642), np.float64(-69.84060290989441)]</t>
-  </si>
-  <si>
-    <t>[np.float64(83.55910418932244), np.float64(-68.93929132641404)]</t>
-  </si>
-  <si>
-    <t>[np.float64(821.391156499109), np.float64(-11.01222739908917)]</t>
-  </si>
-  <si>
-    <t>[np.float64(614.3008628509622), np.float64(-72.57659705813728)]</t>
-  </si>
-  <si>
-    <t>[np.float64(550.4766263352727), np.float64(-54.676935854252065)]</t>
-  </si>
-  <si>
-    <t>[np.float64(146.48117776003156), np.float64(-71.11663424418998)]</t>
-  </si>
-  <si>
-    <t>[np.float64(151.91438805955605), np.float64(-44.8919973841945)]</t>
-  </si>
-  <si>
-    <t>[np.float64(884.6591539083929), np.float64(-12.20608398294928)]</t>
-  </si>
-  <si>
-    <t>[np.float64(167.37641387361924), np.float64(-46.34145468142276)]</t>
-  </si>
-  <si>
-    <t>[np.float64(527.7962224036208), np.float64(-117.6965675074776)]</t>
-  </si>
-  <si>
-    <t>[np.float64(470.0764498824211), np.float64(-81.8587951708497)]</t>
-  </si>
-  <si>
-    <t>[np.float64(68.42759695717471), np.float64(-5.9840809325996815)]</t>
-  </si>
-  <si>
-    <t>[np.float64(713.0236483111931), np.float64(-29.90283111100962)]</t>
-  </si>
-  <si>
-    <t>[np.float64(501.4141731493591), np.float64(-23.317593792115076)]</t>
-  </si>
-  <si>
-    <t>[np.float64(554.3734961789373), np.float64(-22.00591202014141)]</t>
-  </si>
-  <si>
-    <t>[np.float64(513.2872096191246), np.float64(-4.243257125701916)]</t>
-  </si>
-  <si>
-    <t>[np.float64(707.5779928397983), np.float64(-66.3046274217545)]</t>
-  </si>
-  <si>
-    <t>[np.float64(802.0294223684026), np.float64(-19.869895625765707)]</t>
-  </si>
-  <si>
-    <t>[np.float64(387.5915283514927), np.float64(-68.14259665757709)]</t>
-  </si>
-  <si>
-    <t>[np.float64(491.47471311471793), np.float64(-3.24603432692993)]</t>
-  </si>
-  <si>
-    <t>[np.float64(980.9536194267416), np.float64(-19.751000734120908)]</t>
-  </si>
-  <si>
-    <t>[np.float64(147.44271915579776), np.float64(-5.799415953770563)]</t>
-  </si>
-  <si>
-    <t>[np.float64(345.2525525256166), np.float64(-50.23746671541505)]</t>
-  </si>
-  <si>
-    <t>[np.float64(128.89423288713175), np.float64(-4.411330898339884)]</t>
-  </si>
-  <si>
-    <t>[np.float64(754.9306496156581), np.float64(-28.031209767393648)]</t>
-  </si>
-  <si>
-    <t>[np.float64(666.785139287678), np.float64(-40.6091633648831)]</t>
-  </si>
-  <si>
-    <t>[np.float64(143.02988453272468), np.float64(-78.21884491280298)]</t>
-  </si>
-  <si>
-    <t>[np.float64(875.2089984637561), np.float64(-43.22791400348444)]</t>
-  </si>
-  <si>
-    <t>[np.float64(429.89647105010164), np.float64(-68.86941684224905)]</t>
-  </si>
-  <si>
-    <t>[np.float64(510.7467837494648), np.float64(-61.07779398565742)]</t>
-  </si>
-  <si>
-    <t>[np.float64(466.2601077893962), np.float64(-12.006452918763102)]</t>
-  </si>
-  <si>
-    <t>[np.float64(896.239937176825), np.float64(-100.17753689404844)]</t>
-  </si>
-  <si>
-    <t>[np.float64(133.86816695213122), np.float64(-50.287668940173376)]</t>
-  </si>
-  <si>
-    <t>[np.float64(800.6848565574288), np.float64(-89.90426334076756)]</t>
-  </si>
-  <si>
-    <t>[np.float64(538.4101999868036), np.float64(-0.2641324633360682)]</t>
-  </si>
-  <si>
-    <t>[np.float64(471.1315686490597), np.float64(-97.84504839489279)]</t>
-  </si>
-  <si>
-    <t>[np.float64(189.13299068015522), np.float64(-17.33483689494608)]</t>
-  </si>
-  <si>
-    <t>[np.float64(348.1636088676187), np.float64(-69.4549427261478)]</t>
-  </si>
-  <si>
-    <t>[np.float64(858.9805263499992), np.float64(-63.402135727277596)]</t>
-  </si>
-  <si>
-    <t>[np.float64(24.42865535692629), np.float64(-33.833809086513725)]</t>
-  </si>
-  <si>
-    <t>[np.float64(270.0603020061123), np.float64(-37.6748905641731)]</t>
-  </si>
-  <si>
-    <t>[np.float64(3.2896514724931603), np.float64(-28.645207879792906)]</t>
-  </si>
-  <si>
-    <t>[np.float64(85.04452184792343), np.float64(-7.859798606545382)]</t>
-  </si>
-  <si>
-    <t>[np.float64(511.99171540345776), np.float64(-67.20213399405077)]</t>
-  </si>
-  <si>
-    <t>[np.float64(274.3871479539144), np.float64(-26.37579469243576)]</t>
-  </si>
-  <si>
-    <t>[np.float64(476.243197546716), np.float64(-27.668164515952753)]</t>
-  </si>
-  <si>
-    <t>[np.float64(372.27575658718837), np.float64(-8.923579081905814)]</t>
-  </si>
-  <si>
-    <t>[np.float64(213.06099580998915), np.float64(-58.878423435315085)]</t>
-  </si>
-  <si>
-    <t>[np.float64(245.41806500849762), np.float64(-53.66809300145917)]</t>
-  </si>
-  <si>
-    <t>[np.float64(435.30722428107174), np.float64(-19.55097914387011)]</t>
-  </si>
-  <si>
-    <t>[np.float64(249.67324304343063), np.float64(-40.36057476880205)]</t>
-  </si>
-  <si>
-    <t>[np.float64(479.2141914670593), np.float64(-51.96073837672577)]</t>
-  </si>
-  <si>
-    <t>[np.float64(29.916895541495347), np.float64(-25.86389714047573)]</t>
-  </si>
-  <si>
-    <t>[np.float64(912.048718153437), np.float64(-44.24370026803558)]</t>
-  </si>
-  <si>
-    <t>[np.float64(54.22602847740543), np.float64(-11.96276471375586)]</t>
-  </si>
-  <si>
-    <t>[np.float64(2.7319118281209365), np.float64(-75.331224230869)]</t>
-  </si>
-  <si>
-    <t>[np.float64(13.405757534372565), np.float64(-52.44495308885985)]</t>
-  </si>
-  <si>
-    <t>[np.float64(763.1763577701931), np.float64(-47.241535244172155)]</t>
-  </si>
-  <si>
-    <t>[np.float64(974.6562422443867), np.float64(-40.93645053245609)]</t>
-  </si>
-  <si>
-    <t>[np.float64(309.07792657045565), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(467.2134461320424), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(544.2373016278519), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(499.7015975978243), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(832.8129768102044), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(910.6620944880085), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(781.5501525827768), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(947.1449473255919), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(174.2738604561519), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(512.1460983817421), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(133.5228554717268), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(806.0827033823335), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(373.1191762822642), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(83.55910418932244), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(821.391156499109), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(614.3008628509622), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(550.4766263352727), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(146.48117776003156), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(151.91438805955605), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(884.6591539083929), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(167.37641387361924), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(527.7962224036208), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(470.0764498824211), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(68.42759695717471), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(713.0236483111931), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(501.4141731493591), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(554.3734961789373), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(513.2872096191246), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(707.5779928397983), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(802.0294223684026), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(387.5915283514927), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(491.47471311471793), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(980.9536194267416), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(147.44271915579776), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(345.2525525256166), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(128.89423288713175), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(754.9306496156581), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(666.785139287678), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(143.02988453272468), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(875.2089984637561), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(429.89647105010164), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(510.7467837494648), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(466.2601077893962), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(896.239937176825), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(133.86816695213122), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(800.6848565574288), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(538.4101999868036), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(471.1315686490597), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(189.13299068015522), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(348.1636088676187), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(858.9805263499992), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(24.42865535692629), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(270.0603020061123), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(3.2896514724931607), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(85.04452184792343), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(511.99171540345776), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(274.3871479539144), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(476.243197546716), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(372.27575658718837), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(213.06099580998915), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(245.41806500849762), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(435.30722428107174), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(249.67324304343063), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(479.2141914670593), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(29.916895541495347), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(912.048718153437), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(54.22602847740543), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(2.7319118281209365), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(13.405757534372567), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(763.1763577701931), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(974.6562422443867), np.float64(0.0)]</t>
+    <t>[np.float64(439.2555741759444), np.float64(-67.45759897905714)]</t>
+  </si>
+  <si>
+    <t>[np.float64(113.855261954387), np.float64(-3.9529748937083014)]</t>
+  </si>
+  <si>
+    <t>[np.float64(375.9444040870893), np.float64(-65.48133549587885)]</t>
+  </si>
+  <si>
+    <t>[np.float64(130.7009713938775), np.float64(-21.007664667249287)]</t>
+  </si>
+  <si>
+    <t>[np.float64(693.1861607022436), np.float64(-50.176829455010534)]</t>
+  </si>
+  <si>
+    <t>[np.float64(649.0008954599699), np.float64(-16.98923611227201)]</t>
+  </si>
+  <si>
+    <t>[np.float64(867.3645516137615), np.float64(-1.5886176480599943)]</t>
+  </si>
+  <si>
+    <t>[np.float64(924.9799245897209), np.float64(-19.433138010897892)]</t>
+  </si>
+  <si>
+    <t>[np.float64(27.313694808545506), np.float64(-30.003860265316234)]</t>
+  </si>
+  <si>
+    <t>[np.float64(703.0024834813827), np.float64(-70.83641511049052)]</t>
+  </si>
+  <si>
+    <t>[np.float64(53.86174336406624), np.float64(-17.24161359642676)]</t>
+  </si>
+  <si>
+    <t>[np.float64(251.55480043599732), np.float64(-35.718627970742205)]</t>
+  </si>
+  <si>
+    <t>[np.float64(74.97614438655853), np.float64(-25.47341357881703)]</t>
+  </si>
+  <si>
+    <t>[np.float64(139.5992547646462), np.float64(-16.566544346737487)]</t>
+  </si>
+  <si>
+    <t>[np.float64(604.9169485602836), np.float64(-14.478417153387795)]</t>
+  </si>
+  <si>
+    <t>[np.float64(597.5083706178752), np.float64(-78.52360374686123)]</t>
+  </si>
+  <si>
+    <t>[np.float64(228.5049728605182), np.float64(-38.28529266658006)]</t>
+  </si>
+  <si>
+    <t>[np.float64(439.48187662742674), np.float64(-58.40700509466933)]</t>
+  </si>
+  <si>
+    <t>[np.float64(63.79436814434081), np.float64(-84.4671585736777)]</t>
+  </si>
+  <si>
+    <t>[np.float64(409.7392594392075), np.float64(-58.08532419804476)]</t>
+  </si>
+  <si>
+    <t>[np.float64(6.726973383522683), np.float64(-65.70942160224126)]</t>
+  </si>
+  <si>
+    <t>[np.float64(247.3805532967447), np.float64(-23.112897625299638)]</t>
+  </si>
+  <si>
+    <t>[np.float64(855.9299251861805), np.float64(-43.44644336572435)]</t>
+  </si>
+  <si>
+    <t>[np.float64(81.67367672230586), np.float64(-75.08310249941132)]</t>
+  </si>
+  <si>
+    <t>[np.float64(473.6180017386396), np.float64(-66.56374066286173)]</t>
+  </si>
+  <si>
+    <t>[np.float64(231.93796994819016), np.float64(-5.498762167241921)]</t>
+  </si>
+  <si>
+    <t>[np.float64(182.0451965872103), np.float64(-18.577490405561548)]</t>
+  </si>
+  <si>
+    <t>[np.float64(442.56459671039784), np.float64(-16.6829538847619)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.82605962515888), np.float64(-60.09776586834812)]</t>
+  </si>
+  <si>
+    <t>[np.float64(171.73999383917328), np.float64(-30.098856684371185)]</t>
+  </si>
+  <si>
+    <t>[np.float64(370.70806320472906), np.float64(-51.845031149320675)]</t>
+  </si>
+  <si>
+    <t>[np.float64(243.17157019790216), np.float64(-59.63831553947375)]</t>
+  </si>
+  <si>
+    <t>[np.float64(777.7350627257568), np.float64(-69.50266976843523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(106.85308639439317), np.float64(-33.58073805688707)]</t>
+  </si>
+  <si>
+    <t>[np.float64(321.2010563978412), np.float64(-56.81887137355545)]</t>
+  </si>
+  <si>
+    <t>[np.float64(393.8061973613973), np.float64(-14.925343041948395)]</t>
+  </si>
+  <si>
+    <t>[np.float64(597.7204922205598), np.float64(-4.810147077134388)]</t>
+  </si>
+  <si>
+    <t>[np.float64(769.4629084379967), np.float64(-28.268835961658624)]</t>
+  </si>
+  <si>
+    <t>[np.float64(71.52408720596969), np.float64(-75.94970199271734)]</t>
+  </si>
+  <si>
+    <t>[np.float64(74.63935044051262), np.float64(-20.10692809724253)]</t>
+  </si>
+  <si>
+    <t>[np.float64(690.8103695498024), np.float64(-18.446678643320297)]</t>
+  </si>
+  <si>
+    <t>[np.float64(705.2258775325961), np.float64(-18.677246368279043)]</t>
+  </si>
+  <si>
+    <t>[np.float64(68.470639268578), np.float64(-31.006908125445307)]</t>
+  </si>
+  <si>
+    <t>[np.float64(110.70829043563046), np.float64(-12.393024756421369)]</t>
+  </si>
+  <si>
+    <t>[np.float64(222.2107940723853), np.float64(-45.19221798206047)]</t>
+  </si>
+  <si>
+    <t>[np.float64(284.17093264085725), np.float64(-41.56635386768539)]</t>
+  </si>
+  <si>
+    <t>[np.float64(694.4960509369624), np.float64(-38.63889106443969)]</t>
+  </si>
+  <si>
+    <t>[np.float64(539.6305345551673), np.float64(-86.121848412948)]</t>
+  </si>
+  <si>
+    <t>[np.float64(994.1435538073938), np.float64(-58.72530786828577)]</t>
+  </si>
+  <si>
+    <t>[np.float64(743.0849578297946), np.float64(-37.620174581382)]</t>
+  </si>
+  <si>
+    <t>[np.float64(439.2555741759444), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(113.855261954387), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(375.9444040870893), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(130.7009713938775), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(693.1861607022436), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(649.0008954599699), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(867.3645516137615), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(924.9799245897209), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(27.313694808545506), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(703.0024834813827), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(53.86174336406624), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(251.55480043599732), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(74.97614438655853), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(139.5992547646462), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(604.9169485602836), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(597.5083706178752), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(228.5049728605182), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(439.48187662742674), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(63.79436814434081), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(409.7392594392075), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(6.726973383522683), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(247.3805532967447), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(855.9299251861805), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(81.67367672230586), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(473.6180017386396), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(231.93796994819016), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(182.0451965872103), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(442.56459671039784), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.82605962515888), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(171.73999383917328), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(370.70806320472906), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(243.17157019790216), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(777.7350627257568), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(106.85308639439317), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(321.2010563978412), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(393.8061973613973), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(597.7204922205598), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(769.4629084379967), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(71.52408720596969), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(74.6393504405126), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(690.8103695498024), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(705.2258775325961), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(68.470639268578), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(110.70829043563046), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(222.2107940723853), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(284.17093264085725), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(694.4960509369624), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(539.6305345551673), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(994.1435538073938), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(743.0849578297946), np.float64(0.0)]</t>
   </si>
 </sst>
 </file>
@@ -884,7 +758,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -924,7 +798,7 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -942,7 +816,7 @@
         <v>29</v>
       </c>
       <c r="I2" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -953,7 +827,7 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
@@ -971,7 +845,7 @@
         <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -982,7 +856,7 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
@@ -1000,7 +874,7 @@
         <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1011,7 +885,7 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
@@ -1029,7 +903,7 @@
         <v>32</v>
       </c>
       <c r="I5" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1040,7 +914,7 @@
         <v>2</v>
       </c>
       <c r="C6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -1052,13 +926,13 @@
         <v>28</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="s">
         <v>33</v>
       </c>
       <c r="I6" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1069,10 +943,10 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
         <v>27</v>
@@ -1081,13 +955,13 @@
         <v>28</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="s">
         <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>105</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1098,11 +972,11 @@
         <v>2</v>
       </c>
       <c r="C8">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
       <c r="E8" t="s">
         <v>27</v>
       </c>
@@ -1110,13 +984,13 @@
         <v>28</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="s">
         <v>35</v>
       </c>
       <c r="I8" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1127,10 +1001,10 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
@@ -1139,13 +1013,13 @@
         <v>28</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="s">
         <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1156,10 +1030,10 @@
         <v>2</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E10" t="s">
         <v>27</v>
@@ -1168,13 +1042,13 @@
         <v>28</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="s">
         <v>37</v>
       </c>
       <c r="I10" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1185,10 +1059,10 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E11" t="s">
         <v>27</v>
@@ -1197,13 +1071,13 @@
         <v>28</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="s">
         <v>38</v>
       </c>
       <c r="I11" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1214,7 +1088,7 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
         <v>18</v>
@@ -1226,13 +1100,13 @@
         <v>28</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="s">
         <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1243,10 +1117,10 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E13" t="s">
         <v>27</v>
@@ -1255,13 +1129,13 @@
         <v>28</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="s">
         <v>40</v>
       </c>
       <c r="I13" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1272,10 +1146,10 @@
         <v>2</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E14" t="s">
         <v>27</v>
@@ -1290,7 +1164,7 @@
         <v>41</v>
       </c>
       <c r="I14" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1301,10 +1175,10 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
         <v>27</v>
@@ -1313,13 +1187,13 @@
         <v>28</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1330,10 +1204,10 @@
         <v>2</v>
       </c>
       <c r="C16">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
         <v>27</v>
@@ -1342,13 +1216,13 @@
         <v>28</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="s">
         <v>43</v>
       </c>
       <c r="I16" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1362,7 +1236,7 @@
         <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
         <v>27</v>
@@ -1371,13 +1245,13 @@
         <v>28</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="s">
         <v>44</v>
       </c>
       <c r="I17" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1388,10 +1262,10 @@
         <v>2</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E18" t="s">
         <v>27</v>
@@ -1400,13 +1274,13 @@
         <v>28</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
       </c>
       <c r="I18" t="s">
-        <v>116</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1417,10 +1291,10 @@
         <v>2</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E19" t="s">
         <v>27</v>
@@ -1429,13 +1303,13 @@
         <v>28</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="s">
         <v>46</v>
       </c>
       <c r="I19" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1446,7 +1320,7 @@
         <v>2</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" t="s">
         <v>18</v>
@@ -1458,13 +1332,13 @@
         <v>28</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>47</v>
       </c>
       <c r="I20" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1475,10 +1349,10 @@
         <v>2</v>
       </c>
       <c r="C21">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E21" t="s">
         <v>27</v>
@@ -1493,7 +1367,7 @@
         <v>48</v>
       </c>
       <c r="I21" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1504,10 +1378,10 @@
         <v>2</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E22" t="s">
         <v>27</v>
@@ -1522,7 +1396,7 @@
         <v>49</v>
       </c>
       <c r="I22" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1533,10 +1407,10 @@
         <v>2</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23" t="s">
         <v>27</v>
@@ -1545,13 +1419,13 @@
         <v>28</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="s">
         <v>50</v>
       </c>
       <c r="I23" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1562,10 +1436,10 @@
         <v>2</v>
       </c>
       <c r="C24">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E24" t="s">
         <v>27</v>
@@ -1574,13 +1448,13 @@
         <v>28</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="s">
         <v>51</v>
       </c>
       <c r="I24" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1594,7 +1468,7 @@
         <v>2</v>
       </c>
       <c r="D25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E25" t="s">
         <v>27</v>
@@ -1603,13 +1477,13 @@
         <v>28</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" t="s">
         <v>52</v>
       </c>
       <c r="I25" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1620,10 +1494,10 @@
         <v>2</v>
       </c>
       <c r="C26">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E26" t="s">
         <v>27</v>
@@ -1638,7 +1512,7 @@
         <v>53</v>
       </c>
       <c r="I26" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1649,10 +1523,10 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D27" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E27" t="s">
         <v>27</v>
@@ -1661,13 +1535,13 @@
         <v>28</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="s">
         <v>54</v>
       </c>
       <c r="I27" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1678,10 +1552,10 @@
         <v>2</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E28" t="s">
         <v>27</v>
@@ -1696,7 +1570,7 @@
         <v>55</v>
       </c>
       <c r="I28" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1707,10 +1581,10 @@
         <v>2</v>
       </c>
       <c r="C29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s">
         <v>27</v>
@@ -1725,7 +1599,7 @@
         <v>56</v>
       </c>
       <c r="I29" t="s">
-        <v>127</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1736,7 +1610,7 @@
         <v>2</v>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D30" t="s">
         <v>22</v>
@@ -1748,13 +1622,13 @@
         <v>28</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" t="s">
         <v>57</v>
       </c>
       <c r="I30" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1765,10 +1639,10 @@
         <v>2</v>
       </c>
       <c r="C31">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E31" t="s">
         <v>27</v>
@@ -1777,13 +1651,13 @@
         <v>28</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H31" t="s">
         <v>58</v>
       </c>
       <c r="I31" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1797,7 +1671,7 @@
         <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E32" t="s">
         <v>27</v>
@@ -1806,13 +1680,13 @@
         <v>28</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H32" t="s">
         <v>59</v>
       </c>
       <c r="I32" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1823,10 +1697,10 @@
         <v>2</v>
       </c>
       <c r="C33">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E33" t="s">
         <v>27</v>
@@ -1841,7 +1715,7 @@
         <v>60</v>
       </c>
       <c r="I33" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1852,10 +1726,10 @@
         <v>2</v>
       </c>
       <c r="C34">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E34" t="s">
         <v>27</v>
@@ -1864,13 +1738,13 @@
         <v>28</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" t="s">
         <v>61</v>
       </c>
       <c r="I34" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1884,7 +1758,7 @@
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E35" t="s">
         <v>27</v>
@@ -1893,13 +1767,13 @@
         <v>28</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" t="s">
         <v>62</v>
       </c>
       <c r="I35" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1910,10 +1784,10 @@
         <v>2</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E36" t="s">
         <v>27</v>
@@ -1922,13 +1796,13 @@
         <v>28</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" t="s">
         <v>63</v>
       </c>
       <c r="I36" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1939,10 +1813,10 @@
         <v>2</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D37" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E37" t="s">
         <v>27</v>
@@ -1951,13 +1825,13 @@
         <v>28</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37" t="s">
         <v>64</v>
       </c>
       <c r="I37" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1968,10 +1842,10 @@
         <v>2</v>
       </c>
       <c r="C38">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E38" t="s">
         <v>27</v>
@@ -1980,13 +1854,13 @@
         <v>28</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" t="s">
         <v>65</v>
       </c>
       <c r="I38" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1997,7 +1871,7 @@
         <v>2</v>
       </c>
       <c r="C39">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s">
         <v>23</v>
@@ -2009,13 +1883,13 @@
         <v>28</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="s">
         <v>66</v>
       </c>
       <c r="I39" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -2026,7 +1900,7 @@
         <v>2</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40" t="s">
         <v>18</v>
@@ -2038,13 +1912,13 @@
         <v>28</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" t="s">
         <v>67</v>
       </c>
       <c r="I40" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -2055,10 +1929,10 @@
         <v>2</v>
       </c>
       <c r="C41">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E41" t="s">
         <v>27</v>
@@ -2067,13 +1941,13 @@
         <v>28</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" t="s">
         <v>68</v>
       </c>
       <c r="I41" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -2084,10 +1958,10 @@
         <v>2</v>
       </c>
       <c r="C42">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E42" t="s">
         <v>27</v>
@@ -2096,13 +1970,13 @@
         <v>28</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="s">
         <v>69</v>
       </c>
       <c r="I42" t="s">
-        <v>140</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -2113,10 +1987,10 @@
         <v>2</v>
       </c>
       <c r="C43">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E43" t="s">
         <v>27</v>
@@ -2125,13 +1999,13 @@
         <v>28</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H43" t="s">
         <v>70</v>
       </c>
       <c r="I43" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2142,10 +2016,10 @@
         <v>2</v>
       </c>
       <c r="C44">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E44" t="s">
         <v>27</v>
@@ -2154,13 +2028,13 @@
         <v>28</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="s">
         <v>71</v>
       </c>
       <c r="I44" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2171,10 +2045,10 @@
         <v>2</v>
       </c>
       <c r="C45">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E45" t="s">
         <v>27</v>
@@ -2189,7 +2063,7 @@
         <v>72</v>
       </c>
       <c r="I45" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2200,10 +2074,10 @@
         <v>2</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E46" t="s">
         <v>27</v>
@@ -2212,13 +2086,13 @@
         <v>28</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="s">
         <v>73</v>
       </c>
       <c r="I46" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2229,10 +2103,10 @@
         <v>2</v>
       </c>
       <c r="C47">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
         <v>27</v>
@@ -2241,13 +2115,13 @@
         <v>28</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" t="s">
         <v>74</v>
       </c>
       <c r="I47" t="s">
-        <v>145</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2258,10 +2132,10 @@
         <v>2</v>
       </c>
       <c r="C48">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E48" t="s">
         <v>27</v>
@@ -2270,13 +2144,13 @@
         <v>28</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" t="s">
         <v>75</v>
       </c>
       <c r="I48" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2287,10 +2161,10 @@
         <v>2</v>
       </c>
       <c r="C49">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D49" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E49" t="s">
         <v>27</v>
@@ -2305,7 +2179,7 @@
         <v>76</v>
       </c>
       <c r="I49" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2316,10 +2190,10 @@
         <v>2</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E50" t="s">
         <v>27</v>
@@ -2328,13 +2202,13 @@
         <v>28</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" t="s">
         <v>77</v>
       </c>
       <c r="I50" t="s">
-        <v>148</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2345,10 +2219,10 @@
         <v>2</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E51" t="s">
         <v>27</v>
@@ -2357,622 +2231,13 @@
         <v>28</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H51" t="s">
         <v>78</v>
       </c>
       <c r="I51" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" t="s">
-        <v>9</v>
-      </c>
-      <c r="B52">
-        <v>2</v>
-      </c>
-      <c r="C52">
-        <v>15</v>
-      </c>
-      <c r="D52" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" t="s">
-        <v>27</v>
-      </c>
-      <c r="F52" t="s">
-        <v>28</v>
-      </c>
-      <c r="G52">
-        <v>1</v>
-      </c>
-      <c r="H52" t="s">
-        <v>79</v>
-      </c>
-      <c r="I52" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" t="s">
-        <v>9</v>
-      </c>
-      <c r="B53">
-        <v>2</v>
-      </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53" t="s">
-        <v>25</v>
-      </c>
-      <c r="E53" t="s">
-        <v>27</v>
-      </c>
-      <c r="F53" t="s">
-        <v>28</v>
-      </c>
-      <c r="G53">
-        <v>1</v>
-      </c>
-      <c r="H53" t="s">
-        <v>80</v>
-      </c>
-      <c r="I53" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" t="s">
-        <v>9</v>
-      </c>
-      <c r="B54">
-        <v>2</v>
-      </c>
-      <c r="C54">
-        <v>5</v>
-      </c>
-      <c r="D54" t="s">
-        <v>26</v>
-      </c>
-      <c r="E54" t="s">
-        <v>27</v>
-      </c>
-      <c r="F54" t="s">
-        <v>28</v>
-      </c>
-      <c r="G54">
-        <v>2</v>
-      </c>
-      <c r="H54" t="s">
-        <v>81</v>
-      </c>
-      <c r="I54" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" t="s">
-        <v>9</v>
-      </c>
-      <c r="B55">
-        <v>2</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" t="s">
-        <v>27</v>
-      </c>
-      <c r="F55" t="s">
-        <v>28</v>
-      </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55" t="s">
-        <v>82</v>
-      </c>
-      <c r="I55" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56" t="s">
-        <v>9</v>
-      </c>
-      <c r="B56">
-        <v>2</v>
-      </c>
-      <c r="C56">
-        <v>2</v>
-      </c>
-      <c r="D56" t="s">
-        <v>20</v>
-      </c>
-      <c r="E56" t="s">
-        <v>27</v>
-      </c>
-      <c r="F56" t="s">
-        <v>28</v>
-      </c>
-      <c r="G56">
-        <v>2</v>
-      </c>
-      <c r="H56" t="s">
-        <v>83</v>
-      </c>
-      <c r="I56" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
-      <c r="A57" t="s">
-        <v>9</v>
-      </c>
-      <c r="B57">
-        <v>2</v>
-      </c>
-      <c r="C57">
-        <v>9</v>
-      </c>
-      <c r="D57" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" t="s">
-        <v>27</v>
-      </c>
-      <c r="F57" t="s">
-        <v>28</v>
-      </c>
-      <c r="G57">
-        <v>2</v>
-      </c>
-      <c r="H57" t="s">
-        <v>84</v>
-      </c>
-      <c r="I57" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9">
-      <c r="A58" t="s">
-        <v>9</v>
-      </c>
-      <c r="B58">
-        <v>2</v>
-      </c>
-      <c r="C58">
-        <v>5</v>
-      </c>
-      <c r="D58" t="s">
-        <v>26</v>
-      </c>
-      <c r="E58" t="s">
-        <v>27</v>
-      </c>
-      <c r="F58" t="s">
-        <v>28</v>
-      </c>
-      <c r="G58">
-        <v>2</v>
-      </c>
-      <c r="H58" t="s">
-        <v>85</v>
-      </c>
-      <c r="I58" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="A59" t="s">
-        <v>9</v>
-      </c>
-      <c r="B59">
-        <v>2</v>
-      </c>
-      <c r="C59">
-        <v>9</v>
-      </c>
-      <c r="D59" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" t="s">
-        <v>27</v>
-      </c>
-      <c r="F59" t="s">
-        <v>28</v>
-      </c>
-      <c r="G59">
-        <v>0</v>
-      </c>
-      <c r="H59" t="s">
-        <v>86</v>
-      </c>
-      <c r="I59" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60" t="s">
-        <v>9</v>
-      </c>
-      <c r="B60">
-        <v>2</v>
-      </c>
-      <c r="C60">
-        <v>7</v>
-      </c>
-      <c r="D60" t="s">
-        <v>19</v>
-      </c>
-      <c r="E60" t="s">
-        <v>27</v>
-      </c>
-      <c r="F60" t="s">
-        <v>28</v>
-      </c>
-      <c r="G60">
-        <v>1</v>
-      </c>
-      <c r="H60" t="s">
-        <v>87</v>
-      </c>
-      <c r="I60" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61" t="s">
-        <v>9</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
-      </c>
-      <c r="C61">
-        <v>4</v>
-      </c>
-      <c r="D61" t="s">
-        <v>17</v>
-      </c>
-      <c r="E61" t="s">
-        <v>27</v>
-      </c>
-      <c r="F61" t="s">
-        <v>28</v>
-      </c>
-      <c r="G61">
-        <v>2</v>
-      </c>
-      <c r="H61" t="s">
-        <v>88</v>
-      </c>
-      <c r="I61" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62" t="s">
-        <v>9</v>
-      </c>
-      <c r="B62">
-        <v>2</v>
-      </c>
-      <c r="C62">
-        <v>5</v>
-      </c>
-      <c r="D62" t="s">
-        <v>26</v>
-      </c>
-      <c r="E62" t="s">
-        <v>27</v>
-      </c>
-      <c r="F62" t="s">
-        <v>28</v>
-      </c>
-      <c r="G62">
-        <v>1</v>
-      </c>
-      <c r="H62" t="s">
-        <v>89</v>
-      </c>
-      <c r="I62" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9">
-      <c r="A63" t="s">
-        <v>9</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
-      <c r="C63">
-        <v>8</v>
-      </c>
-      <c r="D63" t="s">
-        <v>24</v>
-      </c>
-      <c r="E63" t="s">
-        <v>27</v>
-      </c>
-      <c r="F63" t="s">
-        <v>28</v>
-      </c>
-      <c r="G63">
-        <v>1</v>
-      </c>
-      <c r="H63" t="s">
-        <v>90</v>
-      </c>
-      <c r="I63" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64" t="s">
-        <v>9</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
-      </c>
-      <c r="C64">
-        <v>5</v>
-      </c>
-      <c r="D64" t="s">
-        <v>26</v>
-      </c>
-      <c r="E64" t="s">
-        <v>27</v>
-      </c>
-      <c r="F64" t="s">
-        <v>28</v>
-      </c>
-      <c r="G64">
-        <v>1</v>
-      </c>
-      <c r="H64" t="s">
-        <v>91</v>
-      </c>
-      <c r="I64" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9">
-      <c r="A65" t="s">
-        <v>9</v>
-      </c>
-      <c r="B65">
-        <v>2</v>
-      </c>
-      <c r="C65">
-        <v>9</v>
-      </c>
-      <c r="D65" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" t="s">
-        <v>27</v>
-      </c>
-      <c r="F65" t="s">
-        <v>28</v>
-      </c>
-      <c r="G65">
-        <v>0</v>
-      </c>
-      <c r="H65" t="s">
-        <v>92</v>
-      </c>
-      <c r="I65" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
-      <c r="A66" t="s">
-        <v>9</v>
-      </c>
-      <c r="B66">
-        <v>2</v>
-      </c>
-      <c r="C66">
-        <v>1</v>
-      </c>
-      <c r="D66" t="s">
-        <v>25</v>
-      </c>
-      <c r="E66" t="s">
-        <v>27</v>
-      </c>
-      <c r="F66" t="s">
-        <v>28</v>
-      </c>
-      <c r="G66">
-        <v>1</v>
-      </c>
-      <c r="H66" t="s">
-        <v>93</v>
-      </c>
-      <c r="I66" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9">
-      <c r="A67" t="s">
-        <v>9</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
-      </c>
-      <c r="C67">
-        <v>16</v>
-      </c>
-      <c r="D67" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" t="s">
-        <v>27</v>
-      </c>
-      <c r="F67" t="s">
-        <v>28</v>
-      </c>
-      <c r="G67">
-        <v>1</v>
-      </c>
-      <c r="H67" t="s">
-        <v>94</v>
-      </c>
-      <c r="I67" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9">
-      <c r="A68" t="s">
-        <v>9</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
-      <c r="C68">
-        <v>2</v>
-      </c>
-      <c r="D68" t="s">
-        <v>20</v>
-      </c>
-      <c r="E68" t="s">
-        <v>27</v>
-      </c>
-      <c r="F68" t="s">
-        <v>28</v>
-      </c>
-      <c r="G68">
-        <v>0</v>
-      </c>
-      <c r="H68" t="s">
-        <v>95</v>
-      </c>
-      <c r="I68" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9">
-      <c r="A69" t="s">
-        <v>9</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
-      </c>
-      <c r="C69">
-        <v>1</v>
-      </c>
-      <c r="D69" t="s">
-        <v>25</v>
-      </c>
-      <c r="E69" t="s">
-        <v>27</v>
-      </c>
-      <c r="F69" t="s">
-        <v>28</v>
-      </c>
-      <c r="G69">
-        <v>0</v>
-      </c>
-      <c r="H69" t="s">
-        <v>96</v>
-      </c>
-      <c r="I69" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
-      <c r="A70" t="s">
-        <v>9</v>
-      </c>
-      <c r="B70">
-        <v>2</v>
-      </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
-      <c r="D70" t="s">
-        <v>25</v>
-      </c>
-      <c r="E70" t="s">
-        <v>27</v>
-      </c>
-      <c r="F70" t="s">
-        <v>28</v>
-      </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70" t="s">
-        <v>97</v>
-      </c>
-      <c r="I70" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
-      <c r="A71" t="s">
-        <v>9</v>
-      </c>
-      <c r="B71">
-        <v>2</v>
-      </c>
-      <c r="C71">
-        <v>14</v>
-      </c>
-      <c r="D71" t="s">
-        <v>15</v>
-      </c>
-      <c r="E71" t="s">
-        <v>27</v>
-      </c>
-      <c r="F71" t="s">
-        <v>28</v>
-      </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71" t="s">
-        <v>98</v>
-      </c>
-      <c r="I71" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9">
-      <c r="A72" t="s">
-        <v>9</v>
-      </c>
-      <c r="B72">
-        <v>2</v>
-      </c>
-      <c r="C72">
-        <v>17</v>
-      </c>
-      <c r="D72" t="s">
-        <v>16</v>
-      </c>
-      <c r="E72" t="s">
-        <v>27</v>
-      </c>
-      <c r="F72" t="s">
-        <v>28</v>
-      </c>
-      <c r="G72">
-        <v>1</v>
-      </c>
-      <c r="H72" t="s">
-        <v>99</v>
-      </c>
-      <c r="I72" t="s">
-        <v>170</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/Data/output/DIR Stroke Position.xlsx
+++ b/Data/output/DIR Stroke Position.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="128">
   <si>
     <t>Direct_or_Indirect</t>
   </si>
@@ -46,361 +46,358 @@
     <t>Direct</t>
   </si>
   <si>
+    <t>1004.0</t>
+  </si>
+  <si>
+    <t>1006.0</t>
+  </si>
+  <si>
+    <t>1017.0</t>
+  </si>
+  <si>
+    <t>1013.0</t>
+  </si>
+  <si>
+    <t>1007.0</t>
+  </si>
+  <si>
+    <t>1010.0</t>
+  </si>
+  <si>
+    <t>1014.0</t>
+  </si>
+  <si>
+    <t>1015.0</t>
+  </si>
+  <si>
+    <t>1002.0</t>
+  </si>
+  <si>
+    <t>1016.0</t>
+  </si>
+  <si>
+    <t>1012.0</t>
+  </si>
+  <si>
+    <t>1001.0</t>
+  </si>
+  <si>
+    <t>1011.0</t>
+  </si>
+  <si>
+    <t>1003.0</t>
+  </si>
+  <si>
     <t>1008.0</t>
   </si>
   <si>
-    <t>1003.0</t>
-  </si>
-  <si>
-    <t>1007.0</t>
-  </si>
-  <si>
-    <t>1012.0</t>
-  </si>
-  <si>
-    <t>1015.0</t>
-  </si>
-  <si>
-    <t>1016.0</t>
-  </si>
-  <si>
-    <t>1001.0</t>
-  </si>
-  <si>
-    <t>1013.0</t>
-  </si>
-  <si>
-    <t>1002.0</t>
-  </si>
-  <si>
-    <t>1005.0</t>
-  </si>
-  <si>
-    <t>1011.0</t>
-  </si>
-  <si>
     <t>1009.0</t>
   </si>
   <si>
-    <t>1004.0</t>
-  </si>
-  <si>
-    <t>1014.0</t>
-  </si>
-  <si>
-    <t>1006.0</t>
-  </si>
-  <si>
-    <t>1010.0</t>
-  </si>
-  <si>
-    <t>1017.0</t>
-  </si>
-  <si>
     <t>0.0</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>[np.float64(439.2555741759444), np.float64(-67.45759897905714)]</t>
-  </si>
-  <si>
-    <t>[np.float64(113.855261954387), np.float64(-3.9529748937083014)]</t>
-  </si>
-  <si>
-    <t>[np.float64(375.9444040870893), np.float64(-65.48133549587885)]</t>
-  </si>
-  <si>
-    <t>[np.float64(130.7009713938775), np.float64(-21.007664667249287)]</t>
-  </si>
-  <si>
-    <t>[np.float64(693.1861607022436), np.float64(-50.176829455010534)]</t>
-  </si>
-  <si>
-    <t>[np.float64(649.0008954599699), np.float64(-16.98923611227201)]</t>
-  </si>
-  <si>
-    <t>[np.float64(867.3645516137615), np.float64(-1.5886176480599943)]</t>
-  </si>
-  <si>
-    <t>[np.float64(924.9799245897209), np.float64(-19.433138010897892)]</t>
-  </si>
-  <si>
-    <t>[np.float64(27.313694808545506), np.float64(-30.003860265316234)]</t>
-  </si>
-  <si>
-    <t>[np.float64(703.0024834813827), np.float64(-70.83641511049052)]</t>
-  </si>
-  <si>
-    <t>[np.float64(53.86174336406624), np.float64(-17.24161359642676)]</t>
-  </si>
-  <si>
-    <t>[np.float64(251.55480043599732), np.float64(-35.718627970742205)]</t>
-  </si>
-  <si>
-    <t>[np.float64(74.97614438655853), np.float64(-25.47341357881703)]</t>
-  </si>
-  <si>
-    <t>[np.float64(139.5992547646462), np.float64(-16.566544346737487)]</t>
-  </si>
-  <si>
-    <t>[np.float64(604.9169485602836), np.float64(-14.478417153387795)]</t>
-  </si>
-  <si>
-    <t>[np.float64(597.5083706178752), np.float64(-78.52360374686123)]</t>
-  </si>
-  <si>
-    <t>[np.float64(228.5049728605182), np.float64(-38.28529266658006)]</t>
-  </si>
-  <si>
-    <t>[np.float64(439.48187662742674), np.float64(-58.40700509466933)]</t>
-  </si>
-  <si>
-    <t>[np.float64(63.79436814434081), np.float64(-84.4671585736777)]</t>
-  </si>
-  <si>
-    <t>[np.float64(409.7392594392075), np.float64(-58.08532419804476)]</t>
-  </si>
-  <si>
-    <t>[np.float64(6.726973383522683), np.float64(-65.70942160224126)]</t>
-  </si>
-  <si>
-    <t>[np.float64(247.3805532967447), np.float64(-23.112897625299638)]</t>
-  </si>
-  <si>
-    <t>[np.float64(855.9299251861805), np.float64(-43.44644336572435)]</t>
-  </si>
-  <si>
-    <t>[np.float64(81.67367672230586), np.float64(-75.08310249941132)]</t>
-  </si>
-  <si>
-    <t>[np.float64(473.6180017386396), np.float64(-66.56374066286173)]</t>
-  </si>
-  <si>
-    <t>[np.float64(231.93796994819016), np.float64(-5.498762167241921)]</t>
-  </si>
-  <si>
-    <t>[np.float64(182.0451965872103), np.float64(-18.577490405561548)]</t>
-  </si>
-  <si>
-    <t>[np.float64(442.56459671039784), np.float64(-16.6829538847619)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.82605962515888), np.float64(-60.09776586834812)]</t>
-  </si>
-  <si>
-    <t>[np.float64(171.73999383917328), np.float64(-30.098856684371185)]</t>
-  </si>
-  <si>
-    <t>[np.float64(370.70806320472906), np.float64(-51.845031149320675)]</t>
-  </si>
-  <si>
-    <t>[np.float64(243.17157019790216), np.float64(-59.63831553947375)]</t>
-  </si>
-  <si>
-    <t>[np.float64(777.7350627257568), np.float64(-69.50266976843523)]</t>
-  </si>
-  <si>
-    <t>[np.float64(106.85308639439317), np.float64(-33.58073805688707)]</t>
-  </si>
-  <si>
-    <t>[np.float64(321.2010563978412), np.float64(-56.81887137355545)]</t>
-  </si>
-  <si>
-    <t>[np.float64(393.8061973613973), np.float64(-14.925343041948395)]</t>
-  </si>
-  <si>
-    <t>[np.float64(597.7204922205598), np.float64(-4.810147077134388)]</t>
-  </si>
-  <si>
-    <t>[np.float64(769.4629084379967), np.float64(-28.268835961658624)]</t>
-  </si>
-  <si>
-    <t>[np.float64(71.52408720596969), np.float64(-75.94970199271734)]</t>
-  </si>
-  <si>
-    <t>[np.float64(74.63935044051262), np.float64(-20.10692809724253)]</t>
-  </si>
-  <si>
-    <t>[np.float64(690.8103695498024), np.float64(-18.446678643320297)]</t>
-  </si>
-  <si>
-    <t>[np.float64(705.2258775325961), np.float64(-18.677246368279043)]</t>
-  </si>
-  <si>
-    <t>[np.float64(68.470639268578), np.float64(-31.006908125445307)]</t>
-  </si>
-  <si>
-    <t>[np.float64(110.70829043563046), np.float64(-12.393024756421369)]</t>
-  </si>
-  <si>
-    <t>[np.float64(222.2107940723853), np.float64(-45.19221798206047)]</t>
-  </si>
-  <si>
-    <t>[np.float64(284.17093264085725), np.float64(-41.56635386768539)]</t>
-  </si>
-  <si>
-    <t>[np.float64(694.4960509369624), np.float64(-38.63889106443969)]</t>
-  </si>
-  <si>
-    <t>[np.float64(539.6305345551673), np.float64(-86.121848412948)]</t>
-  </si>
-  <si>
-    <t>[np.float64(994.1435538073938), np.float64(-58.72530786828577)]</t>
-  </si>
-  <si>
-    <t>[np.float64(743.0849578297946), np.float64(-37.620174581382)]</t>
-  </si>
-  <si>
-    <t>[np.float64(439.2555741759444), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(113.855261954387), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(375.9444040870893), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(130.7009713938775), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(693.1861607022436), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(649.0008954599699), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(867.3645516137615), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(924.9799245897209), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(27.313694808545506), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(703.0024834813827), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(53.86174336406624), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(251.55480043599732), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(74.97614438655853), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(139.5992547646462), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(604.9169485602836), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(597.5083706178752), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(228.5049728605182), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(439.48187662742674), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(63.79436814434081), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(409.7392594392075), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(6.726973383522683), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(247.3805532967447), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(855.9299251861805), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(81.67367672230586), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(473.6180017386396), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(231.93796994819016), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(182.0451965872103), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(442.56459671039784), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(201.82605962515888), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(171.73999383917328), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(370.70806320472906), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(243.17157019790216), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(777.7350627257568), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(106.85308639439317), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(321.2010563978412), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(393.8061973613973), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(597.7204922205598), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(769.4629084379967), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(71.52408720596969), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(74.6393504405126), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(690.8103695498024), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(705.2258775325961), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(68.470639268578), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(110.70829043563046), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(222.2107940723853), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(284.17093264085725), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(694.4960509369624), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(539.6305345551673), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(994.1435538073938), np.float64(0.0)]</t>
-  </si>
-  <si>
-    <t>[np.float64(743.0849578297946), np.float64(0.0)]</t>
+    <t>[np.float64(160.2961530508832), np.float64(-67.85389150854655)]</t>
+  </si>
+  <si>
+    <t>[np.float64(312.008453926336), np.float64(-58.69905454211073)]</t>
+  </si>
+  <si>
+    <t>[np.float64(942.2401402613564), np.float64(-29.08131532335733)]</t>
+  </si>
+  <si>
+    <t>[np.float64(320.3420240254176), np.float64(-47.2052401461184)]</t>
+  </si>
+  <si>
+    <t>[np.float64(982.8601381953165), np.float64(-3.516344518773053)]</t>
+  </si>
+  <si>
+    <t>[np.float64(716.5954621447797), np.float64(-79.23262928088366)]</t>
+  </si>
+  <si>
+    <t>[np.float64(381.3830877881243), np.float64(-39.06881097347241)]</t>
+  </si>
+  <si>
+    <t>[np.float64(546.8541378167012), np.float64(-64.06381068858991)]</t>
+  </si>
+  <si>
+    <t>[np.float64(765.9598335336275), np.float64(-118.59048100742598)]</t>
+  </si>
+  <si>
+    <t>[np.float64(851.5174394138554), np.float64(-8.151380955976038)]</t>
+  </si>
+  <si>
+    <t>[np.float64(813.9160291435797), np.float64(-74.08043292731918)]</t>
+  </si>
+  <si>
+    <t>[np.float64(64.02627788007675), np.float64(-47.20537661436674)]</t>
+  </si>
+  <si>
+    <t>[np.float64(894.2395375973165), np.float64(-36.02463385091164)]</t>
+  </si>
+  <si>
+    <t>[np.float64(786.8916893014919), np.float64(-13.022913452309467)]</t>
+  </si>
+  <si>
+    <t>[np.float64(747.2928036125347), np.float64(-121.56471692410207)]</t>
+  </si>
+  <si>
+    <t>[np.float64(866.7035085301883), np.float64(-69.92895086790634)]</t>
+  </si>
+  <si>
+    <t>[np.float64(886.0994448771776), np.float64(-44.44614170844068)]</t>
+  </si>
+  <si>
+    <t>[np.float64(720.8303210883616), np.float64(-8.567053838587526)]</t>
+  </si>
+  <si>
+    <t>[np.float64(675.3629822820552), np.float64(-30.69109341168553)]</t>
+  </si>
+  <si>
+    <t>[np.float64(322.0840849288688), np.float64(-28.699040129413333)]</t>
+  </si>
+  <si>
+    <t>[np.float64(33.54151763540825), np.float64(-37.574960940816595)]</t>
+  </si>
+  <si>
+    <t>[np.float64(297.88810275817923), np.float64(-58.93012531135264)]</t>
+  </si>
+  <si>
+    <t>[np.float64(835.317847706138), np.float64(-43.46737570159439)]</t>
+  </si>
+  <si>
+    <t>[np.float64(306.21831016689316), np.float64(-57.47773017236523)]</t>
+  </si>
+  <si>
+    <t>[np.float64(57.99243447011049), np.float64(-42.431727702009994)]</t>
+  </si>
+  <si>
+    <t>[np.float64(390.25076914897795), np.float64(-49.39539588820037)]</t>
+  </si>
+  <si>
+    <t>[np.float64(721.5409497568218), np.float64(-6.266971024989402)]</t>
+  </si>
+  <si>
+    <t>[np.float64(177.74749893631747), np.float64(-101.14405660517741)]</t>
+  </si>
+  <si>
+    <t>[np.float64(885.2130201980872), np.float64(-14.063371855178048)]</t>
+  </si>
+  <si>
+    <t>[np.float64(630.0936424475204), np.float64(-44.271413907499095)]</t>
+  </si>
+  <si>
+    <t>[np.float64(947.7662795650203), np.float64(-31.02352911443745)]</t>
+  </si>
+  <si>
+    <t>[np.float64(317.1980220508711), np.float64(-36.7100152973062)]</t>
+  </si>
+  <si>
+    <t>[np.float64(83.57933451742194), np.float64(-10.229448416722903)]</t>
+  </si>
+  <si>
+    <t>[np.float64(121.42668198363371), np.float64(-102.03569613304205)]</t>
+  </si>
+  <si>
+    <t>[np.float64(302.3741936539596), np.float64(-17.980417088571926)]</t>
+  </si>
+  <si>
+    <t>[np.float64(402.8376028285825), np.float64(-44.32949854769606)]</t>
+  </si>
+  <si>
+    <t>[np.float64(474.79028415099253), np.float64(-45.46564204916888)]</t>
+  </si>
+  <si>
+    <t>[np.float64(962.5222470904205), np.float64(-21.382952632117963)]</t>
+  </si>
+  <si>
+    <t>[np.float64(839.6943677116317), np.float64(-91.65140115733561)]</t>
+  </si>
+  <si>
+    <t>[np.float64(109.19871242852952), np.float64(-17.090944016241224)]</t>
+  </si>
+  <si>
+    <t>[np.float64(849.4034826034084), np.float64(-69.20766171104935)]</t>
+  </si>
+  <si>
+    <t>[np.float64(426.95626934096185), np.float64(-26.780786242748377)]</t>
+  </si>
+  <si>
+    <t>[np.float64(304.9579860392654), np.float64(-61.440254442028845)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.28996376221608), np.float64(-19.191988208721455)]</t>
+  </si>
+  <si>
+    <t>[np.float64(896.9931429636953), np.float64(-3.9565338562866827)]</t>
+  </si>
+  <si>
+    <t>[np.float64(281.60486886981596), np.float64(-35.76278101244907)]</t>
+  </si>
+  <si>
+    <t>[np.float64(340.32238859732536), np.float64(-18.226310401486444)]</t>
+  </si>
+  <si>
+    <t>[np.float64(296.88941582071305), np.float64(-34.97956942971791)]</t>
+  </si>
+  <si>
+    <t>[np.float64(70.36852230923563), np.float64(-44.7138813861078)]</t>
+  </si>
+  <si>
+    <t>[np.float64(983.6037397507005), np.float64(-47.39863876381071)]</t>
+  </si>
+  <si>
+    <t>[np.float64(160.2961530508832), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(312.008453926336), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(942.2401402613564), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(320.3420240254176), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(982.8601381953165), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(716.5954621447797), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(381.3830877881243), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(546.8541378167012), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(765.9598335336275), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(851.5174394138554), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(813.9160291435797), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(64.02627788007675), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(894.2395375973165), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(786.8916893014919), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(747.2928036125347), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(866.7035085301883), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(886.0994448771776), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(720.8303210883616), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(675.3629822820552), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(322.0840849288688), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(33.54151763540825), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(297.88810275817923), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(835.317847706138), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(306.21831016689316), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(57.99243447011049), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(390.25076914897795), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(721.5409497568218), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(177.74749893631747), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(885.2130201980872), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(630.0936424475204), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(947.7662795650203), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(317.1980220508711), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(83.57933451742196), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(121.42668198363371), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(302.3741936539596), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(402.8376028285825), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(474.79028415099253), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(962.5222470904205), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(839.6943677116317), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(109.19871242852952), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(849.4034826034084), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(426.95626934096185), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(304.9579860392654), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(201.28996376221608), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(896.9931429636953), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(281.60486886981596), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(340.32238859732536), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(296.88941582071305), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(70.36852230923563), np.float64(0.0)]</t>
+  </si>
+  <si>
+    <t>[np.float64(983.6037397507005), np.float64(0.0)]</t>
   </si>
 </sst>
 </file>
@@ -798,25 +795,25 @@
         <v>2</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
         <v>28</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>29</v>
-      </c>
       <c r="I2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -827,25 +824,25 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -856,25 +853,25 @@
         <v>2</v>
       </c>
       <c r="C4">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -885,25 +882,25 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -914,25 +911,25 @@
         <v>2</v>
       </c>
       <c r="C6">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
       <c r="H6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -943,25 +940,25 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -972,25 +969,25 @@
         <v>2</v>
       </c>
       <c r="C8">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>2</v>
       </c>
       <c r="H8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1001,25 +998,25 @@
         <v>2</v>
       </c>
       <c r="C9">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
         <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1030,25 +1027,25 @@
         <v>2</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
         <v>16</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1059,25 +1056,25 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1088,25 +1085,25 @@
         <v>2</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1117,25 +1114,25 @@
         <v>2</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1146,25 +1143,25 @@
         <v>2</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1175,25 +1172,25 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1204,25 +1201,25 @@
         <v>2</v>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1233,25 +1230,25 @@
         <v>2</v>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1262,25 +1259,25 @@
         <v>2</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
         <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I18" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -1291,25 +1288,25 @@
         <v>2</v>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -1320,25 +1317,25 @@
         <v>2</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -1349,25 +1346,25 @@
         <v>2</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -1381,22 +1378,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I22" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -1407,25 +1404,25 @@
         <v>2</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -1439,22 +1436,22 @@
         <v>15</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1465,25 +1462,25 @@
         <v>2</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -1494,25 +1491,25 @@
         <v>2</v>
       </c>
       <c r="C26">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D26" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -1523,25 +1520,25 @@
         <v>2</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -1552,25 +1549,25 @@
         <v>2</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -1581,25 +1578,25 @@
         <v>2</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1610,25 +1607,25 @@
         <v>2</v>
       </c>
       <c r="C30">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -1639,25 +1636,25 @@
         <v>2</v>
       </c>
       <c r="C31">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D31" t="s">
         <v>22</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -1668,25 +1665,25 @@
         <v>2</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D32" t="s">
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -1697,25 +1694,25 @@
         <v>2</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -1726,25 +1723,25 @@
         <v>2</v>
       </c>
       <c r="C34">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D34" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -1758,22 +1755,22 @@
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E35" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -1787,22 +1784,22 @@
         <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I36" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -1813,25 +1810,25 @@
         <v>2</v>
       </c>
       <c r="C37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D37" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E37" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -1842,25 +1839,25 @@
         <v>2</v>
       </c>
       <c r="C38">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E38" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -1871,25 +1868,25 @@
         <v>2</v>
       </c>
       <c r="C39">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I39" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -1900,25 +1897,25 @@
         <v>2</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I40" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -1929,25 +1926,25 @@
         <v>2</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I41" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -1958,25 +1955,25 @@
         <v>2</v>
       </c>
       <c r="C42">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I42" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -1987,25 +1984,25 @@
         <v>2</v>
       </c>
       <c r="C43">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I43" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -2016,25 +2013,25 @@
         <v>2</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D44" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E44" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I44" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -2045,25 +2042,25 @@
         <v>2</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I45" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -2074,25 +2071,25 @@
         <v>2</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D46" t="s">
         <v>19</v>
       </c>
       <c r="E46" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I46" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -2106,22 +2103,22 @@
         <v>6</v>
       </c>
       <c r="D47" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E47" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -2132,25 +2129,25 @@
         <v>2</v>
       </c>
       <c r="C48">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I48" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -2161,25 +2158,25 @@
         <v>2</v>
       </c>
       <c r="C49">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D49" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="E49" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I49" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -2190,25 +2187,25 @@
         <v>2</v>
       </c>
       <c r="C50">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D50" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F50" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -2219,25 +2216,25 @@
         <v>2</v>
       </c>
       <c r="C51">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G51">
         <v>2</v>
       </c>
       <c r="H51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I51" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
